--- a/docs/Raw Data/Municipalities/geostat-population-regional-gdp/municipal-population-and-regional-gdp.xlsx
+++ b/docs/Raw Data/Municipalities/geostat-population-regional-gdp/municipal-population-and-regional-gdp.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R78a3f776b6dd4a0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Population" sheetId="2" r:id="R2a3b454e5b114659"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional GDP" sheetId="3" r:id="R39d7230ee4444713"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geography map" sheetId="4" r:id="R045bc735f4384c58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R596542cc24a549b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Population" sheetId="2" r:id="R2335569669ea4d24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional GDP" sheetId="3" r:id="R604d9beaed414478"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geography map" sheetId="4" r:id="Rd6be994b98f54f6c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -431,7 +431,7 @@
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="20" t="str">
-        <x:v>Review date</x:v>
+        <x:v>Retrieval/review date</x:v>
       </x:c>
       <x:c r="B10" s="24" t="n">
         <x:v>46237</x:v>
@@ -483,7 +483,7 @@
     <x:col min="8" max="8" width="42" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="66" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="116" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -557,7 +557,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K2" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 5; year 2015 column W (cell W5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L2" s="32" t="n">
         <x:v>46237</x:v>
@@ -595,7 +595,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K3" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 9; year 2015 column W (cell W9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L3" s="32" t="n">
         <x:v>46237</x:v>
@@ -633,7 +633,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2015 column W (cell W11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L4" s="32" t="n">
         <x:v>46237</x:v>
@@ -671,7 +671,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K5" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2015 column W (cell W13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L5" s="32" t="n">
         <x:v>46237</x:v>
@@ -709,7 +709,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K6" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2015 column W (cell W10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L6" s="32" t="n">
         <x:v>46237</x:v>
@@ -747,7 +747,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K7" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2015 column W (cell W12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L7" s="32" t="n">
         <x:v>46237</x:v>
@@ -785,7 +785,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K8" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2015 column W (cell W14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L8" s="32" t="n">
         <x:v>46237</x:v>
@@ -823,7 +823,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K9" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 35; year 2015 column W (cell W35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L9" s="32" t="n">
         <x:v>46237</x:v>
@@ -861,7 +861,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K10" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2015 column W (cell W36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L10" s="32" t="n">
         <x:v>46237</x:v>
@@ -899,7 +899,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K11" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2015 column W (cell W37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L11" s="32" t="n">
         <x:v>46237</x:v>
@@ -937,7 +937,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K12" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2015 column W (cell W38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L12" s="32" t="n">
         <x:v>46237</x:v>
@@ -975,7 +975,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K13" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2015 column W (cell W39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L13" s="32" t="n">
         <x:v>46237</x:v>
@@ -1013,7 +1013,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K14" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2015 column W (cell W40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L14" s="32" t="n">
         <x:v>46237</x:v>
@@ -1051,7 +1051,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K15" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2015 column W (cell W41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L15" s="32" t="n">
         <x:v>46237</x:v>
@@ -1089,7 +1089,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K16" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2015 column W (cell W42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L16" s="32" t="n">
         <x:v>46237</x:v>
@@ -1127,7 +1127,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K17" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 21; year 2015 column W (cell W21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L17" s="32" t="n">
         <x:v>46237</x:v>
@@ -1165,7 +1165,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K18" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2015 column W (cell W30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L18" s="32" t="n">
         <x:v>46237</x:v>
@@ -1203,7 +1203,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K19" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2015 column W (cell W28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L19" s="32" t="n">
         <x:v>46237</x:v>
@@ -1241,7 +1241,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2015 column W (cell W29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L20" s="32" t="n">
         <x:v>46237</x:v>
@@ -1279,7 +1279,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2015 column W (cell W22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L21" s="32" t="n">
         <x:v>46237</x:v>
@@ -1317,7 +1317,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K22" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2015 column W (cell W23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L22" s="32" t="n">
         <x:v>46237</x:v>
@@ -1355,7 +1355,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2015 column W (cell W24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L23" s="32" t="n">
         <x:v>46237</x:v>
@@ -1393,7 +1393,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K24" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2015 column W (cell W25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L24" s="32" t="n">
         <x:v>46237</x:v>
@@ -1431,7 +1431,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K25" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2015 column W (cell W26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L25" s="32" t="n">
         <x:v>46237</x:v>
@@ -1469,7 +1469,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2015 column W (cell W27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L26" s="32" t="n">
         <x:v>46237</x:v>
@@ -1507,7 +1507,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K27" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2015 column W (cell W31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L27" s="32" t="n">
         <x:v>46237</x:v>
@@ -1545,7 +1545,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2015 column W (cell W32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L28" s="32" t="n">
         <x:v>46237</x:v>
@@ -1583,7 +1583,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K29" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 58; year 2015 column W (cell W58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L29" s="32" t="n">
         <x:v>46237</x:v>
@@ -1621,7 +1621,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2015 column W (cell W60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L30" s="32" t="n">
         <x:v>46237</x:v>
@@ -1659,7 +1659,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K31" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2015 column W (cell W59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L31" s="32" t="n">
         <x:v>46237</x:v>
@@ -1697,7 +1697,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K32" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2015 column W (cell W61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L32" s="32" t="n">
         <x:v>46237</x:v>
@@ -1735,7 +1735,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K33" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2015 column W (cell W62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L33" s="32" t="n">
         <x:v>46237</x:v>
@@ -1773,7 +1773,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K34" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2015 column W (cell W63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L34" s="32" t="n">
         <x:v>46237</x:v>
@@ -1811,7 +1811,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K35" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2015 column W (cell W64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L35" s="32" t="n">
         <x:v>46237</x:v>
@@ -1849,7 +1849,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K36" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2015 column W (cell W65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L36" s="32" t="n">
         <x:v>46237</x:v>
@@ -1887,7 +1887,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2015 column W (cell W66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L37" s="32" t="n">
         <x:v>46237</x:v>
@@ -1925,7 +1925,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K38" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 85; year 2015 column W (cell W85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L38" s="32" t="n">
         <x:v>46237</x:v>
@@ -1963,7 +1963,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K39" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2015 column W (cell W89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L39" s="32" t="n">
         <x:v>46237</x:v>
@@ -2001,7 +2001,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K40" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 88; year 2015 column W (cell W88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L40" s="32" t="n">
         <x:v>46237</x:v>
@@ -2039,7 +2039,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K41" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 91; year 2015 column W (cell W91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L41" s="32" t="n">
         <x:v>46237</x:v>
@@ -2077,7 +2077,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K42" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 76; year 2015 column W (cell W76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L42" s="32" t="n">
         <x:v>46237</x:v>
@@ -2115,7 +2115,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K43" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2015 column W (cell W77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L43" s="32" t="n">
         <x:v>46237</x:v>
@@ -2153,7 +2153,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K44" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2015 column W (cell W78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L44" s="32" t="n">
         <x:v>46237</x:v>
@@ -2191,7 +2191,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K45" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2015 column W (cell W79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L45" s="32" t="n">
         <x:v>46237</x:v>
@@ -2229,7 +2229,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K46" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2015 column W (cell W80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L46" s="32" t="n">
         <x:v>46237</x:v>
@@ -2267,7 +2267,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K47" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2015 column W (cell W81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L47" s="32" t="n">
         <x:v>46237</x:v>
@@ -2305,7 +2305,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K48" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2015 column W (cell W82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L48" s="32" t="n">
         <x:v>46237</x:v>
@@ -2343,7 +2343,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K49" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 17; year 2015 column W (cell W17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L49" s="32" t="n">
         <x:v>46237</x:v>
@@ -2381,7 +2381,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K50" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2015 column W (cell W18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L50" s="32" t="n">
         <x:v>46237</x:v>
@@ -2419,7 +2419,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K51" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2015 column W (cell W19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L51" s="32" t="n">
         <x:v>46237</x:v>
@@ -2457,7 +2457,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K52" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2015 column W (cell W73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L52" s="32" t="n">
         <x:v>46237</x:v>
@@ -2495,7 +2495,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K53" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 69; year 2015 column W (cell W69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L53" s="32" t="n">
         <x:v>46237</x:v>
@@ -2533,7 +2533,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K54" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2015 column W (cell W70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L54" s="32" t="n">
         <x:v>46237</x:v>
@@ -2571,7 +2571,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K55" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2015 column W (cell W71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L55" s="32" t="n">
         <x:v>46237</x:v>
@@ -2609,7 +2609,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K56" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2015 column W (cell W72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L56" s="32" t="n">
         <x:v>46237</x:v>
@@ -2647,7 +2647,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K57" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2015 column W (cell W74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L57" s="32" t="n">
         <x:v>46237</x:v>
@@ -2685,7 +2685,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K58" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 46; year 2015 column W (cell W46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L58" s="32" t="n">
         <x:v>46237</x:v>
@@ -2723,7 +2723,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K59" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2015 column W (cell W47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L59" s="32" t="n">
         <x:v>46237</x:v>
@@ -2761,7 +2761,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K60" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2015 column W (cell W48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L60" s="32" t="n">
         <x:v>46237</x:v>
@@ -2799,7 +2799,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K61" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2015 column W (cell W49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L61" s="32" t="n">
         <x:v>46237</x:v>
@@ -2837,7 +2837,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K62" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 52; year 2015 column W (cell W52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L62" s="32" t="n">
         <x:v>46237</x:v>
@@ -2875,7 +2875,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K63" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2015 column W (cell W53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L63" s="32" t="n">
         <x:v>46237</x:v>
@@ -2913,7 +2913,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K64" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2015 column W (cell W54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L64" s="32" t="n">
         <x:v>46237</x:v>
@@ -2951,7 +2951,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K65" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2015 column W (cell W55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L65" s="32" t="n">
         <x:v>46237</x:v>
@@ -2989,7 +2989,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K66" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 5; year 2016 column X (cell X5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L66" s="32" t="n">
         <x:v>46237</x:v>
@@ -3027,7 +3027,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K67" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 9; year 2016 column X (cell X9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L67" s="32" t="n">
         <x:v>46237</x:v>
@@ -3065,7 +3065,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K68" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2016 column X (cell X11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L68" s="32" t="n">
         <x:v>46237</x:v>
@@ -3103,7 +3103,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K69" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2016 column X (cell X13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L69" s="32" t="n">
         <x:v>46237</x:v>
@@ -3141,7 +3141,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K70" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2016 column X (cell X10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L70" s="32" t="n">
         <x:v>46237</x:v>
@@ -3179,7 +3179,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K71" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2016 column X (cell X12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L71" s="32" t="n">
         <x:v>46237</x:v>
@@ -3217,7 +3217,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K72" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2016 column X (cell X14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L72" s="32" t="n">
         <x:v>46237</x:v>
@@ -3255,7 +3255,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K73" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 35; year 2016 column X (cell X35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L73" s="32" t="n">
         <x:v>46237</x:v>
@@ -3293,7 +3293,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K74" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2016 column X (cell X36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L74" s="32" t="n">
         <x:v>46237</x:v>
@@ -3331,7 +3331,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K75" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2016 column X (cell X37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L75" s="32" t="n">
         <x:v>46237</x:v>
@@ -3369,7 +3369,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K76" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2016 column X (cell X38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L76" s="32" t="n">
         <x:v>46237</x:v>
@@ -3407,7 +3407,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K77" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2016 column X (cell X39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L77" s="32" t="n">
         <x:v>46237</x:v>
@@ -3445,7 +3445,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K78" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2016 column X (cell X40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L78" s="32" t="n">
         <x:v>46237</x:v>
@@ -3483,7 +3483,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K79" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2016 column X (cell X41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L79" s="32" t="n">
         <x:v>46237</x:v>
@@ -3521,7 +3521,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K80" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2016 column X (cell X42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L80" s="32" t="n">
         <x:v>46237</x:v>
@@ -3559,7 +3559,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K81" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 21; year 2016 column X (cell X21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L81" s="32" t="n">
         <x:v>46237</x:v>
@@ -3597,7 +3597,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2016 column X (cell X30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L82" s="32" t="n">
         <x:v>46237</x:v>
@@ -3635,7 +3635,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K83" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2016 column X (cell X28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L83" s="32" t="n">
         <x:v>46237</x:v>
@@ -3673,7 +3673,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K84" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2016 column X (cell X29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L84" s="32" t="n">
         <x:v>46237</x:v>
@@ -3711,7 +3711,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K85" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2016 column X (cell X22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L85" s="32" t="n">
         <x:v>46237</x:v>
@@ -3749,7 +3749,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K86" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2016 column X (cell X23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L86" s="32" t="n">
         <x:v>46237</x:v>
@@ -3787,7 +3787,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K87" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2016 column X (cell X24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L87" s="32" t="n">
         <x:v>46237</x:v>
@@ -3825,7 +3825,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K88" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2016 column X (cell X25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L88" s="32" t="n">
         <x:v>46237</x:v>
@@ -3863,7 +3863,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K89" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2016 column X (cell X26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L89" s="32" t="n">
         <x:v>46237</x:v>
@@ -3901,7 +3901,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K90" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2016 column X (cell X27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L90" s="32" t="n">
         <x:v>46237</x:v>
@@ -3939,7 +3939,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K91" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2016 column X (cell X31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L91" s="32" t="n">
         <x:v>46237</x:v>
@@ -3977,7 +3977,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K92" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2016 column X (cell X32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L92" s="32" t="n">
         <x:v>46237</x:v>
@@ -4015,7 +4015,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K93" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 58; year 2016 column X (cell X58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L93" s="32" t="n">
         <x:v>46237</x:v>
@@ -4053,7 +4053,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K94" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2016 column X (cell X60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L94" s="32" t="n">
         <x:v>46237</x:v>
@@ -4091,7 +4091,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K95" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2016 column X (cell X59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L95" s="32" t="n">
         <x:v>46237</x:v>
@@ -4129,7 +4129,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K96" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2016 column X (cell X61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L96" s="32" t="n">
         <x:v>46237</x:v>
@@ -4167,7 +4167,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K97" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2016 column X (cell X62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L97" s="32" t="n">
         <x:v>46237</x:v>
@@ -4205,7 +4205,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K98" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2016 column X (cell X63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L98" s="32" t="n">
         <x:v>46237</x:v>
@@ -4243,7 +4243,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K99" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2016 column X (cell X64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L99" s="32" t="n">
         <x:v>46237</x:v>
@@ -4281,7 +4281,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K100" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2016 column X (cell X65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L100" s="32" t="n">
         <x:v>46237</x:v>
@@ -4319,7 +4319,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K101" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2016 column X (cell X66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L101" s="32" t="n">
         <x:v>46237</x:v>
@@ -4357,7 +4357,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K102" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 85; year 2016 column X (cell X85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L102" s="32" t="n">
         <x:v>46237</x:v>
@@ -4395,7 +4395,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K103" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2016 column X (cell X89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L103" s="32" t="n">
         <x:v>46237</x:v>
@@ -4433,7 +4433,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K104" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 88; year 2016 column X (cell X88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L104" s="32" t="n">
         <x:v>46237</x:v>
@@ -4471,7 +4471,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K105" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 91; year 2016 column X (cell X91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L105" s="32" t="n">
         <x:v>46237</x:v>
@@ -4509,7 +4509,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K106" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 76; year 2016 column X (cell X76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L106" s="32" t="n">
         <x:v>46237</x:v>
@@ -4547,7 +4547,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K107" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2016 column X (cell X77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L107" s="32" t="n">
         <x:v>46237</x:v>
@@ -4585,7 +4585,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K108" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2016 column X (cell X78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L108" s="32" t="n">
         <x:v>46237</x:v>
@@ -4623,7 +4623,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K109" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2016 column X (cell X79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L109" s="32" t="n">
         <x:v>46237</x:v>
@@ -4661,7 +4661,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K110" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2016 column X (cell X80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L110" s="32" t="n">
         <x:v>46237</x:v>
@@ -4699,7 +4699,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K111" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2016 column X (cell X81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L111" s="32" t="n">
         <x:v>46237</x:v>
@@ -4737,7 +4737,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K112" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2016 column X (cell X82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L112" s="32" t="n">
         <x:v>46237</x:v>
@@ -4775,7 +4775,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K113" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 17; year 2016 column X (cell X17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L113" s="32" t="n">
         <x:v>46237</x:v>
@@ -4813,7 +4813,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K114" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2016 column X (cell X18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L114" s="32" t="n">
         <x:v>46237</x:v>
@@ -4851,7 +4851,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K115" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2016 column X (cell X19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L115" s="32" t="n">
         <x:v>46237</x:v>
@@ -4889,7 +4889,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K116" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2016 column X (cell X73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L116" s="32" t="n">
         <x:v>46237</x:v>
@@ -4927,7 +4927,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K117" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 69; year 2016 column X (cell X69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L117" s="32" t="n">
         <x:v>46237</x:v>
@@ -4965,7 +4965,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K118" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2016 column X (cell X70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L118" s="32" t="n">
         <x:v>46237</x:v>
@@ -5003,7 +5003,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K119" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2016 column X (cell X71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L119" s="32" t="n">
         <x:v>46237</x:v>
@@ -5041,7 +5041,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K120" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2016 column X (cell X72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L120" s="32" t="n">
         <x:v>46237</x:v>
@@ -5079,7 +5079,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K121" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2016 column X (cell X74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L121" s="32" t="n">
         <x:v>46237</x:v>
@@ -5117,7 +5117,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K122" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 46; year 2016 column X (cell X46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L122" s="32" t="n">
         <x:v>46237</x:v>
@@ -5155,7 +5155,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K123" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2016 column X (cell X47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L123" s="32" t="n">
         <x:v>46237</x:v>
@@ -5193,7 +5193,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K124" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2016 column X (cell X48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L124" s="32" t="n">
         <x:v>46237</x:v>
@@ -5231,7 +5231,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K125" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2016 column X (cell X49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L125" s="32" t="n">
         <x:v>46237</x:v>
@@ -5269,7 +5269,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K126" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 52; year 2016 column X (cell X52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L126" s="32" t="n">
         <x:v>46237</x:v>
@@ -5307,7 +5307,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K127" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2016 column X (cell X53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L127" s="32" t="n">
         <x:v>46237</x:v>
@@ -5345,7 +5345,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K128" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2016 column X (cell X54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L128" s="32" t="n">
         <x:v>46237</x:v>
@@ -5383,7 +5383,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K129" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2016 column X (cell X55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L129" s="32" t="n">
         <x:v>46237</x:v>
@@ -5421,7 +5421,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K130" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 5; year 2017 column Y (cell Y5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L130" s="32" t="n">
         <x:v>46237</x:v>
@@ -5459,7 +5459,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K131" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 9; year 2017 column Y (cell Y9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L131" s="32" t="n">
         <x:v>46237</x:v>
@@ -5497,7 +5497,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K132" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2017 column Y (cell Y11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L132" s="32" t="n">
         <x:v>46237</x:v>
@@ -5535,7 +5535,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K133" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2017 column Y (cell Y13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L133" s="32" t="n">
         <x:v>46237</x:v>
@@ -5573,7 +5573,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K134" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2017 column Y (cell Y10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L134" s="32" t="n">
         <x:v>46237</x:v>
@@ -5611,7 +5611,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K135" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2017 column Y (cell Y12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L135" s="32" t="n">
         <x:v>46237</x:v>
@@ -5649,7 +5649,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K136" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2017 column Y (cell Y14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L136" s="32" t="n">
         <x:v>46237</x:v>
@@ -5687,7 +5687,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K137" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 35; year 2017 column Y (cell Y35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L137" s="32" t="n">
         <x:v>46237</x:v>
@@ -5725,7 +5725,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K138" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2017 column Y (cell Y36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L138" s="32" t="n">
         <x:v>46237</x:v>
@@ -5763,7 +5763,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K139" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2017 column Y (cell Y37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L139" s="32" t="n">
         <x:v>46237</x:v>
@@ -5801,7 +5801,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K140" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2017 column Y (cell Y38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L140" s="32" t="n">
         <x:v>46237</x:v>
@@ -5839,7 +5839,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K141" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2017 column Y (cell Y39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L141" s="32" t="n">
         <x:v>46237</x:v>
@@ -5877,7 +5877,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K142" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2017 column Y (cell Y40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L142" s="32" t="n">
         <x:v>46237</x:v>
@@ -5915,7 +5915,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K143" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2017 column Y (cell Y41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L143" s="32" t="n">
         <x:v>46237</x:v>
@@ -5953,7 +5953,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K144" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2017 column Y (cell Y42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L144" s="32" t="n">
         <x:v>46237</x:v>
@@ -5991,7 +5991,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K145" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 21; year 2017 column Y (cell Y21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L145" s="32" t="n">
         <x:v>46237</x:v>
@@ -6029,7 +6029,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K146" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2017 column Y (cell Y30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L146" s="32" t="n">
         <x:v>46237</x:v>
@@ -6067,7 +6067,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K147" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2017 column Y (cell Y28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L147" s="32" t="n">
         <x:v>46237</x:v>
@@ -6105,7 +6105,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K148" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2017 column Y (cell Y29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L148" s="32" t="n">
         <x:v>46237</x:v>
@@ -6143,7 +6143,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K149" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2017 column Y (cell Y22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L149" s="32" t="n">
         <x:v>46237</x:v>
@@ -6181,7 +6181,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K150" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2017 column Y (cell Y23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L150" s="32" t="n">
         <x:v>46237</x:v>
@@ -6219,7 +6219,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K151" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2017 column Y (cell Y24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L151" s="32" t="n">
         <x:v>46237</x:v>
@@ -6257,7 +6257,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K152" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2017 column Y (cell Y25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L152" s="32" t="n">
         <x:v>46237</x:v>
@@ -6295,7 +6295,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K153" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2017 column Y (cell Y26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L153" s="32" t="n">
         <x:v>46237</x:v>
@@ -6333,7 +6333,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K154" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2017 column Y (cell Y27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L154" s="32" t="n">
         <x:v>46237</x:v>
@@ -6371,7 +6371,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K155" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2017 column Y (cell Y31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L155" s="32" t="n">
         <x:v>46237</x:v>
@@ -6409,7 +6409,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K156" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2017 column Y (cell Y32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L156" s="32" t="n">
         <x:v>46237</x:v>
@@ -6447,7 +6447,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K157" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 58; year 2017 column Y (cell Y58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L157" s="32" t="n">
         <x:v>46237</x:v>
@@ -6485,7 +6485,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K158" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2017 column Y (cell Y60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L158" s="32" t="n">
         <x:v>46237</x:v>
@@ -6523,7 +6523,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K159" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2017 column Y (cell Y59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L159" s="32" t="n">
         <x:v>46237</x:v>
@@ -6561,7 +6561,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K160" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2017 column Y (cell Y61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L160" s="32" t="n">
         <x:v>46237</x:v>
@@ -6599,7 +6599,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K161" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2017 column Y (cell Y62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L161" s="32" t="n">
         <x:v>46237</x:v>
@@ -6637,7 +6637,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K162" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2017 column Y (cell Y63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L162" s="32" t="n">
         <x:v>46237</x:v>
@@ -6675,7 +6675,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K163" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2017 column Y (cell Y64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L163" s="32" t="n">
         <x:v>46237</x:v>
@@ -6713,7 +6713,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K164" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2017 column Y (cell Y65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L164" s="32" t="n">
         <x:v>46237</x:v>
@@ -6751,7 +6751,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K165" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2017 column Y (cell Y66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L165" s="32" t="n">
         <x:v>46237</x:v>
@@ -6789,7 +6789,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K166" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 85; year 2017 column Y (cell Y85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L166" s="32" t="n">
         <x:v>46237</x:v>
@@ -6827,7 +6827,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K167" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2017 column Y (cell Y89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L167" s="32" t="n">
         <x:v>46237</x:v>
@@ -6865,7 +6865,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K168" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 88; year 2017 column Y (cell Y88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L168" s="32" t="n">
         <x:v>46237</x:v>
@@ -6903,7 +6903,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K169" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 91; year 2017 column Y (cell Y91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L169" s="32" t="n">
         <x:v>46237</x:v>
@@ -6941,7 +6941,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K170" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 76; year 2017 column Y (cell Y76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L170" s="32" t="n">
         <x:v>46237</x:v>
@@ -6979,7 +6979,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K171" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2017 column Y (cell Y77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L171" s="32" t="n">
         <x:v>46237</x:v>
@@ -7017,7 +7017,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K172" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2017 column Y (cell Y78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L172" s="32" t="n">
         <x:v>46237</x:v>
@@ -7055,7 +7055,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K173" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2017 column Y (cell Y79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L173" s="32" t="n">
         <x:v>46237</x:v>
@@ -7093,7 +7093,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K174" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2017 column Y (cell Y80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L174" s="32" t="n">
         <x:v>46237</x:v>
@@ -7131,7 +7131,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K175" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2017 column Y (cell Y81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L175" s="32" t="n">
         <x:v>46237</x:v>
@@ -7169,7 +7169,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K176" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2017 column Y (cell Y82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L176" s="32" t="n">
         <x:v>46237</x:v>
@@ -7207,7 +7207,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K177" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 17; year 2017 column Y (cell Y17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L177" s="32" t="n">
         <x:v>46237</x:v>
@@ -7245,7 +7245,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K178" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2017 column Y (cell Y18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L178" s="32" t="n">
         <x:v>46237</x:v>
@@ -7283,7 +7283,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K179" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2017 column Y (cell Y19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L179" s="32" t="n">
         <x:v>46237</x:v>
@@ -7321,7 +7321,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K180" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2017 column Y (cell Y73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L180" s="32" t="n">
         <x:v>46237</x:v>
@@ -7359,7 +7359,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K181" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 69; year 2017 column Y (cell Y69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L181" s="32" t="n">
         <x:v>46237</x:v>
@@ -7397,7 +7397,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K182" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2017 column Y (cell Y70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L182" s="32" t="n">
         <x:v>46237</x:v>
@@ -7435,7 +7435,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K183" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2017 column Y (cell Y71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L183" s="32" t="n">
         <x:v>46237</x:v>
@@ -7473,7 +7473,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K184" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2017 column Y (cell Y72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L184" s="32" t="n">
         <x:v>46237</x:v>
@@ -7511,7 +7511,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K185" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2017 column Y (cell Y74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L185" s="32" t="n">
         <x:v>46237</x:v>
@@ -7549,7 +7549,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K186" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 46; year 2017 column Y (cell Y46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L186" s="32" t="n">
         <x:v>46237</x:v>
@@ -7587,7 +7587,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K187" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2017 column Y (cell Y47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L187" s="32" t="n">
         <x:v>46237</x:v>
@@ -7625,7 +7625,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K188" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2017 column Y (cell Y48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L188" s="32" t="n">
         <x:v>46237</x:v>
@@ -7663,7 +7663,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K189" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2017 column Y (cell Y49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L189" s="32" t="n">
         <x:v>46237</x:v>
@@ -7701,7 +7701,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K190" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 52; year 2017 column Y (cell Y52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L190" s="32" t="n">
         <x:v>46237</x:v>
@@ -7739,7 +7739,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K191" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2017 column Y (cell Y53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L191" s="32" t="n">
         <x:v>46237</x:v>
@@ -7777,7 +7777,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K192" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2017 column Y (cell Y54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L192" s="32" t="n">
         <x:v>46237</x:v>
@@ -7815,7 +7815,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K193" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2017 column Y (cell Y55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L193" s="32" t="n">
         <x:v>46237</x:v>
@@ -7853,7 +7853,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K194" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 5; year 2018 column Z (cell Z5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L194" s="32" t="n">
         <x:v>46237</x:v>
@@ -7891,7 +7891,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K195" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 9; year 2018 column Z (cell Z9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L195" s="32" t="n">
         <x:v>46237</x:v>
@@ -7929,7 +7929,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K196" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2018 column Z (cell Z11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L196" s="32" t="n">
         <x:v>46237</x:v>
@@ -7967,7 +7967,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K197" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2018 column Z (cell Z13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L197" s="32" t="n">
         <x:v>46237</x:v>
@@ -8005,7 +8005,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K198" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2018 column Z (cell Z10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L198" s="32" t="n">
         <x:v>46237</x:v>
@@ -8043,7 +8043,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K199" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2018 column Z (cell Z12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L199" s="32" t="n">
         <x:v>46237</x:v>
@@ -8081,7 +8081,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K200" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2018 column Z (cell Z14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L200" s="32" t="n">
         <x:v>46237</x:v>
@@ -8119,7 +8119,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K201" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 35; year 2018 column Z (cell Z35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L201" s="32" t="n">
         <x:v>46237</x:v>
@@ -8157,7 +8157,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K202" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2018 column Z (cell Z36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L202" s="32" t="n">
         <x:v>46237</x:v>
@@ -8195,7 +8195,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K203" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2018 column Z (cell Z37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L203" s="32" t="n">
         <x:v>46237</x:v>
@@ -8233,7 +8233,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K204" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2018 column Z (cell Z38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L204" s="32" t="n">
         <x:v>46237</x:v>
@@ -8271,7 +8271,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K205" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2018 column Z (cell Z39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L205" s="32" t="n">
         <x:v>46237</x:v>
@@ -8309,7 +8309,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K206" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2018 column Z (cell Z40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L206" s="32" t="n">
         <x:v>46237</x:v>
@@ -8347,7 +8347,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K207" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2018 column Z (cell Z41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L207" s="32" t="n">
         <x:v>46237</x:v>
@@ -8385,7 +8385,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K208" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2018 column Z (cell Z42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L208" s="32" t="n">
         <x:v>46237</x:v>
@@ -8423,7 +8423,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K209" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 21; year 2018 column Z (cell Z21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L209" s="32" t="n">
         <x:v>46237</x:v>
@@ -8461,7 +8461,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K210" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2018 column Z (cell Z30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L210" s="32" t="n">
         <x:v>46237</x:v>
@@ -8499,7 +8499,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K211" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2018 column Z (cell Z28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L211" s="32" t="n">
         <x:v>46237</x:v>
@@ -8537,7 +8537,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K212" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2018 column Z (cell Z29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L212" s="32" t="n">
         <x:v>46237</x:v>
@@ -8575,7 +8575,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K213" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2018 column Z (cell Z22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L213" s="32" t="n">
         <x:v>46237</x:v>
@@ -8613,7 +8613,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K214" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2018 column Z (cell Z23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L214" s="32" t="n">
         <x:v>46237</x:v>
@@ -8651,7 +8651,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K215" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2018 column Z (cell Z24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L215" s="32" t="n">
         <x:v>46237</x:v>
@@ -8689,7 +8689,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K216" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2018 column Z (cell Z25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L216" s="32" t="n">
         <x:v>46237</x:v>
@@ -8727,7 +8727,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K217" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2018 column Z (cell Z26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L217" s="32" t="n">
         <x:v>46237</x:v>
@@ -8765,7 +8765,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K218" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2018 column Z (cell Z27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L218" s="32" t="n">
         <x:v>46237</x:v>
@@ -8803,7 +8803,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K219" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2018 column Z (cell Z31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L219" s="32" t="n">
         <x:v>46237</x:v>
@@ -8841,7 +8841,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K220" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2018 column Z (cell Z32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L220" s="32" t="n">
         <x:v>46237</x:v>
@@ -8879,7 +8879,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K221" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 58; year 2018 column Z (cell Z58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L221" s="32" t="n">
         <x:v>46237</x:v>
@@ -8917,7 +8917,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K222" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2018 column Z (cell Z60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L222" s="32" t="n">
         <x:v>46237</x:v>
@@ -8955,7 +8955,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K223" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2018 column Z (cell Z59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L223" s="32" t="n">
         <x:v>46237</x:v>
@@ -8993,7 +8993,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K224" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2018 column Z (cell Z61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L224" s="32" t="n">
         <x:v>46237</x:v>
@@ -9031,7 +9031,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K225" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2018 column Z (cell Z62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L225" s="32" t="n">
         <x:v>46237</x:v>
@@ -9069,7 +9069,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K226" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2018 column Z (cell Z63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L226" s="32" t="n">
         <x:v>46237</x:v>
@@ -9107,7 +9107,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K227" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2018 column Z (cell Z64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L227" s="32" t="n">
         <x:v>46237</x:v>
@@ -9145,7 +9145,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K228" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2018 column Z (cell Z65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L228" s="32" t="n">
         <x:v>46237</x:v>
@@ -9183,7 +9183,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K229" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2018 column Z (cell Z66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L229" s="32" t="n">
         <x:v>46237</x:v>
@@ -9221,7 +9221,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K230" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 85; year 2018 column Z (cell Z85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L230" s="32" t="n">
         <x:v>46237</x:v>
@@ -9259,7 +9259,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K231" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2018 column Z (cell Z89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L231" s="32" t="n">
         <x:v>46237</x:v>
@@ -9297,7 +9297,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K232" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 88; year 2018 column Z (cell Z88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L232" s="32" t="n">
         <x:v>46237</x:v>
@@ -9335,7 +9335,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K233" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 91; year 2018 column Z (cell Z91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L233" s="32" t="n">
         <x:v>46237</x:v>
@@ -9373,7 +9373,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K234" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 76; year 2018 column Z (cell Z76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L234" s="32" t="n">
         <x:v>46237</x:v>
@@ -9411,7 +9411,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K235" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2018 column Z (cell Z77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L235" s="32" t="n">
         <x:v>46237</x:v>
@@ -9449,7 +9449,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K236" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2018 column Z (cell Z78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L236" s="32" t="n">
         <x:v>46237</x:v>
@@ -9487,7 +9487,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K237" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2018 column Z (cell Z79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L237" s="32" t="n">
         <x:v>46237</x:v>
@@ -9525,7 +9525,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K238" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2018 column Z (cell Z80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L238" s="32" t="n">
         <x:v>46237</x:v>
@@ -9563,7 +9563,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K239" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2018 column Z (cell Z81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L239" s="32" t="n">
         <x:v>46237</x:v>
@@ -9601,7 +9601,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K240" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2018 column Z (cell Z82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L240" s="32" t="n">
         <x:v>46237</x:v>
@@ -9639,7 +9639,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K241" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 17; year 2018 column Z (cell Z17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L241" s="32" t="n">
         <x:v>46237</x:v>
@@ -9677,7 +9677,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K242" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2018 column Z (cell Z18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L242" s="32" t="n">
         <x:v>46237</x:v>
@@ -9715,7 +9715,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K243" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2018 column Z (cell Z19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L243" s="32" t="n">
         <x:v>46237</x:v>
@@ -9753,7 +9753,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K244" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2018 column Z (cell Z73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L244" s="32" t="n">
         <x:v>46237</x:v>
@@ -9791,7 +9791,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K245" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 69; year 2018 column Z (cell Z69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L245" s="32" t="n">
         <x:v>46237</x:v>
@@ -9829,7 +9829,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K246" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2018 column Z (cell Z70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L246" s="32" t="n">
         <x:v>46237</x:v>
@@ -9867,7 +9867,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K247" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2018 column Z (cell Z71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L247" s="32" t="n">
         <x:v>46237</x:v>
@@ -9905,7 +9905,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K248" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2018 column Z (cell Z72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L248" s="32" t="n">
         <x:v>46237</x:v>
@@ -9943,7 +9943,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K249" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2018 column Z (cell Z74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L249" s="32" t="n">
         <x:v>46237</x:v>
@@ -9981,7 +9981,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K250" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 46; year 2018 column Z (cell Z46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L250" s="32" t="n">
         <x:v>46237</x:v>
@@ -10019,7 +10019,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K251" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2018 column Z (cell Z47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L251" s="32" t="n">
         <x:v>46237</x:v>
@@ -10057,7 +10057,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K252" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2018 column Z (cell Z48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L252" s="32" t="n">
         <x:v>46237</x:v>
@@ -10095,7 +10095,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K253" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2018 column Z (cell Z49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L253" s="32" t="n">
         <x:v>46237</x:v>
@@ -10133,7 +10133,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K254" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 52; year 2018 column Z (cell Z52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L254" s="32" t="n">
         <x:v>46237</x:v>
@@ -10171,7 +10171,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K255" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2018 column Z (cell Z53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L255" s="32" t="n">
         <x:v>46237</x:v>
@@ -10209,7 +10209,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K256" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2018 column Z (cell Z54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L256" s="32" t="n">
         <x:v>46237</x:v>
@@ -10247,7 +10247,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K257" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2018 column Z (cell Z55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L257" s="32" t="n">
         <x:v>46237</x:v>
@@ -10285,7 +10285,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K258" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 5; year 2019 column AA (cell AA5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L258" s="32" t="n">
         <x:v>46237</x:v>
@@ -10323,7 +10323,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K259" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 9; year 2019 column AA (cell AA9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L259" s="32" t="n">
         <x:v>46237</x:v>
@@ -10361,7 +10361,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K260" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2019 column AA (cell AA11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L260" s="32" t="n">
         <x:v>46237</x:v>
@@ -10399,7 +10399,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K261" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2019 column AA (cell AA13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L261" s="32" t="n">
         <x:v>46237</x:v>
@@ -10437,7 +10437,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K262" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2019 column AA (cell AA10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L262" s="32" t="n">
         <x:v>46237</x:v>
@@ -10475,7 +10475,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K263" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2019 column AA (cell AA12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L263" s="32" t="n">
         <x:v>46237</x:v>
@@ -10513,7 +10513,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K264" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2019 column AA (cell AA14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L264" s="32" t="n">
         <x:v>46237</x:v>
@@ -10551,7 +10551,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K265" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 35; year 2019 column AA (cell AA35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L265" s="32" t="n">
         <x:v>46237</x:v>
@@ -10589,7 +10589,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K266" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2019 column AA (cell AA36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L266" s="32" t="n">
         <x:v>46237</x:v>
@@ -10627,7 +10627,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K267" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2019 column AA (cell AA37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L267" s="32" t="n">
         <x:v>46237</x:v>
@@ -10665,7 +10665,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K268" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2019 column AA (cell AA38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L268" s="32" t="n">
         <x:v>46237</x:v>
@@ -10703,7 +10703,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K269" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2019 column AA (cell AA39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L269" s="32" t="n">
         <x:v>46237</x:v>
@@ -10741,7 +10741,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K270" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2019 column AA (cell AA40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L270" s="32" t="n">
         <x:v>46237</x:v>
@@ -10779,7 +10779,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K271" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2019 column AA (cell AA41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L271" s="32" t="n">
         <x:v>46237</x:v>
@@ -10817,7 +10817,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K272" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2019 column AA (cell AA42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L272" s="32" t="n">
         <x:v>46237</x:v>
@@ -10855,7 +10855,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K273" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 21; year 2019 column AA (cell AA21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L273" s="32" t="n">
         <x:v>46237</x:v>
@@ -10893,7 +10893,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K274" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2019 column AA (cell AA30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L274" s="32" t="n">
         <x:v>46237</x:v>
@@ -10931,7 +10931,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K275" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2019 column AA (cell AA28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L275" s="32" t="n">
         <x:v>46237</x:v>
@@ -10969,7 +10969,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K276" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2019 column AA (cell AA29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L276" s="32" t="n">
         <x:v>46237</x:v>
@@ -11007,7 +11007,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K277" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2019 column AA (cell AA22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L277" s="32" t="n">
         <x:v>46237</x:v>
@@ -11045,7 +11045,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K278" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2019 column AA (cell AA23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L278" s="32" t="n">
         <x:v>46237</x:v>
@@ -11083,7 +11083,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K279" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2019 column AA (cell AA24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L279" s="32" t="n">
         <x:v>46237</x:v>
@@ -11121,7 +11121,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K280" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2019 column AA (cell AA25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L280" s="32" t="n">
         <x:v>46237</x:v>
@@ -11159,7 +11159,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K281" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2019 column AA (cell AA26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L281" s="32" t="n">
         <x:v>46237</x:v>
@@ -11197,7 +11197,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K282" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2019 column AA (cell AA27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L282" s="32" t="n">
         <x:v>46237</x:v>
@@ -11235,7 +11235,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K283" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2019 column AA (cell AA31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L283" s="32" t="n">
         <x:v>46237</x:v>
@@ -11273,7 +11273,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K284" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2019 column AA (cell AA32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L284" s="32" t="n">
         <x:v>46237</x:v>
@@ -11311,7 +11311,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K285" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 58; year 2019 column AA (cell AA58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L285" s="32" t="n">
         <x:v>46237</x:v>
@@ -11349,7 +11349,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K286" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2019 column AA (cell AA60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L286" s="32" t="n">
         <x:v>46237</x:v>
@@ -11387,7 +11387,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K287" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2019 column AA (cell AA59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L287" s="32" t="n">
         <x:v>46237</x:v>
@@ -11425,7 +11425,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K288" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2019 column AA (cell AA61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L288" s="32" t="n">
         <x:v>46237</x:v>
@@ -11463,7 +11463,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K289" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2019 column AA (cell AA62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L289" s="32" t="n">
         <x:v>46237</x:v>
@@ -11501,7 +11501,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K290" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2019 column AA (cell AA63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L290" s="32" t="n">
         <x:v>46237</x:v>
@@ -11539,7 +11539,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K291" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2019 column AA (cell AA64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L291" s="32" t="n">
         <x:v>46237</x:v>
@@ -11577,7 +11577,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K292" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2019 column AA (cell AA65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L292" s="32" t="n">
         <x:v>46237</x:v>
@@ -11615,7 +11615,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K293" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2019 column AA (cell AA66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L293" s="32" t="n">
         <x:v>46237</x:v>
@@ -11653,7 +11653,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K294" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 85; year 2019 column AA (cell AA85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L294" s="32" t="n">
         <x:v>46237</x:v>
@@ -11691,7 +11691,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K295" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2019 column AA (cell AA89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L295" s="32" t="n">
         <x:v>46237</x:v>
@@ -11729,7 +11729,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K296" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 88; year 2019 column AA (cell AA88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L296" s="32" t="n">
         <x:v>46237</x:v>
@@ -11767,7 +11767,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K297" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 91; year 2019 column AA (cell AA91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L297" s="32" t="n">
         <x:v>46237</x:v>
@@ -11805,7 +11805,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K298" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 76; year 2019 column AA (cell AA76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L298" s="32" t="n">
         <x:v>46237</x:v>
@@ -11843,7 +11843,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K299" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2019 column AA (cell AA77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L299" s="32" t="n">
         <x:v>46237</x:v>
@@ -11881,7 +11881,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K300" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2019 column AA (cell AA78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L300" s="32" t="n">
         <x:v>46237</x:v>
@@ -11919,7 +11919,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K301" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2019 column AA (cell AA79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L301" s="32" t="n">
         <x:v>46237</x:v>
@@ -11957,7 +11957,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K302" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2019 column AA (cell AA80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L302" s="32" t="n">
         <x:v>46237</x:v>
@@ -11995,7 +11995,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K303" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2019 column AA (cell AA81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L303" s="32" t="n">
         <x:v>46237</x:v>
@@ -12033,7 +12033,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K304" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2019 column AA (cell AA82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L304" s="32" t="n">
         <x:v>46237</x:v>
@@ -12071,7 +12071,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K305" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 17; year 2019 column AA (cell AA17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L305" s="32" t="n">
         <x:v>46237</x:v>
@@ -12109,7 +12109,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K306" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2019 column AA (cell AA18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L306" s="32" t="n">
         <x:v>46237</x:v>
@@ -12147,7 +12147,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K307" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2019 column AA (cell AA19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L307" s="32" t="n">
         <x:v>46237</x:v>
@@ -12185,7 +12185,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K308" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2019 column AA (cell AA73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L308" s="32" t="n">
         <x:v>46237</x:v>
@@ -12223,7 +12223,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K309" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 69; year 2019 column AA (cell AA69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L309" s="32" t="n">
         <x:v>46237</x:v>
@@ -12261,7 +12261,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K310" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2019 column AA (cell AA70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L310" s="32" t="n">
         <x:v>46237</x:v>
@@ -12299,7 +12299,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K311" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2019 column AA (cell AA71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L311" s="32" t="n">
         <x:v>46237</x:v>
@@ -12337,7 +12337,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K312" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2019 column AA (cell AA72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L312" s="32" t="n">
         <x:v>46237</x:v>
@@ -12375,7 +12375,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K313" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2019 column AA (cell AA74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L313" s="32" t="n">
         <x:v>46237</x:v>
@@ -12413,7 +12413,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K314" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 46; year 2019 column AA (cell AA46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L314" s="32" t="n">
         <x:v>46237</x:v>
@@ -12451,7 +12451,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K315" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2019 column AA (cell AA47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L315" s="32" t="n">
         <x:v>46237</x:v>
@@ -12489,7 +12489,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K316" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2019 column AA (cell AA48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L316" s="32" t="n">
         <x:v>46237</x:v>
@@ -12527,7 +12527,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K317" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2019 column AA (cell AA49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L317" s="32" t="n">
         <x:v>46237</x:v>
@@ -12565,7 +12565,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K318" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 52; year 2019 column AA (cell AA52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L318" s="32" t="n">
         <x:v>46237</x:v>
@@ -12603,7 +12603,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K319" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2019 column AA (cell AA53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L319" s="32" t="n">
         <x:v>46237</x:v>
@@ -12641,7 +12641,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K320" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2019 column AA (cell AA54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L320" s="32" t="n">
         <x:v>46237</x:v>
@@ -12679,7 +12679,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K321" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2019 column AA (cell AA55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L321" s="32" t="n">
         <x:v>46237</x:v>
@@ -12717,7 +12717,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K322" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 5; year 2020 column AB (cell AB5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L322" s="32" t="n">
         <x:v>46237</x:v>
@@ -12755,7 +12755,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K323" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 9; year 2020 column AB (cell AB9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L323" s="32" t="n">
         <x:v>46237</x:v>
@@ -12793,7 +12793,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K324" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2020 column AB (cell AB11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L324" s="32" t="n">
         <x:v>46237</x:v>
@@ -12831,7 +12831,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K325" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2020 column AB (cell AB13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L325" s="32" t="n">
         <x:v>46237</x:v>
@@ -12869,7 +12869,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K326" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2020 column AB (cell AB10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L326" s="32" t="n">
         <x:v>46237</x:v>
@@ -12907,7 +12907,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K327" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2020 column AB (cell AB12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L327" s="32" t="n">
         <x:v>46237</x:v>
@@ -12945,7 +12945,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K328" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2020 column AB (cell AB14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L328" s="32" t="n">
         <x:v>46237</x:v>
@@ -12983,7 +12983,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K329" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 35; year 2020 column AB (cell AB35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L329" s="32" t="n">
         <x:v>46237</x:v>
@@ -13021,7 +13021,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K330" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2020 column AB (cell AB36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L330" s="32" t="n">
         <x:v>46237</x:v>
@@ -13059,7 +13059,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K331" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2020 column AB (cell AB37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L331" s="32" t="n">
         <x:v>46237</x:v>
@@ -13097,7 +13097,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K332" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2020 column AB (cell AB38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L332" s="32" t="n">
         <x:v>46237</x:v>
@@ -13135,7 +13135,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K333" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2020 column AB (cell AB39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L333" s="32" t="n">
         <x:v>46237</x:v>
@@ -13173,7 +13173,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K334" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2020 column AB (cell AB40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L334" s="32" t="n">
         <x:v>46237</x:v>
@@ -13211,7 +13211,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K335" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2020 column AB (cell AB41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L335" s="32" t="n">
         <x:v>46237</x:v>
@@ -13249,7 +13249,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K336" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2020 column AB (cell AB42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L336" s="32" t="n">
         <x:v>46237</x:v>
@@ -13287,7 +13287,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K337" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 21; year 2020 column AB (cell AB21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L337" s="32" t="n">
         <x:v>46237</x:v>
@@ -13325,7 +13325,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K338" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2020 column AB (cell AB30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L338" s="32" t="n">
         <x:v>46237</x:v>
@@ -13363,7 +13363,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K339" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2020 column AB (cell AB28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L339" s="32" t="n">
         <x:v>46237</x:v>
@@ -13401,7 +13401,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K340" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2020 column AB (cell AB29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L340" s="32" t="n">
         <x:v>46237</x:v>
@@ -13439,7 +13439,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K341" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2020 column AB (cell AB22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L341" s="32" t="n">
         <x:v>46237</x:v>
@@ -13477,7 +13477,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K342" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2020 column AB (cell AB23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L342" s="32" t="n">
         <x:v>46237</x:v>
@@ -13515,7 +13515,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K343" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2020 column AB (cell AB24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L343" s="32" t="n">
         <x:v>46237</x:v>
@@ -13553,7 +13553,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K344" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2020 column AB (cell AB25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L344" s="32" t="n">
         <x:v>46237</x:v>
@@ -13591,7 +13591,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K345" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2020 column AB (cell AB26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L345" s="32" t="n">
         <x:v>46237</x:v>
@@ -13629,7 +13629,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K346" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2020 column AB (cell AB27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L346" s="32" t="n">
         <x:v>46237</x:v>
@@ -13667,7 +13667,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K347" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2020 column AB (cell AB31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L347" s="32" t="n">
         <x:v>46237</x:v>
@@ -13705,7 +13705,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K348" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2020 column AB (cell AB32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L348" s="32" t="n">
         <x:v>46237</x:v>
@@ -13743,7 +13743,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K349" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 58; year 2020 column AB (cell AB58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L349" s="32" t="n">
         <x:v>46237</x:v>
@@ -13781,7 +13781,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K350" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2020 column AB (cell AB60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L350" s="32" t="n">
         <x:v>46237</x:v>
@@ -13819,7 +13819,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K351" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2020 column AB (cell AB59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L351" s="32" t="n">
         <x:v>46237</x:v>
@@ -13857,7 +13857,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K352" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2020 column AB (cell AB61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L352" s="32" t="n">
         <x:v>46237</x:v>
@@ -13895,7 +13895,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K353" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2020 column AB (cell AB62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L353" s="32" t="n">
         <x:v>46237</x:v>
@@ -13933,7 +13933,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K354" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2020 column AB (cell AB63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L354" s="32" t="n">
         <x:v>46237</x:v>
@@ -13971,7 +13971,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K355" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2020 column AB (cell AB64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L355" s="32" t="n">
         <x:v>46237</x:v>
@@ -14009,7 +14009,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K356" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2020 column AB (cell AB65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L356" s="32" t="n">
         <x:v>46237</x:v>
@@ -14047,7 +14047,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K357" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2020 column AB (cell AB66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L357" s="32" t="n">
         <x:v>46237</x:v>
@@ -14085,7 +14085,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K358" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 85; year 2020 column AB (cell AB85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L358" s="32" t="n">
         <x:v>46237</x:v>
@@ -14123,7 +14123,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K359" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2020 column AB (cell AB89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L359" s="32" t="n">
         <x:v>46237</x:v>
@@ -14161,7 +14161,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K360" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 88; year 2020 column AB (cell AB88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L360" s="32" t="n">
         <x:v>46237</x:v>
@@ -14199,7 +14199,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K361" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 91; year 2020 column AB (cell AB91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L361" s="32" t="n">
         <x:v>46237</x:v>
@@ -14237,7 +14237,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K362" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 76; year 2020 column AB (cell AB76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L362" s="32" t="n">
         <x:v>46237</x:v>
@@ -14275,7 +14275,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K363" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2020 column AB (cell AB77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L363" s="32" t="n">
         <x:v>46237</x:v>
@@ -14313,7 +14313,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K364" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2020 column AB (cell AB78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L364" s="32" t="n">
         <x:v>46237</x:v>
@@ -14351,7 +14351,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K365" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2020 column AB (cell AB79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L365" s="32" t="n">
         <x:v>46237</x:v>
@@ -14389,7 +14389,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K366" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2020 column AB (cell AB80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L366" s="32" t="n">
         <x:v>46237</x:v>
@@ -14427,7 +14427,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K367" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2020 column AB (cell AB81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L367" s="32" t="n">
         <x:v>46237</x:v>
@@ -14465,7 +14465,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K368" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2020 column AB (cell AB82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L368" s="32" t="n">
         <x:v>46237</x:v>
@@ -14503,7 +14503,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K369" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 17; year 2020 column AB (cell AB17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L369" s="32" t="n">
         <x:v>46237</x:v>
@@ -14541,7 +14541,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K370" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2020 column AB (cell AB18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L370" s="32" t="n">
         <x:v>46237</x:v>
@@ -14579,7 +14579,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K371" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2020 column AB (cell AB19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L371" s="32" t="n">
         <x:v>46237</x:v>
@@ -14617,7 +14617,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K372" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2020 column AB (cell AB73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L372" s="32" t="n">
         <x:v>46237</x:v>
@@ -14655,7 +14655,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K373" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 69; year 2020 column AB (cell AB69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L373" s="32" t="n">
         <x:v>46237</x:v>
@@ -14693,7 +14693,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K374" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2020 column AB (cell AB70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L374" s="32" t="n">
         <x:v>46237</x:v>
@@ -14731,7 +14731,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K375" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2020 column AB (cell AB71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L375" s="32" t="n">
         <x:v>46237</x:v>
@@ -14769,7 +14769,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K376" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2020 column AB (cell AB72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L376" s="32" t="n">
         <x:v>46237</x:v>
@@ -14807,7 +14807,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K377" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2020 column AB (cell AB74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L377" s="32" t="n">
         <x:v>46237</x:v>
@@ -14845,7 +14845,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K378" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 46; year 2020 column AB (cell AB46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L378" s="32" t="n">
         <x:v>46237</x:v>
@@ -14883,7 +14883,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K379" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2020 column AB (cell AB47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L379" s="32" t="n">
         <x:v>46237</x:v>
@@ -14921,7 +14921,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K380" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2020 column AB (cell AB48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L380" s="32" t="n">
         <x:v>46237</x:v>
@@ -14959,7 +14959,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K381" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2020 column AB (cell AB49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L381" s="32" t="n">
         <x:v>46237</x:v>
@@ -14997,7 +14997,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K382" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 52; year 2020 column AB (cell AB52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L382" s="32" t="n">
         <x:v>46237</x:v>
@@ -15035,7 +15035,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K383" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2020 column AB (cell AB53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L383" s="32" t="n">
         <x:v>46237</x:v>
@@ -15073,7 +15073,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K384" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2020 column AB (cell AB54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L384" s="32" t="n">
         <x:v>46237</x:v>
@@ -15111,7 +15111,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K385" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2020 column AB (cell AB55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L385" s="32" t="n">
         <x:v>46237</x:v>
@@ -15149,7 +15149,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K386" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 5; year 2021 column AC (cell AC5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L386" s="32" t="n">
         <x:v>46237</x:v>
@@ -15187,7 +15187,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K387" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 9; year 2021 column AC (cell AC9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L387" s="32" t="n">
         <x:v>46237</x:v>
@@ -15225,7 +15225,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K388" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2021 column AC (cell AC11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L388" s="32" t="n">
         <x:v>46237</x:v>
@@ -15263,7 +15263,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K389" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2021 column AC (cell AC13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L389" s="32" t="n">
         <x:v>46237</x:v>
@@ -15301,7 +15301,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K390" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2021 column AC (cell AC10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L390" s="32" t="n">
         <x:v>46237</x:v>
@@ -15339,7 +15339,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K391" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2021 column AC (cell AC12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L391" s="32" t="n">
         <x:v>46237</x:v>
@@ -15377,7 +15377,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K392" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2021 column AC (cell AC14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L392" s="32" t="n">
         <x:v>46237</x:v>
@@ -15415,7 +15415,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K393" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 35; year 2021 column AC (cell AC35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L393" s="32" t="n">
         <x:v>46237</x:v>
@@ -15453,7 +15453,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K394" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2021 column AC (cell AC36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L394" s="32" t="n">
         <x:v>46237</x:v>
@@ -15491,7 +15491,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K395" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2021 column AC (cell AC37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L395" s="32" t="n">
         <x:v>46237</x:v>
@@ -15529,7 +15529,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K396" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2021 column AC (cell AC38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L396" s="32" t="n">
         <x:v>46237</x:v>
@@ -15567,7 +15567,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K397" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2021 column AC (cell AC39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L397" s="32" t="n">
         <x:v>46237</x:v>
@@ -15605,7 +15605,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K398" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2021 column AC (cell AC40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L398" s="32" t="n">
         <x:v>46237</x:v>
@@ -15643,7 +15643,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K399" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2021 column AC (cell AC41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L399" s="32" t="n">
         <x:v>46237</x:v>
@@ -15681,7 +15681,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K400" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2021 column AC (cell AC42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L400" s="32" t="n">
         <x:v>46237</x:v>
@@ -15719,7 +15719,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K401" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 21; year 2021 column AC (cell AC21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L401" s="32" t="n">
         <x:v>46237</x:v>
@@ -15757,7 +15757,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K402" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2021 column AC (cell AC30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L402" s="32" t="n">
         <x:v>46237</x:v>
@@ -15795,7 +15795,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K403" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2021 column AC (cell AC28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L403" s="32" t="n">
         <x:v>46237</x:v>
@@ -15833,7 +15833,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K404" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2021 column AC (cell AC29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L404" s="32" t="n">
         <x:v>46237</x:v>
@@ -15871,7 +15871,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K405" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2021 column AC (cell AC22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L405" s="32" t="n">
         <x:v>46237</x:v>
@@ -15909,7 +15909,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K406" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2021 column AC (cell AC23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L406" s="32" t="n">
         <x:v>46237</x:v>
@@ -15947,7 +15947,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K407" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2021 column AC (cell AC24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L407" s="32" t="n">
         <x:v>46237</x:v>
@@ -15985,7 +15985,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K408" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2021 column AC (cell AC25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L408" s="32" t="n">
         <x:v>46237</x:v>
@@ -16023,7 +16023,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K409" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2021 column AC (cell AC26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L409" s="32" t="n">
         <x:v>46237</x:v>
@@ -16061,7 +16061,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K410" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2021 column AC (cell AC27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L410" s="32" t="n">
         <x:v>46237</x:v>
@@ -16099,7 +16099,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K411" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2021 column AC (cell AC31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L411" s="32" t="n">
         <x:v>46237</x:v>
@@ -16137,7 +16137,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K412" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2021 column AC (cell AC32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L412" s="32" t="n">
         <x:v>46237</x:v>
@@ -16175,7 +16175,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K413" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 58; year 2021 column AC (cell AC58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L413" s="32" t="n">
         <x:v>46237</x:v>
@@ -16213,7 +16213,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K414" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2021 column AC (cell AC60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L414" s="32" t="n">
         <x:v>46237</x:v>
@@ -16251,7 +16251,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K415" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2021 column AC (cell AC59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L415" s="32" t="n">
         <x:v>46237</x:v>
@@ -16289,7 +16289,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K416" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2021 column AC (cell AC61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L416" s="32" t="n">
         <x:v>46237</x:v>
@@ -16327,7 +16327,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K417" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2021 column AC (cell AC62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L417" s="32" t="n">
         <x:v>46237</x:v>
@@ -16365,7 +16365,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K418" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2021 column AC (cell AC63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L418" s="32" t="n">
         <x:v>46237</x:v>
@@ -16403,7 +16403,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K419" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2021 column AC (cell AC64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L419" s="32" t="n">
         <x:v>46237</x:v>
@@ -16441,7 +16441,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K420" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2021 column AC (cell AC65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L420" s="32" t="n">
         <x:v>46237</x:v>
@@ -16479,7 +16479,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K421" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2021 column AC (cell AC66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L421" s="32" t="n">
         <x:v>46237</x:v>
@@ -16517,7 +16517,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K422" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 85; year 2021 column AC (cell AC85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L422" s="32" t="n">
         <x:v>46237</x:v>
@@ -16555,7 +16555,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K423" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2021 column AC (cell AC89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L423" s="32" t="n">
         <x:v>46237</x:v>
@@ -16593,7 +16593,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K424" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 88; year 2021 column AC (cell AC88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L424" s="32" t="n">
         <x:v>46237</x:v>
@@ -16631,7 +16631,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K425" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 91; year 2021 column AC (cell AC91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L425" s="32" t="n">
         <x:v>46237</x:v>
@@ -16669,7 +16669,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K426" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 76; year 2021 column AC (cell AC76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L426" s="32" t="n">
         <x:v>46237</x:v>
@@ -16707,7 +16707,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K427" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2021 column AC (cell AC77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L427" s="32" t="n">
         <x:v>46237</x:v>
@@ -16745,7 +16745,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K428" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2021 column AC (cell AC78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L428" s="32" t="n">
         <x:v>46237</x:v>
@@ -16783,7 +16783,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K429" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2021 column AC (cell AC79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L429" s="32" t="n">
         <x:v>46237</x:v>
@@ -16821,7 +16821,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K430" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2021 column AC (cell AC80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L430" s="32" t="n">
         <x:v>46237</x:v>
@@ -16859,7 +16859,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K431" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2021 column AC (cell AC81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L431" s="32" t="n">
         <x:v>46237</x:v>
@@ -16897,7 +16897,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K432" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2021 column AC (cell AC82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L432" s="32" t="n">
         <x:v>46237</x:v>
@@ -16935,7 +16935,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K433" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 17; year 2021 column AC (cell AC17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L433" s="32" t="n">
         <x:v>46237</x:v>
@@ -16973,7 +16973,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K434" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2021 column AC (cell AC18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L434" s="32" t="n">
         <x:v>46237</x:v>
@@ -17011,7 +17011,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K435" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2021 column AC (cell AC19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L435" s="32" t="n">
         <x:v>46237</x:v>
@@ -17049,7 +17049,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K436" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2021 column AC (cell AC73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L436" s="32" t="n">
         <x:v>46237</x:v>
@@ -17087,7 +17087,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K437" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 69; year 2021 column AC (cell AC69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L437" s="32" t="n">
         <x:v>46237</x:v>
@@ -17125,7 +17125,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K438" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2021 column AC (cell AC70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L438" s="32" t="n">
         <x:v>46237</x:v>
@@ -17163,7 +17163,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K439" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2021 column AC (cell AC71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L439" s="32" t="n">
         <x:v>46237</x:v>
@@ -17201,7 +17201,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K440" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2021 column AC (cell AC72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L440" s="32" t="n">
         <x:v>46237</x:v>
@@ -17239,7 +17239,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K441" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2021 column AC (cell AC74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L441" s="32" t="n">
         <x:v>46237</x:v>
@@ -17277,7 +17277,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K442" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 46; year 2021 column AC (cell AC46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L442" s="32" t="n">
         <x:v>46237</x:v>
@@ -17315,7 +17315,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K443" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2021 column AC (cell AC47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L443" s="32" t="n">
         <x:v>46237</x:v>
@@ -17353,7 +17353,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K444" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2021 column AC (cell AC48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L444" s="32" t="n">
         <x:v>46237</x:v>
@@ -17391,7 +17391,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K445" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2021 column AC (cell AC49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L445" s="32" t="n">
         <x:v>46237</x:v>
@@ -17429,7 +17429,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K446" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 52; year 2021 column AC (cell AC52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L446" s="32" t="n">
         <x:v>46237</x:v>
@@ -17467,7 +17467,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K447" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2021 column AC (cell AC53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L447" s="32" t="n">
         <x:v>46237</x:v>
@@ -17505,7 +17505,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K448" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2021 column AC (cell AC54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L448" s="32" t="n">
         <x:v>46237</x:v>
@@ -17543,7 +17543,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K449" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2021 column AC (cell AC55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L449" s="32" t="n">
         <x:v>46237</x:v>
@@ -17581,7 +17581,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K450" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 5; year 2022 column AD (cell AD5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L450" s="32" t="n">
         <x:v>46237</x:v>
@@ -17619,7 +17619,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K451" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 9; year 2022 column AD (cell AD9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L451" s="32" t="n">
         <x:v>46237</x:v>
@@ -17657,7 +17657,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K452" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2022 column AD (cell AD11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L452" s="32" t="n">
         <x:v>46237</x:v>
@@ -17695,7 +17695,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K453" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2022 column AD (cell AD13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L453" s="32" t="n">
         <x:v>46237</x:v>
@@ -17733,7 +17733,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K454" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2022 column AD (cell AD10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L454" s="32" t="n">
         <x:v>46237</x:v>
@@ -17771,7 +17771,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K455" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2022 column AD (cell AD12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L455" s="32" t="n">
         <x:v>46237</x:v>
@@ -17809,7 +17809,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K456" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2022 column AD (cell AD14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L456" s="32" t="n">
         <x:v>46237</x:v>
@@ -17847,7 +17847,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K457" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 35; year 2022 column AD (cell AD35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L457" s="32" t="n">
         <x:v>46237</x:v>
@@ -17885,7 +17885,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K458" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2022 column AD (cell AD36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L458" s="32" t="n">
         <x:v>46237</x:v>
@@ -17923,7 +17923,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K459" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2022 column AD (cell AD37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L459" s="32" t="n">
         <x:v>46237</x:v>
@@ -17961,7 +17961,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K460" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2022 column AD (cell AD38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L460" s="32" t="n">
         <x:v>46237</x:v>
@@ -17999,7 +17999,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K461" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2022 column AD (cell AD39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L461" s="32" t="n">
         <x:v>46237</x:v>
@@ -18037,7 +18037,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K462" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2022 column AD (cell AD40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L462" s="32" t="n">
         <x:v>46237</x:v>
@@ -18075,7 +18075,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K463" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2022 column AD (cell AD41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L463" s="32" t="n">
         <x:v>46237</x:v>
@@ -18113,7 +18113,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K464" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2022 column AD (cell AD42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L464" s="32" t="n">
         <x:v>46237</x:v>
@@ -18151,7 +18151,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K465" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 21; year 2022 column AD (cell AD21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L465" s="32" t="n">
         <x:v>46237</x:v>
@@ -18189,7 +18189,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K466" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2022 column AD (cell AD30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L466" s="32" t="n">
         <x:v>46237</x:v>
@@ -18227,7 +18227,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K467" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2022 column AD (cell AD28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L467" s="32" t="n">
         <x:v>46237</x:v>
@@ -18265,7 +18265,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K468" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2022 column AD (cell AD29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L468" s="32" t="n">
         <x:v>46237</x:v>
@@ -18303,7 +18303,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K469" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2022 column AD (cell AD22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L469" s="32" t="n">
         <x:v>46237</x:v>
@@ -18341,7 +18341,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K470" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2022 column AD (cell AD23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L470" s="32" t="n">
         <x:v>46237</x:v>
@@ -18379,7 +18379,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K471" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2022 column AD (cell AD24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L471" s="32" t="n">
         <x:v>46237</x:v>
@@ -18417,7 +18417,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K472" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2022 column AD (cell AD25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L472" s="32" t="n">
         <x:v>46237</x:v>
@@ -18455,7 +18455,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K473" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2022 column AD (cell AD26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L473" s="32" t="n">
         <x:v>46237</x:v>
@@ -18493,7 +18493,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K474" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2022 column AD (cell AD27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L474" s="32" t="n">
         <x:v>46237</x:v>
@@ -18531,7 +18531,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K475" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2022 column AD (cell AD31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L475" s="32" t="n">
         <x:v>46237</x:v>
@@ -18569,7 +18569,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K476" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2022 column AD (cell AD32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L476" s="32" t="n">
         <x:v>46237</x:v>
@@ -18607,7 +18607,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K477" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 58; year 2022 column AD (cell AD58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L477" s="32" t="n">
         <x:v>46237</x:v>
@@ -18645,7 +18645,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K478" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2022 column AD (cell AD60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L478" s="32" t="n">
         <x:v>46237</x:v>
@@ -18683,7 +18683,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K479" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2022 column AD (cell AD59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L479" s="32" t="n">
         <x:v>46237</x:v>
@@ -18721,7 +18721,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K480" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2022 column AD (cell AD61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L480" s="32" t="n">
         <x:v>46237</x:v>
@@ -18759,7 +18759,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K481" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2022 column AD (cell AD62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L481" s="32" t="n">
         <x:v>46237</x:v>
@@ -18797,7 +18797,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K482" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2022 column AD (cell AD63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L482" s="32" t="n">
         <x:v>46237</x:v>
@@ -18835,7 +18835,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K483" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2022 column AD (cell AD64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L483" s="32" t="n">
         <x:v>46237</x:v>
@@ -18873,7 +18873,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K484" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2022 column AD (cell AD65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L484" s="32" t="n">
         <x:v>46237</x:v>
@@ -18911,7 +18911,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K485" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2022 column AD (cell AD66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L485" s="32" t="n">
         <x:v>46237</x:v>
@@ -18949,7 +18949,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K486" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 85; year 2022 column AD (cell AD85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L486" s="32" t="n">
         <x:v>46237</x:v>
@@ -18987,7 +18987,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K487" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2022 column AD (cell AD89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L487" s="32" t="n">
         <x:v>46237</x:v>
@@ -19025,7 +19025,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K488" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 88; year 2022 column AD (cell AD88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L488" s="32" t="n">
         <x:v>46237</x:v>
@@ -19063,7 +19063,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K489" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 91; year 2022 column AD (cell AD91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L489" s="32" t="n">
         <x:v>46237</x:v>
@@ -19101,7 +19101,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K490" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 76; year 2022 column AD (cell AD76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L490" s="32" t="n">
         <x:v>46237</x:v>
@@ -19139,7 +19139,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K491" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2022 column AD (cell AD77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L491" s="32" t="n">
         <x:v>46237</x:v>
@@ -19177,7 +19177,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K492" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2022 column AD (cell AD78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L492" s="32" t="n">
         <x:v>46237</x:v>
@@ -19215,7 +19215,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K493" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2022 column AD (cell AD79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L493" s="32" t="n">
         <x:v>46237</x:v>
@@ -19253,7 +19253,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K494" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2022 column AD (cell AD80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L494" s="32" t="n">
         <x:v>46237</x:v>
@@ -19291,7 +19291,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K495" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2022 column AD (cell AD81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L495" s="32" t="n">
         <x:v>46237</x:v>
@@ -19329,7 +19329,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K496" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2022 column AD (cell AD82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L496" s="32" t="n">
         <x:v>46237</x:v>
@@ -19367,7 +19367,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K497" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 17; year 2022 column AD (cell AD17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L497" s="32" t="n">
         <x:v>46237</x:v>
@@ -19405,7 +19405,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K498" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2022 column AD (cell AD18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L498" s="32" t="n">
         <x:v>46237</x:v>
@@ -19443,7 +19443,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K499" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2022 column AD (cell AD19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L499" s="32" t="n">
         <x:v>46237</x:v>
@@ -19481,7 +19481,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K500" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2022 column AD (cell AD73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L500" s="32" t="n">
         <x:v>46237</x:v>
@@ -19519,7 +19519,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K501" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 69; year 2022 column AD (cell AD69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L501" s="32" t="n">
         <x:v>46237</x:v>
@@ -19557,7 +19557,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K502" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2022 column AD (cell AD70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L502" s="32" t="n">
         <x:v>46237</x:v>
@@ -19595,7 +19595,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K503" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2022 column AD (cell AD71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L503" s="32" t="n">
         <x:v>46237</x:v>
@@ -19633,7 +19633,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K504" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2022 column AD (cell AD72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L504" s="32" t="n">
         <x:v>46237</x:v>
@@ -19671,7 +19671,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K505" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2022 column AD (cell AD74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L505" s="32" t="n">
         <x:v>46237</x:v>
@@ -19709,7 +19709,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K506" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 46; year 2022 column AD (cell AD46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L506" s="32" t="n">
         <x:v>46237</x:v>
@@ -19747,7 +19747,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K507" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2022 column AD (cell AD47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L507" s="32" t="n">
         <x:v>46237</x:v>
@@ -19785,7 +19785,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K508" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2022 column AD (cell AD48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L508" s="32" t="n">
         <x:v>46237</x:v>
@@ -19823,7 +19823,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K509" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2022 column AD (cell AD49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L509" s="32" t="n">
         <x:v>46237</x:v>
@@ -19861,7 +19861,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K510" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 52; year 2022 column AD (cell AD52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L510" s="32" t="n">
         <x:v>46237</x:v>
@@ -19899,7 +19899,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K511" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2022 column AD (cell AD53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L511" s="32" t="n">
         <x:v>46237</x:v>
@@ -19937,7 +19937,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K512" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2022 column AD (cell AD54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L512" s="32" t="n">
         <x:v>46237</x:v>
@@ -19975,7 +19975,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K513" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2022 column AD (cell AD55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L513" s="32" t="n">
         <x:v>46237</x:v>
@@ -20013,7 +20013,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K514" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 5; year 2023 column AE (cell AE5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L514" s="32" t="n">
         <x:v>46237</x:v>
@@ -20051,7 +20051,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K515" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 9; year 2023 column AE (cell AE9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L515" s="32" t="n">
         <x:v>46237</x:v>
@@ -20089,7 +20089,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K516" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2023 column AE (cell AE11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L516" s="32" t="n">
         <x:v>46237</x:v>
@@ -20127,7 +20127,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K517" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2023 column AE (cell AE13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L517" s="32" t="n">
         <x:v>46237</x:v>
@@ -20165,7 +20165,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K518" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2023 column AE (cell AE10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L518" s="32" t="n">
         <x:v>46237</x:v>
@@ -20203,7 +20203,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K519" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2023 column AE (cell AE12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L519" s="32" t="n">
         <x:v>46237</x:v>
@@ -20241,7 +20241,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K520" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2023 column AE (cell AE14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L520" s="32" t="n">
         <x:v>46237</x:v>
@@ -20279,7 +20279,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K521" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 35; year 2023 column AE (cell AE35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L521" s="32" t="n">
         <x:v>46237</x:v>
@@ -20317,7 +20317,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K522" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2023 column AE (cell AE36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L522" s="32" t="n">
         <x:v>46237</x:v>
@@ -20355,7 +20355,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K523" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2023 column AE (cell AE37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L523" s="32" t="n">
         <x:v>46237</x:v>
@@ -20393,7 +20393,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K524" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2023 column AE (cell AE38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L524" s="32" t="n">
         <x:v>46237</x:v>
@@ -20431,7 +20431,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K525" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2023 column AE (cell AE39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L525" s="32" t="n">
         <x:v>46237</x:v>
@@ -20469,7 +20469,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K526" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2023 column AE (cell AE40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L526" s="32" t="n">
         <x:v>46237</x:v>
@@ -20507,7 +20507,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K527" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2023 column AE (cell AE41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L527" s="32" t="n">
         <x:v>46237</x:v>
@@ -20545,7 +20545,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K528" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2023 column AE (cell AE42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L528" s="32" t="n">
         <x:v>46237</x:v>
@@ -20583,7 +20583,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K529" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 21; year 2023 column AE (cell AE21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L529" s="32" t="n">
         <x:v>46237</x:v>
@@ -20621,7 +20621,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K530" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2023 column AE (cell AE30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L530" s="32" t="n">
         <x:v>46237</x:v>
@@ -20659,7 +20659,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K531" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2023 column AE (cell AE28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L531" s="32" t="n">
         <x:v>46237</x:v>
@@ -20697,7 +20697,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K532" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2023 column AE (cell AE29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L532" s="32" t="n">
         <x:v>46237</x:v>
@@ -20735,7 +20735,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K533" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2023 column AE (cell AE22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L533" s="32" t="n">
         <x:v>46237</x:v>
@@ -20773,7 +20773,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K534" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2023 column AE (cell AE23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L534" s="32" t="n">
         <x:v>46237</x:v>
@@ -20811,7 +20811,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K535" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2023 column AE (cell AE24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L535" s="32" t="n">
         <x:v>46237</x:v>
@@ -20849,7 +20849,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K536" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2023 column AE (cell AE25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L536" s="32" t="n">
         <x:v>46237</x:v>
@@ -20887,7 +20887,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K537" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2023 column AE (cell AE26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L537" s="32" t="n">
         <x:v>46237</x:v>
@@ -20925,7 +20925,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K538" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2023 column AE (cell AE27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L538" s="32" t="n">
         <x:v>46237</x:v>
@@ -20963,7 +20963,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K539" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2023 column AE (cell AE31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L539" s="32" t="n">
         <x:v>46237</x:v>
@@ -21001,7 +21001,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K540" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2023 column AE (cell AE32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L540" s="32" t="n">
         <x:v>46237</x:v>
@@ -21039,7 +21039,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K541" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 58; year 2023 column AE (cell AE58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L541" s="32" t="n">
         <x:v>46237</x:v>
@@ -21077,7 +21077,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K542" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2023 column AE (cell AE60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L542" s="32" t="n">
         <x:v>46237</x:v>
@@ -21115,7 +21115,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K543" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2023 column AE (cell AE59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L543" s="32" t="n">
         <x:v>46237</x:v>
@@ -21153,7 +21153,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K544" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2023 column AE (cell AE61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L544" s="32" t="n">
         <x:v>46237</x:v>
@@ -21191,7 +21191,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K545" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2023 column AE (cell AE62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L545" s="32" t="n">
         <x:v>46237</x:v>
@@ -21229,7 +21229,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K546" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2023 column AE (cell AE63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L546" s="32" t="n">
         <x:v>46237</x:v>
@@ -21267,7 +21267,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K547" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2023 column AE (cell AE64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L547" s="32" t="n">
         <x:v>46237</x:v>
@@ -21305,7 +21305,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K548" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2023 column AE (cell AE65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L548" s="32" t="n">
         <x:v>46237</x:v>
@@ -21343,7 +21343,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K549" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2023 column AE (cell AE66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L549" s="32" t="n">
         <x:v>46237</x:v>
@@ -21381,7 +21381,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K550" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 85; year 2023 column AE (cell AE85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L550" s="32" t="n">
         <x:v>46237</x:v>
@@ -21419,7 +21419,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K551" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2023 column AE (cell AE89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L551" s="32" t="n">
         <x:v>46237</x:v>
@@ -21457,7 +21457,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K552" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 88; year 2023 column AE (cell AE88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L552" s="32" t="n">
         <x:v>46237</x:v>
@@ -21495,7 +21495,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K553" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 91; year 2023 column AE (cell AE91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L553" s="32" t="n">
         <x:v>46237</x:v>
@@ -21533,7 +21533,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K554" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 76; year 2023 column AE (cell AE76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L554" s="32" t="n">
         <x:v>46237</x:v>
@@ -21571,7 +21571,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K555" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2023 column AE (cell AE77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L555" s="32" t="n">
         <x:v>46237</x:v>
@@ -21609,7 +21609,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K556" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2023 column AE (cell AE78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L556" s="32" t="n">
         <x:v>46237</x:v>
@@ -21647,7 +21647,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K557" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2023 column AE (cell AE79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L557" s="32" t="n">
         <x:v>46237</x:v>
@@ -21685,7 +21685,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K558" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2023 column AE (cell AE80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L558" s="32" t="n">
         <x:v>46237</x:v>
@@ -21723,7 +21723,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K559" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2023 column AE (cell AE81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L559" s="32" t="n">
         <x:v>46237</x:v>
@@ -21761,7 +21761,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K560" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2023 column AE (cell AE82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L560" s="32" t="n">
         <x:v>46237</x:v>
@@ -21799,7 +21799,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K561" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 17; year 2023 column AE (cell AE17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L561" s="32" t="n">
         <x:v>46237</x:v>
@@ -21837,7 +21837,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K562" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2023 column AE (cell AE18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L562" s="32" t="n">
         <x:v>46237</x:v>
@@ -21875,7 +21875,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K563" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2023 column AE (cell AE19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L563" s="32" t="n">
         <x:v>46237</x:v>
@@ -21913,7 +21913,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K564" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2023 column AE (cell AE73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L564" s="32" t="n">
         <x:v>46237</x:v>
@@ -21951,7 +21951,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K565" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 69; year 2023 column AE (cell AE69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L565" s="32" t="n">
         <x:v>46237</x:v>
@@ -21989,7 +21989,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K566" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2023 column AE (cell AE70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L566" s="32" t="n">
         <x:v>46237</x:v>
@@ -22027,7 +22027,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K567" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2023 column AE (cell AE71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L567" s="32" t="n">
         <x:v>46237</x:v>
@@ -22065,7 +22065,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K568" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2023 column AE (cell AE72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L568" s="32" t="n">
         <x:v>46237</x:v>
@@ -22103,7 +22103,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K569" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2023 column AE (cell AE74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L569" s="32" t="n">
         <x:v>46237</x:v>
@@ -22141,7 +22141,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K570" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 46; year 2023 column AE (cell AE46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L570" s="32" t="n">
         <x:v>46237</x:v>
@@ -22179,7 +22179,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K571" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2023 column AE (cell AE47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L571" s="32" t="n">
         <x:v>46237</x:v>
@@ -22217,7 +22217,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K572" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2023 column AE (cell AE48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L572" s="32" t="n">
         <x:v>46237</x:v>
@@ -22255,7 +22255,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K573" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2023 column AE (cell AE49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L573" s="32" t="n">
         <x:v>46237</x:v>
@@ -22293,7 +22293,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K574" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 52; year 2023 column AE (cell AE52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L574" s="32" t="n">
         <x:v>46237</x:v>
@@ -22331,7 +22331,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K575" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2023 column AE (cell AE53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L575" s="32" t="n">
         <x:v>46237</x:v>
@@ -22369,7 +22369,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K576" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2023 column AE (cell AE54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L576" s="32" t="n">
         <x:v>46237</x:v>
@@ -22407,7 +22407,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K577" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2023 column AE (cell AE55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L577" s="32" t="n">
         <x:v>46237</x:v>
@@ -22445,7 +22445,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K578" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 5; year 2024 column AF (cell AF5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L578" s="32" t="n">
         <x:v>46237</x:v>
@@ -22483,7 +22483,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K579" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 9; year 2024 column AF (cell AF9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L579" s="32" t="n">
         <x:v>46237</x:v>
@@ -22521,7 +22521,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K580" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2024 column AF (cell AF11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L580" s="32" t="n">
         <x:v>46237</x:v>
@@ -22559,7 +22559,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K581" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2024 column AF (cell AF13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L581" s="32" t="n">
         <x:v>46237</x:v>
@@ -22597,7 +22597,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K582" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2024 column AF (cell AF10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L582" s="32" t="n">
         <x:v>46237</x:v>
@@ -22635,7 +22635,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K583" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2024 column AF (cell AF12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L583" s="32" t="n">
         <x:v>46237</x:v>
@@ -22673,7 +22673,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K584" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2024 column AF (cell AF14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L584" s="32" t="n">
         <x:v>46237</x:v>
@@ -22711,7 +22711,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K585" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 35; year 2024 column AF (cell AF35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L585" s="32" t="n">
         <x:v>46237</x:v>
@@ -22749,7 +22749,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K586" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2024 column AF (cell AF36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L586" s="32" t="n">
         <x:v>46237</x:v>
@@ -22787,7 +22787,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K587" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2024 column AF (cell AF37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L587" s="32" t="n">
         <x:v>46237</x:v>
@@ -22825,7 +22825,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K588" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2024 column AF (cell AF38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L588" s="32" t="n">
         <x:v>46237</x:v>
@@ -22863,7 +22863,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K589" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2024 column AF (cell AF39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L589" s="32" t="n">
         <x:v>46237</x:v>
@@ -22901,7 +22901,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K590" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2024 column AF (cell AF40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L590" s="32" t="n">
         <x:v>46237</x:v>
@@ -22939,7 +22939,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K591" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2024 column AF (cell AF41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L591" s="32" t="n">
         <x:v>46237</x:v>
@@ -22977,7 +22977,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K592" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2024 column AF (cell AF42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L592" s="32" t="n">
         <x:v>46237</x:v>
@@ -23015,7 +23015,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K593" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 21; year 2024 column AF (cell AF21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L593" s="32" t="n">
         <x:v>46237</x:v>
@@ -23053,7 +23053,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K594" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2024 column AF (cell AF30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L594" s="32" t="n">
         <x:v>46237</x:v>
@@ -23091,7 +23091,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K595" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2024 column AF (cell AF28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L595" s="32" t="n">
         <x:v>46237</x:v>
@@ -23129,7 +23129,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K596" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2024 column AF (cell AF29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L596" s="32" t="n">
         <x:v>46237</x:v>
@@ -23167,7 +23167,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K597" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2024 column AF (cell AF22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L597" s="32" t="n">
         <x:v>46237</x:v>
@@ -23205,7 +23205,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K598" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2024 column AF (cell AF23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L598" s="32" t="n">
         <x:v>46237</x:v>
@@ -23243,7 +23243,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K599" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2024 column AF (cell AF24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L599" s="32" t="n">
         <x:v>46237</x:v>
@@ -23281,7 +23281,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K600" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2024 column AF (cell AF25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L600" s="32" t="n">
         <x:v>46237</x:v>
@@ -23319,7 +23319,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K601" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2024 column AF (cell AF26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L601" s="32" t="n">
         <x:v>46237</x:v>
@@ -23357,7 +23357,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K602" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2024 column AF (cell AF27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L602" s="32" t="n">
         <x:v>46237</x:v>
@@ -23395,7 +23395,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K603" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2024 column AF (cell AF31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L603" s="32" t="n">
         <x:v>46237</x:v>
@@ -23433,7 +23433,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K604" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2024 column AF (cell AF32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L604" s="32" t="n">
         <x:v>46237</x:v>
@@ -23471,7 +23471,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K605" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 58; year 2024 column AF (cell AF58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L605" s="32" t="n">
         <x:v>46237</x:v>
@@ -23509,7 +23509,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K606" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2024 column AF (cell AF60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L606" s="32" t="n">
         <x:v>46237</x:v>
@@ -23547,7 +23547,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K607" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2024 column AF (cell AF59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L607" s="32" t="n">
         <x:v>46237</x:v>
@@ -23585,7 +23585,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K608" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2024 column AF (cell AF61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L608" s="32" t="n">
         <x:v>46237</x:v>
@@ -23623,7 +23623,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K609" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2024 column AF (cell AF62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L609" s="32" t="n">
         <x:v>46237</x:v>
@@ -23661,7 +23661,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K610" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2024 column AF (cell AF63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L610" s="32" t="n">
         <x:v>46237</x:v>
@@ -23699,7 +23699,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K611" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2024 column AF (cell AF64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L611" s="32" t="n">
         <x:v>46237</x:v>
@@ -23737,7 +23737,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K612" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2024 column AF (cell AF65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L612" s="32" t="n">
         <x:v>46237</x:v>
@@ -23775,7 +23775,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K613" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2024 column AF (cell AF66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L613" s="32" t="n">
         <x:v>46237</x:v>
@@ -23813,7 +23813,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K614" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 85; year 2024 column AF (cell AF85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L614" s="32" t="n">
         <x:v>46237</x:v>
@@ -23851,7 +23851,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K615" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2024 column AF (cell AF89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L615" s="32" t="n">
         <x:v>46237</x:v>
@@ -23889,7 +23889,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K616" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 88; year 2024 column AF (cell AF88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L616" s="32" t="n">
         <x:v>46237</x:v>
@@ -23927,7 +23927,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K617" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 91; year 2024 column AF (cell AF91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L617" s="32" t="n">
         <x:v>46237</x:v>
@@ -23965,7 +23965,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K618" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 76; year 2024 column AF (cell AF76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L618" s="32" t="n">
         <x:v>46237</x:v>
@@ -24003,7 +24003,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K619" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2024 column AF (cell AF77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L619" s="32" t="n">
         <x:v>46237</x:v>
@@ -24041,7 +24041,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K620" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2024 column AF (cell AF78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L620" s="32" t="n">
         <x:v>46237</x:v>
@@ -24079,7 +24079,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K621" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2024 column AF (cell AF79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L621" s="32" t="n">
         <x:v>46237</x:v>
@@ -24117,7 +24117,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K622" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2024 column AF (cell AF80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L622" s="32" t="n">
         <x:v>46237</x:v>
@@ -24155,7 +24155,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K623" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2024 column AF (cell AF81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L623" s="32" t="n">
         <x:v>46237</x:v>
@@ -24193,7 +24193,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K624" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2024 column AF (cell AF82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L624" s="32" t="n">
         <x:v>46237</x:v>
@@ -24231,7 +24231,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K625" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 17; year 2024 column AF (cell AF17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L625" s="32" t="n">
         <x:v>46237</x:v>
@@ -24269,7 +24269,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K626" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2024 column AF (cell AF18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L626" s="32" t="n">
         <x:v>46237</x:v>
@@ -24307,7 +24307,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K627" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2024 column AF (cell AF19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L627" s="32" t="n">
         <x:v>46237</x:v>
@@ -24345,7 +24345,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K628" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2024 column AF (cell AF73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L628" s="32" t="n">
         <x:v>46237</x:v>
@@ -24383,7 +24383,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K629" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 69; year 2024 column AF (cell AF69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L629" s="32" t="n">
         <x:v>46237</x:v>
@@ -24421,7 +24421,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K630" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2024 column AF (cell AF70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L630" s="32" t="n">
         <x:v>46237</x:v>
@@ -24459,7 +24459,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K631" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2024 column AF (cell AF71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L631" s="32" t="n">
         <x:v>46237</x:v>
@@ -24497,7 +24497,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K632" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2024 column AF (cell AF72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L632" s="32" t="n">
         <x:v>46237</x:v>
@@ -24535,7 +24535,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K633" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2024 column AF (cell AF74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L633" s="32" t="n">
         <x:v>46237</x:v>
@@ -24573,7 +24573,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K634" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 46; year 2024 column AF (cell AF46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L634" s="32" t="n">
         <x:v>46237</x:v>
@@ -24611,7 +24611,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K635" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2024 column AF (cell AF47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L635" s="32" t="n">
         <x:v>46237</x:v>
@@ -24649,7 +24649,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K636" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2024 column AF (cell AF48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L636" s="32" t="n">
         <x:v>46237</x:v>
@@ -24687,7 +24687,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K637" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2024 column AF (cell AF49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L637" s="32" t="n">
         <x:v>46237</x:v>
@@ -24725,7 +24725,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K638" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 52; year 2024 column AF (cell AF52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L638" s="32" t="n">
         <x:v>46237</x:v>
@@ -24763,7 +24763,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K639" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2024 column AF (cell AF53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L639" s="32" t="n">
         <x:v>46237</x:v>
@@ -24801,7 +24801,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K640" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2024 column AF (cell AF54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L640" s="32" t="n">
         <x:v>46237</x:v>
@@ -24839,7 +24839,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K641" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2024 column AF (cell AF55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L641" s="32" t="n">
         <x:v>46237</x:v>
@@ -24877,7 +24877,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K642" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 5; year 2025 column AG (cell AG5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L642" s="32" t="n">
         <x:v>46237</x:v>
@@ -24915,7 +24915,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K643" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 9; year 2025 column AG (cell AG9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L643" s="32" t="n">
         <x:v>46237</x:v>
@@ -24953,7 +24953,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K644" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2025 column AG (cell AG11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L644" s="32" t="n">
         <x:v>46237</x:v>
@@ -24991,7 +24991,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K645" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2025 column AG (cell AG13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L645" s="32" t="n">
         <x:v>46237</x:v>
@@ -25029,7 +25029,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K646" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2025 column AG (cell AG10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L646" s="32" t="n">
         <x:v>46237</x:v>
@@ -25067,7 +25067,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K647" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2025 column AG (cell AG12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L647" s="32" t="n">
         <x:v>46237</x:v>
@@ -25105,7 +25105,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K648" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2025 column AG (cell AG14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L648" s="32" t="n">
         <x:v>46237</x:v>
@@ -25143,7 +25143,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K649" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 35; year 2025 column AG (cell AG35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L649" s="32" t="n">
         <x:v>46237</x:v>
@@ -25181,7 +25181,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K650" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2025 column AG (cell AG36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L650" s="32" t="n">
         <x:v>46237</x:v>
@@ -25219,7 +25219,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K651" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2025 column AG (cell AG37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L651" s="32" t="n">
         <x:v>46237</x:v>
@@ -25257,7 +25257,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K652" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2025 column AG (cell AG38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L652" s="32" t="n">
         <x:v>46237</x:v>
@@ -25295,7 +25295,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K653" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2025 column AG (cell AG39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L653" s="32" t="n">
         <x:v>46237</x:v>
@@ -25333,7 +25333,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K654" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2025 column AG (cell AG40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L654" s="32" t="n">
         <x:v>46237</x:v>
@@ -25371,7 +25371,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K655" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2025 column AG (cell AG41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L655" s="32" t="n">
         <x:v>46237</x:v>
@@ -25409,7 +25409,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K656" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2025 column AG (cell AG42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L656" s="32" t="n">
         <x:v>46237</x:v>
@@ -25447,7 +25447,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K657" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 21; year 2025 column AG (cell AG21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L657" s="32" t="n">
         <x:v>46237</x:v>
@@ -25485,7 +25485,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K658" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2025 column AG (cell AG30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L658" s="32" t="n">
         <x:v>46237</x:v>
@@ -25523,7 +25523,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K659" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2025 column AG (cell AG28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L659" s="32" t="n">
         <x:v>46237</x:v>
@@ -25561,7 +25561,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K660" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2025 column AG (cell AG29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L660" s="32" t="n">
         <x:v>46237</x:v>
@@ -25599,7 +25599,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K661" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2025 column AG (cell AG22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L661" s="32" t="n">
         <x:v>46237</x:v>
@@ -25637,7 +25637,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K662" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2025 column AG (cell AG23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L662" s="32" t="n">
         <x:v>46237</x:v>
@@ -25675,7 +25675,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K663" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2025 column AG (cell AG24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L663" s="32" t="n">
         <x:v>46237</x:v>
@@ -25713,7 +25713,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K664" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2025 column AG (cell AG25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L664" s="32" t="n">
         <x:v>46237</x:v>
@@ -25751,7 +25751,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K665" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2025 column AG (cell AG26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L665" s="32" t="n">
         <x:v>46237</x:v>
@@ -25789,7 +25789,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K666" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2025 column AG (cell AG27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L666" s="32" t="n">
         <x:v>46237</x:v>
@@ -25827,7 +25827,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K667" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2025 column AG (cell AG31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L667" s="32" t="n">
         <x:v>46237</x:v>
@@ -25865,7 +25865,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K668" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2025 column AG (cell AG32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L668" s="32" t="n">
         <x:v>46237</x:v>
@@ -25903,7 +25903,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K669" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 58; year 2025 column AG (cell AG58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L669" s="32" t="n">
         <x:v>46237</x:v>
@@ -25941,7 +25941,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K670" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2025 column AG (cell AG60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L670" s="32" t="n">
         <x:v>46237</x:v>
@@ -25979,7 +25979,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K671" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2025 column AG (cell AG59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L671" s="32" t="n">
         <x:v>46237</x:v>
@@ -26017,7 +26017,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K672" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2025 column AG (cell AG61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L672" s="32" t="n">
         <x:v>46237</x:v>
@@ -26055,7 +26055,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K673" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2025 column AG (cell AG62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L673" s="32" t="n">
         <x:v>46237</x:v>
@@ -26093,7 +26093,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K674" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2025 column AG (cell AG63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L674" s="32" t="n">
         <x:v>46237</x:v>
@@ -26131,7 +26131,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K675" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2025 column AG (cell AG64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L675" s="32" t="n">
         <x:v>46237</x:v>
@@ -26169,7 +26169,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K676" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2025 column AG (cell AG65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L676" s="32" t="n">
         <x:v>46237</x:v>
@@ -26207,7 +26207,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K677" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2025 column AG (cell AG66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L677" s="32" t="n">
         <x:v>46237</x:v>
@@ -26245,7 +26245,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K678" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 85; year 2025 column AG (cell AG85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L678" s="32" t="n">
         <x:v>46237</x:v>
@@ -26283,7 +26283,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K679" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2025 column AG (cell AG89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L679" s="32" t="n">
         <x:v>46237</x:v>
@@ -26321,7 +26321,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K680" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 88; year 2025 column AG (cell AG88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L680" s="32" t="n">
         <x:v>46237</x:v>
@@ -26359,7 +26359,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K681" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 91; year 2025 column AG (cell AG91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L681" s="32" t="n">
         <x:v>46237</x:v>
@@ -26397,7 +26397,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K682" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 76; year 2025 column AG (cell AG76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L682" s="32" t="n">
         <x:v>46237</x:v>
@@ -26435,7 +26435,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K683" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2025 column AG (cell AG77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L683" s="32" t="n">
         <x:v>46237</x:v>
@@ -26473,7 +26473,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K684" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2025 column AG (cell AG78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L684" s="32" t="n">
         <x:v>46237</x:v>
@@ -26511,7 +26511,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K685" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2025 column AG (cell AG79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L685" s="32" t="n">
         <x:v>46237</x:v>
@@ -26549,7 +26549,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K686" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2025 column AG (cell AG80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L686" s="32" t="n">
         <x:v>46237</x:v>
@@ -26587,7 +26587,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K687" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2025 column AG (cell AG81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L687" s="32" t="n">
         <x:v>46237</x:v>
@@ -26625,7 +26625,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K688" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2025 column AG (cell AG82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L688" s="32" t="n">
         <x:v>46237</x:v>
@@ -26663,7 +26663,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K689" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 17; year 2025 column AG (cell AG17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L689" s="32" t="n">
         <x:v>46237</x:v>
@@ -26701,7 +26701,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K690" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2025 column AG (cell AG18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L690" s="32" t="n">
         <x:v>46237</x:v>
@@ -26739,7 +26739,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K691" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2025 column AG (cell AG19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L691" s="32" t="n">
         <x:v>46237</x:v>
@@ -26777,7 +26777,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K692" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2025 column AG (cell AG73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L692" s="32" t="n">
         <x:v>46237</x:v>
@@ -26815,7 +26815,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K693" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 69; year 2025 column AG (cell AG69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L693" s="32" t="n">
         <x:v>46237</x:v>
@@ -26853,7 +26853,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K694" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2025 column AG (cell AG70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L694" s="32" t="n">
         <x:v>46237</x:v>
@@ -26891,7 +26891,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K695" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2025 column AG (cell AG71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L695" s="32" t="n">
         <x:v>46237</x:v>
@@ -26929,7 +26929,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K696" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2025 column AG (cell AG72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L696" s="32" t="n">
         <x:v>46237</x:v>
@@ -26967,7 +26967,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K697" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2025 column AG (cell AG74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L697" s="32" t="n">
         <x:v>46237</x:v>
@@ -27005,7 +27005,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K698" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 46; year 2025 column AG (cell AG46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L698" s="32" t="n">
         <x:v>46237</x:v>
@@ -27043,7 +27043,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K699" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2025 column AG (cell AG47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L699" s="32" t="n">
         <x:v>46237</x:v>
@@ -27081,7 +27081,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K700" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2025 column AG (cell AG48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L700" s="32" t="n">
         <x:v>46237</x:v>
@@ -27119,7 +27119,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K701" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2025 column AG (cell AG49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L701" s="32" t="n">
         <x:v>46237</x:v>
@@ -27157,7 +27157,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K702" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 52; year 2025 column AG (cell AG52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L702" s="32" t="n">
         <x:v>46237</x:v>
@@ -27195,7 +27195,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K703" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2025 column AG (cell AG53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L703" s="32" t="n">
         <x:v>46237</x:v>
@@ -27233,7 +27233,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K704" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2025 column AG (cell AG54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L704" s="32" t="n">
         <x:v>46237</x:v>
@@ -27271,7 +27271,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K705" t="str">
-        <x:v>Copied from Geostat thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2025 column AG (cell AG55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L705" s="32" t="n">
         <x:v>46237</x:v>
@@ -27294,8 +27294,8 @@
     <x:col min="6" max="6" width="40" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="72" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="100" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -27360,10 +27360,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I2" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J2" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 3; year 2010 column B (cell B3); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K2" s="32" t="n">
         <x:v>46237</x:v>
@@ -27395,10 +27395,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I3" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J3" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 4; year 2010 column B (cell B4); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K3" s="32" t="n">
         <x:v>46237</x:v>
@@ -27430,10 +27430,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I4" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J4" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 5; year 2010 column B (cell B5); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K4" s="32" t="n">
         <x:v>46237</x:v>
@@ -27465,10 +27465,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I5" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J5" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 6; year 2010 column B (cell B6); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K5" s="32" t="n">
         <x:v>46237</x:v>
@@ -27500,10 +27500,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I6" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J6" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 7; year 2010 column B (cell B7); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K6" s="32" t="n">
         <x:v>46237</x:v>
@@ -27535,10 +27535,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I7" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J7" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 8; year 2010 column B (cell B8); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K7" s="32" t="n">
         <x:v>46237</x:v>
@@ -27570,10 +27570,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I8" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J8" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 9; year 2010 column B (cell B9); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K8" s="32" t="n">
         <x:v>46237</x:v>
@@ -27605,10 +27605,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I9" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J9" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 10; year 2010 column B (cell B10); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K9" s="32" t="n">
         <x:v>46237</x:v>
@@ -27640,10 +27640,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I10" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J10" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 11; year 2010 column B (cell B11); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K10" s="32" t="n">
         <x:v>46237</x:v>
@@ -27675,10 +27675,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I11" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J11" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 12; year 2010 column B (cell B12); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K11" s="32" t="n">
         <x:v>46237</x:v>
@@ -27710,10 +27710,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I12" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J12" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 13; year 2010 column B (cell B13); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K12" s="32" t="n">
         <x:v>46237</x:v>
@@ -27745,10 +27745,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I13" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J13" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 3; year 2011 column C (cell C3); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K13" s="32" t="n">
         <x:v>46237</x:v>
@@ -27780,10 +27780,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I14" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J14" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 4; year 2011 column C (cell C4); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K14" s="32" t="n">
         <x:v>46237</x:v>
@@ -27815,10 +27815,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I15" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J15" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 5; year 2011 column C (cell C5); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K15" s="32" t="n">
         <x:v>46237</x:v>
@@ -27850,10 +27850,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I16" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J16" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 6; year 2011 column C (cell C6); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K16" s="32" t="n">
         <x:v>46237</x:v>
@@ -27885,10 +27885,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I17" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J17" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 7; year 2011 column C (cell C7); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K17" s="32" t="n">
         <x:v>46237</x:v>
@@ -27920,10 +27920,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I18" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J18" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 8; year 2011 column C (cell C8); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K18" s="32" t="n">
         <x:v>46237</x:v>
@@ -27955,10 +27955,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I19" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J19" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 9; year 2011 column C (cell C9); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K19" s="32" t="n">
         <x:v>46237</x:v>
@@ -27990,10 +27990,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I20" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J20" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 10; year 2011 column C (cell C10); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K20" s="32" t="n">
         <x:v>46237</x:v>
@@ -28025,10 +28025,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I21" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J21" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 11; year 2011 column C (cell C11); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K21" s="32" t="n">
         <x:v>46237</x:v>
@@ -28060,10 +28060,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I22" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J22" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 12; year 2011 column C (cell C12); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K22" s="32" t="n">
         <x:v>46237</x:v>
@@ -28095,10 +28095,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I23" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J23" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 13; year 2011 column C (cell C13); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K23" s="32" t="n">
         <x:v>46237</x:v>
@@ -28130,10 +28130,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I24" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J24" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 3; year 2012 column D (cell D3); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
         <x:v>46237</x:v>
@@ -28165,10 +28165,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I25" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J25" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 4; year 2012 column D (cell D4); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K25" s="32" t="n">
         <x:v>46237</x:v>
@@ -28200,10 +28200,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I26" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J26" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 5; year 2012 column D (cell D5); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K26" s="32" t="n">
         <x:v>46237</x:v>
@@ -28235,10 +28235,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I27" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J27" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 6; year 2012 column D (cell D6); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K27" s="32" t="n">
         <x:v>46237</x:v>
@@ -28270,10 +28270,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I28" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J28" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 7; year 2012 column D (cell D7); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K28" s="32" t="n">
         <x:v>46237</x:v>
@@ -28305,10 +28305,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I29" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J29" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 8; year 2012 column D (cell D8); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K29" s="32" t="n">
         <x:v>46237</x:v>
@@ -28340,10 +28340,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I30" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J30" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 9; year 2012 column D (cell D9); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K30" s="32" t="n">
         <x:v>46237</x:v>
@@ -28375,10 +28375,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I31" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J31" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 10; year 2012 column D (cell D10); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K31" s="32" t="n">
         <x:v>46237</x:v>
@@ -28410,10 +28410,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I32" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J32" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 11; year 2012 column D (cell D11); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K32" s="32" t="n">
         <x:v>46237</x:v>
@@ -28445,10 +28445,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I33" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J33" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 12; year 2012 column D (cell D12); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K33" s="32" t="n">
         <x:v>46237</x:v>
@@ -28480,10 +28480,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I34" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J34" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 13; year 2012 column D (cell D13); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K34" s="32" t="n">
         <x:v>46237</x:v>
@@ -28515,10 +28515,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I35" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J35" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 3; year 2013 column E (cell E3); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K35" s="32" t="n">
         <x:v>46237</x:v>
@@ -28550,10 +28550,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I36" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J36" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 4; year 2013 column E (cell E4); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K36" s="32" t="n">
         <x:v>46237</x:v>
@@ -28585,10 +28585,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I37" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J37" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 5; year 2013 column E (cell E5); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>46237</x:v>
@@ -28620,10 +28620,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I38" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J38" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 6; year 2013 column E (cell E6); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>46237</x:v>
@@ -28655,10 +28655,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I39" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J39" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 7; year 2013 column E (cell E7); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>46237</x:v>
@@ -28690,10 +28690,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I40" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J40" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 8; year 2013 column E (cell E8); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K40" s="32" t="n">
         <x:v>46237</x:v>
@@ -28725,10 +28725,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I41" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J41" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 9; year 2013 column E (cell E9); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K41" s="32" t="n">
         <x:v>46237</x:v>
@@ -28760,10 +28760,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I42" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J42" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 10; year 2013 column E (cell E10); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K42" s="32" t="n">
         <x:v>46237</x:v>
@@ -28795,10 +28795,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I43" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J43" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 11; year 2013 column E (cell E11); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K43" s="32" t="n">
         <x:v>46237</x:v>
@@ -28830,10 +28830,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I44" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J44" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 12; year 2013 column E (cell E12); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K44" s="32" t="n">
         <x:v>46237</x:v>
@@ -28865,10 +28865,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I45" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J45" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 13; year 2013 column E (cell E13); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K45" s="32" t="n">
         <x:v>46237</x:v>
@@ -28900,10 +28900,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I46" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J46" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 3; year 2014 column F (cell F3); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K46" s="32" t="n">
         <x:v>46237</x:v>
@@ -28935,10 +28935,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I47" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J47" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 4; year 2014 column F (cell F4); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K47" s="32" t="n">
         <x:v>46237</x:v>
@@ -28970,10 +28970,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I48" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J48" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 5; year 2014 column F (cell F5); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K48" s="32" t="n">
         <x:v>46237</x:v>
@@ -29005,10 +29005,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I49" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J49" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 6; year 2014 column F (cell F6); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K49" s="32" t="n">
         <x:v>46237</x:v>
@@ -29040,10 +29040,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I50" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J50" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 7; year 2014 column F (cell F7); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K50" s="32" t="n">
         <x:v>46237</x:v>
@@ -29075,10 +29075,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I51" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J51" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 8; year 2014 column F (cell F8); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K51" s="32" t="n">
         <x:v>46237</x:v>
@@ -29110,10 +29110,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I52" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J52" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 9; year 2014 column F (cell F9); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K52" s="32" t="n">
         <x:v>46237</x:v>
@@ -29145,10 +29145,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I53" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J53" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 10; year 2014 column F (cell F10); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>46237</x:v>
@@ -29180,10 +29180,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I54" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J54" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 11; year 2014 column F (cell F11); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K54" s="32" t="n">
         <x:v>46237</x:v>
@@ -29215,10 +29215,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I55" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J55" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 12; year 2014 column F (cell F12); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K55" s="32" t="n">
         <x:v>46237</x:v>
@@ -29250,10 +29250,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I56" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J56" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 13; year 2014 column F (cell F13); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>46237</x:v>
@@ -29285,10 +29285,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I57" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J57" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 3; year 2015 column G (cell G3); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>46237</x:v>
@@ -29320,10 +29320,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I58" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J58" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 4; year 2015 column G (cell G4); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K58" s="32" t="n">
         <x:v>46237</x:v>
@@ -29355,10 +29355,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I59" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J59" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 5; year 2015 column G (cell G5); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K59" s="32" t="n">
         <x:v>46237</x:v>
@@ -29390,10 +29390,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I60" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J60" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 6; year 2015 column G (cell G6); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K60" s="32" t="n">
         <x:v>46237</x:v>
@@ -29425,10 +29425,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I61" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J61" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 7; year 2015 column G (cell G7); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K61" s="32" t="n">
         <x:v>46237</x:v>
@@ -29460,10 +29460,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I62" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J62" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 8; year 2015 column G (cell G8); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K62" s="32" t="n">
         <x:v>46237</x:v>
@@ -29495,10 +29495,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I63" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J63" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 9; year 2015 column G (cell G9); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K63" s="32" t="n">
         <x:v>46237</x:v>
@@ -29530,10 +29530,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I64" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J64" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 10; year 2015 column G (cell G10); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K64" s="32" t="n">
         <x:v>46237</x:v>
@@ -29565,10 +29565,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I65" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J65" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 11; year 2015 column G (cell G11); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K65" s="32" t="n">
         <x:v>46237</x:v>
@@ -29600,10 +29600,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I66" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J66" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 12; year 2015 column G (cell G12); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K66" s="32" t="n">
         <x:v>46237</x:v>
@@ -29635,10 +29635,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I67" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J67" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 13; year 2015 column G (cell G13); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K67" s="32" t="n">
         <x:v>46237</x:v>
@@ -29670,10 +29670,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I68" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J68" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 3; year 2016 column H (cell H3); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K68" s="32" t="n">
         <x:v>46237</x:v>
@@ -29705,10 +29705,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I69" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J69" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 4; year 2016 column H (cell H4); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K69" s="32" t="n">
         <x:v>46237</x:v>
@@ -29740,10 +29740,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I70" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J70" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 5; year 2016 column H (cell H5); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K70" s="32" t="n">
         <x:v>46237</x:v>
@@ -29775,10 +29775,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I71" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J71" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 6; year 2016 column H (cell H6); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K71" s="32" t="n">
         <x:v>46237</x:v>
@@ -29810,10 +29810,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I72" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J72" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 7; year 2016 column H (cell H7); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K72" s="32" t="n">
         <x:v>46237</x:v>
@@ -29845,10 +29845,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I73" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J73" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 8; year 2016 column H (cell H8); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K73" s="32" t="n">
         <x:v>46237</x:v>
@@ -29880,10 +29880,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I74" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J74" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 9; year 2016 column H (cell H9); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K74" s="32" t="n">
         <x:v>46237</x:v>
@@ -29915,10 +29915,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I75" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J75" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 10; year 2016 column H (cell H10); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K75" s="32" t="n">
         <x:v>46237</x:v>
@@ -29950,10 +29950,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I76" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J76" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 11; year 2016 column H (cell H11); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K76" s="32" t="n">
         <x:v>46237</x:v>
@@ -29985,10 +29985,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I77" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J77" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 12; year 2016 column H (cell H12); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>46237</x:v>
@@ -30020,10 +30020,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I78" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J78" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 13; year 2016 column H (cell H13); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K78" s="32" t="n">
         <x:v>46237</x:v>
@@ -30055,10 +30055,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I79" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J79" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 3; year 2017 column I (cell I3); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K79" s="32" t="n">
         <x:v>46237</x:v>
@@ -30090,10 +30090,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I80" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J80" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 4; year 2017 column I (cell I4); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K80" s="32" t="n">
         <x:v>46237</x:v>
@@ -30125,10 +30125,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I81" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J81" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 5; year 2017 column I (cell I5); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K81" s="32" t="n">
         <x:v>46237</x:v>
@@ -30160,10 +30160,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I82" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J82" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 6; year 2017 column I (cell I6); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K82" s="32" t="n">
         <x:v>46237</x:v>
@@ -30195,10 +30195,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I83" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J83" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 7; year 2017 column I (cell I7); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>46237</x:v>
@@ -30230,10 +30230,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I84" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J84" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 8; year 2017 column I (cell I8); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K84" s="32" t="n">
         <x:v>46237</x:v>
@@ -30265,10 +30265,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I85" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J85" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 9; year 2017 column I (cell I9); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K85" s="32" t="n">
         <x:v>46237</x:v>
@@ -30300,10 +30300,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I86" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J86" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 10; year 2017 column I (cell I10); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K86" s="32" t="n">
         <x:v>46237</x:v>
@@ -30335,10 +30335,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I87" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J87" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 11; year 2017 column I (cell I11); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K87" s="32" t="n">
         <x:v>46237</x:v>
@@ -30370,10 +30370,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I88" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J88" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 12; year 2017 column I (cell I12); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K88" s="32" t="n">
         <x:v>46237</x:v>
@@ -30405,10 +30405,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I89" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J89" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 13; year 2017 column I (cell I13); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K89" s="32" t="n">
         <x:v>46237</x:v>
@@ -30440,10 +30440,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I90" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J90" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 3; year 2018 column J (cell J3); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K90" s="32" t="n">
         <x:v>46237</x:v>
@@ -30475,10 +30475,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I91" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J91" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 4; year 2018 column J (cell J4); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K91" s="32" t="n">
         <x:v>46237</x:v>
@@ -30510,10 +30510,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I92" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J92" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 5; year 2018 column J (cell J5); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K92" s="32" t="n">
         <x:v>46237</x:v>
@@ -30545,10 +30545,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I93" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J93" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 6; year 2018 column J (cell J6); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K93" s="32" t="n">
         <x:v>46237</x:v>
@@ -30580,10 +30580,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I94" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J94" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 7; year 2018 column J (cell J7); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K94" s="32" t="n">
         <x:v>46237</x:v>
@@ -30615,10 +30615,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I95" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J95" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 8; year 2018 column J (cell J8); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K95" s="32" t="n">
         <x:v>46237</x:v>
@@ -30650,10 +30650,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I96" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J96" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 9; year 2018 column J (cell J9); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K96" s="32" t="n">
         <x:v>46237</x:v>
@@ -30685,10 +30685,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I97" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J97" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 10; year 2018 column J (cell J10); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K97" s="32" t="n">
         <x:v>46237</x:v>
@@ -30720,10 +30720,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I98" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J98" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 11; year 2018 column J (cell J11); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K98" s="32" t="n">
         <x:v>46237</x:v>
@@ -30755,10 +30755,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I99" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J99" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 12; year 2018 column J (cell J12); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K99" s="32" t="n">
         <x:v>46237</x:v>
@@ -30790,10 +30790,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I100" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J100" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 13; year 2018 column J (cell J13); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K100" s="32" t="n">
         <x:v>46237</x:v>
@@ -30825,10 +30825,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I101" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J101" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 3; year 2019 column K (cell K3); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K101" s="32" t="n">
         <x:v>46237</x:v>
@@ -30860,10 +30860,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I102" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J102" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 4; year 2019 column K (cell K4); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K102" s="32" t="n">
         <x:v>46237</x:v>
@@ -30895,10 +30895,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I103" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J103" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 5; year 2019 column K (cell K5); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K103" s="32" t="n">
         <x:v>46237</x:v>
@@ -30930,10 +30930,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I104" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J104" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 6; year 2019 column K (cell K6); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K104" s="32" t="n">
         <x:v>46237</x:v>
@@ -30965,10 +30965,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I105" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J105" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 7; year 2019 column K (cell K7); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K105" s="32" t="n">
         <x:v>46237</x:v>
@@ -31000,10 +31000,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I106" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J106" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 8; year 2019 column K (cell K8); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K106" s="32" t="n">
         <x:v>46237</x:v>
@@ -31035,10 +31035,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I107" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J107" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 9; year 2019 column K (cell K9); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K107" s="32" t="n">
         <x:v>46237</x:v>
@@ -31070,10 +31070,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I108" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J108" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 10; year 2019 column K (cell K10); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K108" s="32" t="n">
         <x:v>46237</x:v>
@@ -31105,10 +31105,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I109" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J109" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 11; year 2019 column K (cell K11); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K109" s="32" t="n">
         <x:v>46237</x:v>
@@ -31140,10 +31140,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I110" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J110" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 12; year 2019 column K (cell K12); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K110" s="32" t="n">
         <x:v>46237</x:v>
@@ -31175,10 +31175,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I111" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J111" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 13; year 2019 column K (cell K13); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K111" s="32" t="n">
         <x:v>46237</x:v>
@@ -31210,10 +31210,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I112" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J112" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 3; year 2020 column L (cell L3); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K112" s="32" t="n">
         <x:v>46237</x:v>
@@ -31245,10 +31245,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I113" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J113" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 4; year 2020 column L (cell L4); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K113" s="32" t="n">
         <x:v>46237</x:v>
@@ -31280,10 +31280,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I114" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J114" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 5; year 2020 column L (cell L5); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K114" s="32" t="n">
         <x:v>46237</x:v>
@@ -31315,10 +31315,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I115" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J115" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 6; year 2020 column L (cell L6); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K115" s="32" t="n">
         <x:v>46237</x:v>
@@ -31350,10 +31350,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I116" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J116" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 7; year 2020 column L (cell L7); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K116" s="32" t="n">
         <x:v>46237</x:v>
@@ -31385,10 +31385,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I117" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J117" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 8; year 2020 column L (cell L8); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K117" s="32" t="n">
         <x:v>46237</x:v>
@@ -31420,10 +31420,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I118" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J118" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 9; year 2020 column L (cell L9); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K118" s="32" t="n">
         <x:v>46237</x:v>
@@ -31455,10 +31455,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I119" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J119" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 10; year 2020 column L (cell L10); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K119" s="32" t="n">
         <x:v>46237</x:v>
@@ -31490,10 +31490,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I120" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J120" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 11; year 2020 column L (cell L11); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K120" s="32" t="n">
         <x:v>46237</x:v>
@@ -31525,10 +31525,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I121" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J121" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 12; year 2020 column L (cell L12); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K121" s="32" t="n">
         <x:v>46237</x:v>
@@ -31560,10 +31560,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I122" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J122" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 13; year 2020 column L (cell L13); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K122" s="32" t="n">
         <x:v>46237</x:v>
@@ -31595,10 +31595,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I123" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J123" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 3; year 2021 column M (cell M3); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K123" s="32" t="n">
         <x:v>46237</x:v>
@@ -31630,10 +31630,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I124" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J124" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 4; year 2021 column M (cell M4); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K124" s="32" t="n">
         <x:v>46237</x:v>
@@ -31665,10 +31665,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I125" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J125" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 5; year 2021 column M (cell M5); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K125" s="32" t="n">
         <x:v>46237</x:v>
@@ -31700,10 +31700,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I126" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J126" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 6; year 2021 column M (cell M6); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K126" s="32" t="n">
         <x:v>46237</x:v>
@@ -31735,10 +31735,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I127" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J127" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 7; year 2021 column M (cell M7); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K127" s="32" t="n">
         <x:v>46237</x:v>
@@ -31770,10 +31770,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I128" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J128" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 8; year 2021 column M (cell M8); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K128" s="32" t="n">
         <x:v>46237</x:v>
@@ -31805,10 +31805,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I129" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J129" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 9; year 2021 column M (cell M9); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K129" s="32" t="n">
         <x:v>46237</x:v>
@@ -31840,10 +31840,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I130" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J130" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 10; year 2021 column M (cell M10); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K130" s="32" t="n">
         <x:v>46237</x:v>
@@ -31875,10 +31875,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I131" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J131" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 11; year 2021 column M (cell M11); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K131" s="32" t="n">
         <x:v>46237</x:v>
@@ -31910,10 +31910,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I132" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J132" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 12; year 2021 column M (cell M12); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K132" s="32" t="n">
         <x:v>46237</x:v>
@@ -31945,10 +31945,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I133" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J133" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 13; year 2021 column M (cell M13); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K133" s="32" t="n">
         <x:v>46237</x:v>
@@ -31980,10 +31980,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I134" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J134" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 3; year 2022 column N (cell N3); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K134" s="32" t="n">
         <x:v>46237</x:v>
@@ -32015,10 +32015,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I135" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J135" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 4; year 2022 column N (cell N4); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K135" s="32" t="n">
         <x:v>46237</x:v>
@@ -32050,10 +32050,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I136" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J136" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 5; year 2022 column N (cell N5); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K136" s="32" t="n">
         <x:v>46237</x:v>
@@ -32085,10 +32085,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I137" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J137" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 6; year 2022 column N (cell N6); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K137" s="32" t="n">
         <x:v>46237</x:v>
@@ -32120,10 +32120,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I138" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J138" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 7; year 2022 column N (cell N7); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K138" s="32" t="n">
         <x:v>46237</x:v>
@@ -32155,10 +32155,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I139" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J139" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 8; year 2022 column N (cell N8); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K139" s="32" t="n">
         <x:v>46237</x:v>
@@ -32190,10 +32190,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I140" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J140" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 9; year 2022 column N (cell N9); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K140" s="32" t="n">
         <x:v>46237</x:v>
@@ -32225,10 +32225,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I141" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J141" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 10; year 2022 column N (cell N10); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K141" s="32" t="n">
         <x:v>46237</x:v>
@@ -32260,10 +32260,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I142" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J142" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 11; year 2022 column N (cell N11); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K142" s="32" t="n">
         <x:v>46237</x:v>
@@ -32295,10 +32295,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I143" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J143" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 12; year 2022 column N (cell N12); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K143" s="32" t="n">
         <x:v>46237</x:v>
@@ -32330,10 +32330,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I144" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J144" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 13; year 2022 column N (cell N13); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K144" s="32" t="n">
         <x:v>46237</x:v>
@@ -32365,10 +32365,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I145" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J145" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 3; year 2023 column O (cell O3); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K145" s="32" t="n">
         <x:v>46237</x:v>
@@ -32400,10 +32400,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I146" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J146" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 4; year 2023 column O (cell O4); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K146" s="32" t="n">
         <x:v>46237</x:v>
@@ -32435,10 +32435,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I147" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J147" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 5; year 2023 column O (cell O5); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K147" s="32" t="n">
         <x:v>46237</x:v>
@@ -32470,10 +32470,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I148" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J148" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 6; year 2023 column O (cell O6); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K148" s="32" t="n">
         <x:v>46237</x:v>
@@ -32505,10 +32505,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I149" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J149" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 7; year 2023 column O (cell O7); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K149" s="32" t="n">
         <x:v>46237</x:v>
@@ -32540,10 +32540,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I150" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J150" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 8; year 2023 column O (cell O8); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K150" s="32" t="n">
         <x:v>46237</x:v>
@@ -32575,10 +32575,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I151" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J151" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 9; year 2023 column O (cell O9); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K151" s="32" t="n">
         <x:v>46237</x:v>
@@ -32610,10 +32610,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I152" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J152" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 10; year 2023 column O (cell O10); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K152" s="32" t="n">
         <x:v>46237</x:v>
@@ -32645,10 +32645,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I153" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J153" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 11; year 2023 column O (cell O11); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K153" s="32" t="n">
         <x:v>46237</x:v>
@@ -32680,10 +32680,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I154" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J154" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 12; year 2023 column O (cell O12); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K154" s="32" t="n">
         <x:v>46237</x:v>
@@ -32715,10 +32715,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I155" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J155" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 13; year 2023 column O (cell O13); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K155" s="32" t="n">
         <x:v>46237</x:v>
@@ -32750,10 +32750,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I156" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J156" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 3; year 2024 column P (cell P3); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K156" s="32" t="n">
         <x:v>46237</x:v>
@@ -32785,10 +32785,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I157" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J157" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 4; year 2024 column P (cell P4); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K157" s="32" t="n">
         <x:v>46237</x:v>
@@ -32820,10 +32820,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I158" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J158" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 5; year 2024 column P (cell P5); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K158" s="32" t="n">
         <x:v>46237</x:v>
@@ -32855,10 +32855,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I159" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J159" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 6; year 2024 column P (cell P6); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K159" s="32" t="n">
         <x:v>46237</x:v>
@@ -32890,10 +32890,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I160" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J160" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 7; year 2024 column P (cell P7); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K160" s="32" t="n">
         <x:v>46237</x:v>
@@ -32925,10 +32925,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I161" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J161" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 8; year 2024 column P (cell P8); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K161" s="32" t="n">
         <x:v>46237</x:v>
@@ -32960,10 +32960,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I162" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J162" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 9; year 2024 column P (cell P9); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K162" s="32" t="n">
         <x:v>46237</x:v>
@@ -32995,10 +32995,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I163" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J163" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 10; year 2024 column P (cell P10); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K163" s="32" t="n">
         <x:v>46237</x:v>
@@ -33030,10 +33030,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I164" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J164" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 11; year 2024 column P (cell P11); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K164" s="32" t="n">
         <x:v>46237</x:v>
@@ -33065,10 +33065,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I165" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J165" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 12; year 2024 column P (cell P12); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K165" s="32" t="n">
         <x:v>46237</x:v>
@@ -33100,10 +33100,10 @@
         <x:v>mil. GEL</x:v>
       </x:c>
       <x:c r="I166" t="str">
-        <x:v>official</x:v>
+        <x:v>final_as_published</x:v>
       </x:c>
       <x:c r="J166" t="str">
-        <x:v>Copied from Geostat current-price mil. GEL; no scale conversion; no estimates.</x:v>
+        <x:v>Source sheet "regional GDP"; source row 13; year 2024 column P (cell P13); source already mil. GEL; no scale conversion; no estimates.</x:v>
       </x:c>
       <x:c r="K166" s="32" t="n">
         <x:v>46237</x:v>

--- a/docs/Raw Data/Municipalities/geostat-population-regional-gdp/municipal-population-and-regional-gdp.xlsx
+++ b/docs/Raw Data/Municipalities/geostat-population-regional-gdp/municipal-population-and-regional-gdp.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R596542cc24a549b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Population" sheetId="2" r:id="R2335569669ea4d24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional GDP" sheetId="3" r:id="R604d9beaed414478"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geography map" sheetId="4" r:id="Rd6be994b98f54f6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R4dea224f262d4e0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Population" sheetId="2" r:id="Rfb111adcceaf435e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional GDP" sheetId="3" r:id="R1355dd1b93cb41aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geography map" sheetId="4" r:id="R23710fb2f1d040af"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -557,7 +557,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K2" t="str">
-        <x:v>Source sheet "1"; source row 5; year 2015 column W (cell W5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 6; year 2015 column W (cell W6); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L2" s="32" t="n">
         <x:v>46237</x:v>
@@ -595,7 +595,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K3" t="str">
-        <x:v>Source sheet "1"; source row 9; year 2015 column W (cell W9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2015 column W (cell W10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L3" s="32" t="n">
         <x:v>46237</x:v>
@@ -633,7 +633,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>Source sheet "1"; source row 11; year 2015 column W (cell W11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2015 column W (cell W12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L4" s="32" t="n">
         <x:v>46237</x:v>
@@ -671,7 +671,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K5" t="str">
-        <x:v>Source sheet "1"; source row 13; year 2015 column W (cell W13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2015 column W (cell W14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L5" s="32" t="n">
         <x:v>46237</x:v>
@@ -709,7 +709,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K6" t="str">
-        <x:v>Source sheet "1"; source row 10; year 2015 column W (cell W10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2015 column W (cell W11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L6" s="32" t="n">
         <x:v>46237</x:v>
@@ -747,7 +747,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K7" t="str">
-        <x:v>Source sheet "1"; source row 12; year 2015 column W (cell W12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2015 column W (cell W13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L7" s="32" t="n">
         <x:v>46237</x:v>
@@ -785,7 +785,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K8" t="str">
-        <x:v>Source sheet "1"; source row 14; year 2015 column W (cell W14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 15; year 2015 column W (cell W15); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L8" s="32" t="n">
         <x:v>46237</x:v>
@@ -823,7 +823,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K9" t="str">
-        <x:v>Source sheet "1"; source row 35; year 2015 column W (cell W35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2015 column W (cell W36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L9" s="32" t="n">
         <x:v>46237</x:v>
@@ -861,7 +861,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K10" t="str">
-        <x:v>Source sheet "1"; source row 36; year 2015 column W (cell W36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2015 column W (cell W37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L10" s="32" t="n">
         <x:v>46237</x:v>
@@ -899,7 +899,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K11" t="str">
-        <x:v>Source sheet "1"; source row 37; year 2015 column W (cell W37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2015 column W (cell W38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L11" s="32" t="n">
         <x:v>46237</x:v>
@@ -937,7 +937,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K12" t="str">
-        <x:v>Source sheet "1"; source row 38; year 2015 column W (cell W38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2015 column W (cell W39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L12" s="32" t="n">
         <x:v>46237</x:v>
@@ -975,7 +975,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K13" t="str">
-        <x:v>Source sheet "1"; source row 39; year 2015 column W (cell W39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2015 column W (cell W40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L13" s="32" t="n">
         <x:v>46237</x:v>
@@ -1013,7 +1013,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K14" t="str">
-        <x:v>Source sheet "1"; source row 40; year 2015 column W (cell W40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2015 column W (cell W41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L14" s="32" t="n">
         <x:v>46237</x:v>
@@ -1051,7 +1051,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K15" t="str">
-        <x:v>Source sheet "1"; source row 41; year 2015 column W (cell W41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2015 column W (cell W42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L15" s="32" t="n">
         <x:v>46237</x:v>
@@ -1089,7 +1089,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K16" t="str">
-        <x:v>Source sheet "1"; source row 42; year 2015 column W (cell W42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 43; year 2015 column W (cell W43); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L16" s="32" t="n">
         <x:v>46237</x:v>
@@ -1127,7 +1127,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K17" t="str">
-        <x:v>Source sheet "1"; source row 21; year 2015 column W (cell W21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2015 column W (cell W22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L17" s="32" t="n">
         <x:v>46237</x:v>
@@ -1165,7 +1165,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K18" t="str">
-        <x:v>Source sheet "1"; source row 30; year 2015 column W (cell W30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2015 column W (cell W31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L18" s="32" t="n">
         <x:v>46237</x:v>
@@ -1203,7 +1203,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K19" t="str">
-        <x:v>Source sheet "1"; source row 28; year 2015 column W (cell W28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2015 column W (cell W29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L19" s="32" t="n">
         <x:v>46237</x:v>
@@ -1241,7 +1241,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>Source sheet "1"; source row 29; year 2015 column W (cell W29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2015 column W (cell W30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L20" s="32" t="n">
         <x:v>46237</x:v>
@@ -1279,7 +1279,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>Source sheet "1"; source row 22; year 2015 column W (cell W22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2015 column W (cell W23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L21" s="32" t="n">
         <x:v>46237</x:v>
@@ -1317,7 +1317,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K22" t="str">
-        <x:v>Source sheet "1"; source row 23; year 2015 column W (cell W23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2015 column W (cell W24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L22" s="32" t="n">
         <x:v>46237</x:v>
@@ -1355,7 +1355,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>Source sheet "1"; source row 24; year 2015 column W (cell W24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2015 column W (cell W25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L23" s="32" t="n">
         <x:v>46237</x:v>
@@ -1393,7 +1393,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K24" t="str">
-        <x:v>Source sheet "1"; source row 25; year 2015 column W (cell W25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2015 column W (cell W26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L24" s="32" t="n">
         <x:v>46237</x:v>
@@ -1431,7 +1431,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K25" t="str">
-        <x:v>Source sheet "1"; source row 26; year 2015 column W (cell W26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2015 column W (cell W27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L25" s="32" t="n">
         <x:v>46237</x:v>
@@ -1469,7 +1469,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>Source sheet "1"; source row 27; year 2015 column W (cell W27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2015 column W (cell W28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L26" s="32" t="n">
         <x:v>46237</x:v>
@@ -1507,7 +1507,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K27" t="str">
-        <x:v>Source sheet "1"; source row 31; year 2015 column W (cell W31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2015 column W (cell W32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L27" s="32" t="n">
         <x:v>46237</x:v>
@@ -1545,7 +1545,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>Source sheet "1"; source row 32; year 2015 column W (cell W32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 33; year 2015 column W (cell W33); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L28" s="32" t="n">
         <x:v>46237</x:v>
@@ -1583,7 +1583,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K29" t="str">
-        <x:v>Source sheet "1"; source row 58; year 2015 column W (cell W58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2015 column W (cell W59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L29" s="32" t="n">
         <x:v>46237</x:v>
@@ -1621,7 +1621,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>Source sheet "1"; source row 60; year 2015 column W (cell W60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2015 column W (cell W61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L30" s="32" t="n">
         <x:v>46237</x:v>
@@ -1659,7 +1659,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K31" t="str">
-        <x:v>Source sheet "1"; source row 59; year 2015 column W (cell W59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2015 column W (cell W60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L31" s="32" t="n">
         <x:v>46237</x:v>
@@ -1697,7 +1697,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K32" t="str">
-        <x:v>Source sheet "1"; source row 61; year 2015 column W (cell W61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2015 column W (cell W62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L32" s="32" t="n">
         <x:v>46237</x:v>
@@ -1735,7 +1735,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K33" t="str">
-        <x:v>Source sheet "1"; source row 62; year 2015 column W (cell W62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2015 column W (cell W63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L33" s="32" t="n">
         <x:v>46237</x:v>
@@ -1773,7 +1773,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K34" t="str">
-        <x:v>Source sheet "1"; source row 63; year 2015 column W (cell W63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2015 column W (cell W64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L34" s="32" t="n">
         <x:v>46237</x:v>
@@ -1811,7 +1811,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K35" t="str">
-        <x:v>Source sheet "1"; source row 64; year 2015 column W (cell W64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2015 column W (cell W65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L35" s="32" t="n">
         <x:v>46237</x:v>
@@ -1849,7 +1849,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K36" t="str">
-        <x:v>Source sheet "1"; source row 65; year 2015 column W (cell W65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2015 column W (cell W66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L36" s="32" t="n">
         <x:v>46237</x:v>
@@ -1887,7 +1887,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>Source sheet "1"; source row 66; year 2015 column W (cell W66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 67; year 2015 column W (cell W67); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L37" s="32" t="n">
         <x:v>46237</x:v>
@@ -1925,7 +1925,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K38" t="str">
-        <x:v>Source sheet "1"; source row 85; year 2015 column W (cell W85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 86; year 2015 column W (cell W86); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L38" s="32" t="n">
         <x:v>46237</x:v>
@@ -1963,7 +1963,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K39" t="str">
-        <x:v>Source sheet "1"; source row 89; year 2015 column W (cell W89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 90; year 2015 column W (cell W90); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L39" s="32" t="n">
         <x:v>46237</x:v>
@@ -2001,7 +2001,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K40" t="str">
-        <x:v>Source sheet "1"; source row 88; year 2015 column W (cell W88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2015 column W (cell W89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L40" s="32" t="n">
         <x:v>46237</x:v>
@@ -2039,7 +2039,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K41" t="str">
-        <x:v>Source sheet "1"; source row 91; year 2015 column W (cell W91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 92; year 2015 column W (cell W92); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L41" s="32" t="n">
         <x:v>46237</x:v>
@@ -2077,7 +2077,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K42" t="str">
-        <x:v>Source sheet "1"; source row 76; year 2015 column W (cell W76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2015 column W (cell W77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L42" s="32" t="n">
         <x:v>46237</x:v>
@@ -2115,7 +2115,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K43" t="str">
-        <x:v>Source sheet "1"; source row 77; year 2015 column W (cell W77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2015 column W (cell W78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L43" s="32" t="n">
         <x:v>46237</x:v>
@@ -2153,7 +2153,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K44" t="str">
-        <x:v>Source sheet "1"; source row 78; year 2015 column W (cell W78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2015 column W (cell W79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L44" s="32" t="n">
         <x:v>46237</x:v>
@@ -2191,7 +2191,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K45" t="str">
-        <x:v>Source sheet "1"; source row 79; year 2015 column W (cell W79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2015 column W (cell W80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L45" s="32" t="n">
         <x:v>46237</x:v>
@@ -2229,7 +2229,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K46" t="str">
-        <x:v>Source sheet "1"; source row 80; year 2015 column W (cell W80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2015 column W (cell W81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L46" s="32" t="n">
         <x:v>46237</x:v>
@@ -2267,7 +2267,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K47" t="str">
-        <x:v>Source sheet "1"; source row 81; year 2015 column W (cell W81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2015 column W (cell W82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L47" s="32" t="n">
         <x:v>46237</x:v>
@@ -2305,7 +2305,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K48" t="str">
-        <x:v>Source sheet "1"; source row 82; year 2015 column W (cell W82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 83; year 2015 column W (cell W83); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L48" s="32" t="n">
         <x:v>46237</x:v>
@@ -2343,7 +2343,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K49" t="str">
-        <x:v>Source sheet "1"; source row 17; year 2015 column W (cell W17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2015 column W (cell W18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L49" s="32" t="n">
         <x:v>46237</x:v>
@@ -2381,7 +2381,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K50" t="str">
-        <x:v>Source sheet "1"; source row 18; year 2015 column W (cell W18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2015 column W (cell W19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L50" s="32" t="n">
         <x:v>46237</x:v>
@@ -2419,7 +2419,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K51" t="str">
-        <x:v>Source sheet "1"; source row 19; year 2015 column W (cell W19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 20; year 2015 column W (cell W20); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L51" s="32" t="n">
         <x:v>46237</x:v>
@@ -2457,7 +2457,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K52" t="str">
-        <x:v>Source sheet "1"; source row 73; year 2015 column W (cell W73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2015 column W (cell W74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L52" s="32" t="n">
         <x:v>46237</x:v>
@@ -2495,7 +2495,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K53" t="str">
-        <x:v>Source sheet "1"; source row 69; year 2015 column W (cell W69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2015 column W (cell W70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L53" s="32" t="n">
         <x:v>46237</x:v>
@@ -2533,7 +2533,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K54" t="str">
-        <x:v>Source sheet "1"; source row 70; year 2015 column W (cell W70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2015 column W (cell W71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L54" s="32" t="n">
         <x:v>46237</x:v>
@@ -2571,7 +2571,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K55" t="str">
-        <x:v>Source sheet "1"; source row 71; year 2015 column W (cell W71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2015 column W (cell W72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L55" s="32" t="n">
         <x:v>46237</x:v>
@@ -2609,7 +2609,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K56" t="str">
-        <x:v>Source sheet "1"; source row 72; year 2015 column W (cell W72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2015 column W (cell W73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L56" s="32" t="n">
         <x:v>46237</x:v>
@@ -2647,7 +2647,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K57" t="str">
-        <x:v>Source sheet "1"; source row 74; year 2015 column W (cell W74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 75; year 2015 column W (cell W75); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L57" s="32" t="n">
         <x:v>46237</x:v>
@@ -2685,7 +2685,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K58" t="str">
-        <x:v>Source sheet "1"; source row 46; year 2015 column W (cell W46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2015 column W (cell W47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L58" s="32" t="n">
         <x:v>46237</x:v>
@@ -2723,7 +2723,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K59" t="str">
-        <x:v>Source sheet "1"; source row 47; year 2015 column W (cell W47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2015 column W (cell W48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L59" s="32" t="n">
         <x:v>46237</x:v>
@@ -2761,7 +2761,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K60" t="str">
-        <x:v>Source sheet "1"; source row 48; year 2015 column W (cell W48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2015 column W (cell W49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L60" s="32" t="n">
         <x:v>46237</x:v>
@@ -2799,7 +2799,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K61" t="str">
-        <x:v>Source sheet "1"; source row 49; year 2015 column W (cell W49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 50; year 2015 column W (cell W50); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L61" s="32" t="n">
         <x:v>46237</x:v>
@@ -2837,7 +2837,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K62" t="str">
-        <x:v>Source sheet "1"; source row 52; year 2015 column W (cell W52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2015 column W (cell W53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L62" s="32" t="n">
         <x:v>46237</x:v>
@@ -2875,7 +2875,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K63" t="str">
-        <x:v>Source sheet "1"; source row 53; year 2015 column W (cell W53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2015 column W (cell W54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L63" s="32" t="n">
         <x:v>46237</x:v>
@@ -2913,7 +2913,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K64" t="str">
-        <x:v>Source sheet "1"; source row 54; year 2015 column W (cell W54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2015 column W (cell W55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L64" s="32" t="n">
         <x:v>46237</x:v>
@@ -2951,7 +2951,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K65" t="str">
-        <x:v>Source sheet "1"; source row 55; year 2015 column W (cell W55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 56; year 2015 column W (cell W56); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L65" s="32" t="n">
         <x:v>46237</x:v>
@@ -2989,7 +2989,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K66" t="str">
-        <x:v>Source sheet "1"; source row 5; year 2016 column X (cell X5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 6; year 2016 column X (cell X6); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L66" s="32" t="n">
         <x:v>46237</x:v>
@@ -3027,7 +3027,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K67" t="str">
-        <x:v>Source sheet "1"; source row 9; year 2016 column X (cell X9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2016 column X (cell X10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L67" s="32" t="n">
         <x:v>46237</x:v>
@@ -3065,7 +3065,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K68" t="str">
-        <x:v>Source sheet "1"; source row 11; year 2016 column X (cell X11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2016 column X (cell X12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L68" s="32" t="n">
         <x:v>46237</x:v>
@@ -3103,7 +3103,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K69" t="str">
-        <x:v>Source sheet "1"; source row 13; year 2016 column X (cell X13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2016 column X (cell X14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L69" s="32" t="n">
         <x:v>46237</x:v>
@@ -3141,7 +3141,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K70" t="str">
-        <x:v>Source sheet "1"; source row 10; year 2016 column X (cell X10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2016 column X (cell X11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L70" s="32" t="n">
         <x:v>46237</x:v>
@@ -3179,7 +3179,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K71" t="str">
-        <x:v>Source sheet "1"; source row 12; year 2016 column X (cell X12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2016 column X (cell X13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L71" s="32" t="n">
         <x:v>46237</x:v>
@@ -3217,7 +3217,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K72" t="str">
-        <x:v>Source sheet "1"; source row 14; year 2016 column X (cell X14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 15; year 2016 column X (cell X15); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L72" s="32" t="n">
         <x:v>46237</x:v>
@@ -3255,7 +3255,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K73" t="str">
-        <x:v>Source sheet "1"; source row 35; year 2016 column X (cell X35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2016 column X (cell X36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L73" s="32" t="n">
         <x:v>46237</x:v>
@@ -3293,7 +3293,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K74" t="str">
-        <x:v>Source sheet "1"; source row 36; year 2016 column X (cell X36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2016 column X (cell X37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L74" s="32" t="n">
         <x:v>46237</x:v>
@@ -3331,7 +3331,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K75" t="str">
-        <x:v>Source sheet "1"; source row 37; year 2016 column X (cell X37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2016 column X (cell X38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L75" s="32" t="n">
         <x:v>46237</x:v>
@@ -3369,7 +3369,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K76" t="str">
-        <x:v>Source sheet "1"; source row 38; year 2016 column X (cell X38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2016 column X (cell X39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L76" s="32" t="n">
         <x:v>46237</x:v>
@@ -3407,7 +3407,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K77" t="str">
-        <x:v>Source sheet "1"; source row 39; year 2016 column X (cell X39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2016 column X (cell X40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L77" s="32" t="n">
         <x:v>46237</x:v>
@@ -3445,7 +3445,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K78" t="str">
-        <x:v>Source sheet "1"; source row 40; year 2016 column X (cell X40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2016 column X (cell X41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L78" s="32" t="n">
         <x:v>46237</x:v>
@@ -3483,7 +3483,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K79" t="str">
-        <x:v>Source sheet "1"; source row 41; year 2016 column X (cell X41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2016 column X (cell X42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L79" s="32" t="n">
         <x:v>46237</x:v>
@@ -3521,7 +3521,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K80" t="str">
-        <x:v>Source sheet "1"; source row 42; year 2016 column X (cell X42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 43; year 2016 column X (cell X43); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L80" s="32" t="n">
         <x:v>46237</x:v>
@@ -3559,7 +3559,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K81" t="str">
-        <x:v>Source sheet "1"; source row 21; year 2016 column X (cell X21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2016 column X (cell X22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L81" s="32" t="n">
         <x:v>46237</x:v>
@@ -3597,7 +3597,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>Source sheet "1"; source row 30; year 2016 column X (cell X30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2016 column X (cell X31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L82" s="32" t="n">
         <x:v>46237</x:v>
@@ -3635,7 +3635,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K83" t="str">
-        <x:v>Source sheet "1"; source row 28; year 2016 column X (cell X28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2016 column X (cell X29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L83" s="32" t="n">
         <x:v>46237</x:v>
@@ -3673,7 +3673,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K84" t="str">
-        <x:v>Source sheet "1"; source row 29; year 2016 column X (cell X29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2016 column X (cell X30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L84" s="32" t="n">
         <x:v>46237</x:v>
@@ -3711,7 +3711,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K85" t="str">
-        <x:v>Source sheet "1"; source row 22; year 2016 column X (cell X22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2016 column X (cell X23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L85" s="32" t="n">
         <x:v>46237</x:v>
@@ -3749,7 +3749,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K86" t="str">
-        <x:v>Source sheet "1"; source row 23; year 2016 column X (cell X23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2016 column X (cell X24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L86" s="32" t="n">
         <x:v>46237</x:v>
@@ -3787,7 +3787,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K87" t="str">
-        <x:v>Source sheet "1"; source row 24; year 2016 column X (cell X24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2016 column X (cell X25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L87" s="32" t="n">
         <x:v>46237</x:v>
@@ -3825,7 +3825,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K88" t="str">
-        <x:v>Source sheet "1"; source row 25; year 2016 column X (cell X25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2016 column X (cell X26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L88" s="32" t="n">
         <x:v>46237</x:v>
@@ -3863,7 +3863,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K89" t="str">
-        <x:v>Source sheet "1"; source row 26; year 2016 column X (cell X26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2016 column X (cell X27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L89" s="32" t="n">
         <x:v>46237</x:v>
@@ -3901,7 +3901,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K90" t="str">
-        <x:v>Source sheet "1"; source row 27; year 2016 column X (cell X27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2016 column X (cell X28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L90" s="32" t="n">
         <x:v>46237</x:v>
@@ -3939,7 +3939,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K91" t="str">
-        <x:v>Source sheet "1"; source row 31; year 2016 column X (cell X31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2016 column X (cell X32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L91" s="32" t="n">
         <x:v>46237</x:v>
@@ -3977,7 +3977,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K92" t="str">
-        <x:v>Source sheet "1"; source row 32; year 2016 column X (cell X32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 33; year 2016 column X (cell X33); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L92" s="32" t="n">
         <x:v>46237</x:v>
@@ -4015,7 +4015,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K93" t="str">
-        <x:v>Source sheet "1"; source row 58; year 2016 column X (cell X58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2016 column X (cell X59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L93" s="32" t="n">
         <x:v>46237</x:v>
@@ -4053,7 +4053,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K94" t="str">
-        <x:v>Source sheet "1"; source row 60; year 2016 column X (cell X60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2016 column X (cell X61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L94" s="32" t="n">
         <x:v>46237</x:v>
@@ -4091,7 +4091,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K95" t="str">
-        <x:v>Source sheet "1"; source row 59; year 2016 column X (cell X59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2016 column X (cell X60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L95" s="32" t="n">
         <x:v>46237</x:v>
@@ -4129,7 +4129,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K96" t="str">
-        <x:v>Source sheet "1"; source row 61; year 2016 column X (cell X61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2016 column X (cell X62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L96" s="32" t="n">
         <x:v>46237</x:v>
@@ -4167,7 +4167,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K97" t="str">
-        <x:v>Source sheet "1"; source row 62; year 2016 column X (cell X62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2016 column X (cell X63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L97" s="32" t="n">
         <x:v>46237</x:v>
@@ -4205,7 +4205,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K98" t="str">
-        <x:v>Source sheet "1"; source row 63; year 2016 column X (cell X63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2016 column X (cell X64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L98" s="32" t="n">
         <x:v>46237</x:v>
@@ -4243,7 +4243,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K99" t="str">
-        <x:v>Source sheet "1"; source row 64; year 2016 column X (cell X64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2016 column X (cell X65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L99" s="32" t="n">
         <x:v>46237</x:v>
@@ -4281,7 +4281,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K100" t="str">
-        <x:v>Source sheet "1"; source row 65; year 2016 column X (cell X65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2016 column X (cell X66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L100" s="32" t="n">
         <x:v>46237</x:v>
@@ -4319,7 +4319,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K101" t="str">
-        <x:v>Source sheet "1"; source row 66; year 2016 column X (cell X66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 67; year 2016 column X (cell X67); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L101" s="32" t="n">
         <x:v>46237</x:v>
@@ -4357,7 +4357,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K102" t="str">
-        <x:v>Source sheet "1"; source row 85; year 2016 column X (cell X85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 86; year 2016 column X (cell X86); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L102" s="32" t="n">
         <x:v>46237</x:v>
@@ -4395,7 +4395,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K103" t="str">
-        <x:v>Source sheet "1"; source row 89; year 2016 column X (cell X89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 90; year 2016 column X (cell X90); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L103" s="32" t="n">
         <x:v>46237</x:v>
@@ -4433,7 +4433,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K104" t="str">
-        <x:v>Source sheet "1"; source row 88; year 2016 column X (cell X88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2016 column X (cell X89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L104" s="32" t="n">
         <x:v>46237</x:v>
@@ -4471,7 +4471,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K105" t="str">
-        <x:v>Source sheet "1"; source row 91; year 2016 column X (cell X91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 92; year 2016 column X (cell X92); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L105" s="32" t="n">
         <x:v>46237</x:v>
@@ -4509,7 +4509,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K106" t="str">
-        <x:v>Source sheet "1"; source row 76; year 2016 column X (cell X76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2016 column X (cell X77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L106" s="32" t="n">
         <x:v>46237</x:v>
@@ -4547,7 +4547,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K107" t="str">
-        <x:v>Source sheet "1"; source row 77; year 2016 column X (cell X77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2016 column X (cell X78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L107" s="32" t="n">
         <x:v>46237</x:v>
@@ -4585,7 +4585,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K108" t="str">
-        <x:v>Source sheet "1"; source row 78; year 2016 column X (cell X78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2016 column X (cell X79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L108" s="32" t="n">
         <x:v>46237</x:v>
@@ -4623,7 +4623,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K109" t="str">
-        <x:v>Source sheet "1"; source row 79; year 2016 column X (cell X79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2016 column X (cell X80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L109" s="32" t="n">
         <x:v>46237</x:v>
@@ -4661,7 +4661,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K110" t="str">
-        <x:v>Source sheet "1"; source row 80; year 2016 column X (cell X80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2016 column X (cell X81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L110" s="32" t="n">
         <x:v>46237</x:v>
@@ -4699,7 +4699,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K111" t="str">
-        <x:v>Source sheet "1"; source row 81; year 2016 column X (cell X81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2016 column X (cell X82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L111" s="32" t="n">
         <x:v>46237</x:v>
@@ -4737,7 +4737,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K112" t="str">
-        <x:v>Source sheet "1"; source row 82; year 2016 column X (cell X82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 83; year 2016 column X (cell X83); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L112" s="32" t="n">
         <x:v>46237</x:v>
@@ -4775,7 +4775,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K113" t="str">
-        <x:v>Source sheet "1"; source row 17; year 2016 column X (cell X17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2016 column X (cell X18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L113" s="32" t="n">
         <x:v>46237</x:v>
@@ -4813,7 +4813,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K114" t="str">
-        <x:v>Source sheet "1"; source row 18; year 2016 column X (cell X18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2016 column X (cell X19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L114" s="32" t="n">
         <x:v>46237</x:v>
@@ -4851,7 +4851,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K115" t="str">
-        <x:v>Source sheet "1"; source row 19; year 2016 column X (cell X19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 20; year 2016 column X (cell X20); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L115" s="32" t="n">
         <x:v>46237</x:v>
@@ -4889,7 +4889,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K116" t="str">
-        <x:v>Source sheet "1"; source row 73; year 2016 column X (cell X73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2016 column X (cell X74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L116" s="32" t="n">
         <x:v>46237</x:v>
@@ -4927,7 +4927,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K117" t="str">
-        <x:v>Source sheet "1"; source row 69; year 2016 column X (cell X69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2016 column X (cell X70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L117" s="32" t="n">
         <x:v>46237</x:v>
@@ -4965,7 +4965,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K118" t="str">
-        <x:v>Source sheet "1"; source row 70; year 2016 column X (cell X70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2016 column X (cell X71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L118" s="32" t="n">
         <x:v>46237</x:v>
@@ -5003,7 +5003,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K119" t="str">
-        <x:v>Source sheet "1"; source row 71; year 2016 column X (cell X71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2016 column X (cell X72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L119" s="32" t="n">
         <x:v>46237</x:v>
@@ -5041,7 +5041,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K120" t="str">
-        <x:v>Source sheet "1"; source row 72; year 2016 column X (cell X72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2016 column X (cell X73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L120" s="32" t="n">
         <x:v>46237</x:v>
@@ -5079,7 +5079,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K121" t="str">
-        <x:v>Source sheet "1"; source row 74; year 2016 column X (cell X74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 75; year 2016 column X (cell X75); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L121" s="32" t="n">
         <x:v>46237</x:v>
@@ -5117,7 +5117,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K122" t="str">
-        <x:v>Source sheet "1"; source row 46; year 2016 column X (cell X46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2016 column X (cell X47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L122" s="32" t="n">
         <x:v>46237</x:v>
@@ -5155,7 +5155,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K123" t="str">
-        <x:v>Source sheet "1"; source row 47; year 2016 column X (cell X47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2016 column X (cell X48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L123" s="32" t="n">
         <x:v>46237</x:v>
@@ -5193,7 +5193,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K124" t="str">
-        <x:v>Source sheet "1"; source row 48; year 2016 column X (cell X48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2016 column X (cell X49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L124" s="32" t="n">
         <x:v>46237</x:v>
@@ -5231,7 +5231,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K125" t="str">
-        <x:v>Source sheet "1"; source row 49; year 2016 column X (cell X49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 50; year 2016 column X (cell X50); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L125" s="32" t="n">
         <x:v>46237</x:v>
@@ -5269,7 +5269,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K126" t="str">
-        <x:v>Source sheet "1"; source row 52; year 2016 column X (cell X52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2016 column X (cell X53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L126" s="32" t="n">
         <x:v>46237</x:v>
@@ -5307,7 +5307,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K127" t="str">
-        <x:v>Source sheet "1"; source row 53; year 2016 column X (cell X53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2016 column X (cell X54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L127" s="32" t="n">
         <x:v>46237</x:v>
@@ -5345,7 +5345,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K128" t="str">
-        <x:v>Source sheet "1"; source row 54; year 2016 column X (cell X54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2016 column X (cell X55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L128" s="32" t="n">
         <x:v>46237</x:v>
@@ -5383,7 +5383,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K129" t="str">
-        <x:v>Source sheet "1"; source row 55; year 2016 column X (cell X55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 56; year 2016 column X (cell X56); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L129" s="32" t="n">
         <x:v>46237</x:v>
@@ -5421,7 +5421,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K130" t="str">
-        <x:v>Source sheet "1"; source row 5; year 2017 column Y (cell Y5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 6; year 2017 column Y (cell Y6); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L130" s="32" t="n">
         <x:v>46237</x:v>
@@ -5459,7 +5459,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K131" t="str">
-        <x:v>Source sheet "1"; source row 9; year 2017 column Y (cell Y9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2017 column Y (cell Y10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L131" s="32" t="n">
         <x:v>46237</x:v>
@@ -5497,7 +5497,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K132" t="str">
-        <x:v>Source sheet "1"; source row 11; year 2017 column Y (cell Y11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2017 column Y (cell Y12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L132" s="32" t="n">
         <x:v>46237</x:v>
@@ -5535,7 +5535,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K133" t="str">
-        <x:v>Source sheet "1"; source row 13; year 2017 column Y (cell Y13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2017 column Y (cell Y14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L133" s="32" t="n">
         <x:v>46237</x:v>
@@ -5573,7 +5573,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K134" t="str">
-        <x:v>Source sheet "1"; source row 10; year 2017 column Y (cell Y10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2017 column Y (cell Y11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L134" s="32" t="n">
         <x:v>46237</x:v>
@@ -5611,7 +5611,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K135" t="str">
-        <x:v>Source sheet "1"; source row 12; year 2017 column Y (cell Y12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2017 column Y (cell Y13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L135" s="32" t="n">
         <x:v>46237</x:v>
@@ -5649,7 +5649,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K136" t="str">
-        <x:v>Source sheet "1"; source row 14; year 2017 column Y (cell Y14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 15; year 2017 column Y (cell Y15); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L136" s="32" t="n">
         <x:v>46237</x:v>
@@ -5687,7 +5687,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K137" t="str">
-        <x:v>Source sheet "1"; source row 35; year 2017 column Y (cell Y35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2017 column Y (cell Y36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L137" s="32" t="n">
         <x:v>46237</x:v>
@@ -5725,7 +5725,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K138" t="str">
-        <x:v>Source sheet "1"; source row 36; year 2017 column Y (cell Y36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2017 column Y (cell Y37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L138" s="32" t="n">
         <x:v>46237</x:v>
@@ -5763,7 +5763,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K139" t="str">
-        <x:v>Source sheet "1"; source row 37; year 2017 column Y (cell Y37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2017 column Y (cell Y38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L139" s="32" t="n">
         <x:v>46237</x:v>
@@ -5801,7 +5801,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K140" t="str">
-        <x:v>Source sheet "1"; source row 38; year 2017 column Y (cell Y38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2017 column Y (cell Y39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L140" s="32" t="n">
         <x:v>46237</x:v>
@@ -5839,7 +5839,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K141" t="str">
-        <x:v>Source sheet "1"; source row 39; year 2017 column Y (cell Y39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2017 column Y (cell Y40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L141" s="32" t="n">
         <x:v>46237</x:v>
@@ -5877,7 +5877,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K142" t="str">
-        <x:v>Source sheet "1"; source row 40; year 2017 column Y (cell Y40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2017 column Y (cell Y41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L142" s="32" t="n">
         <x:v>46237</x:v>
@@ -5915,7 +5915,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K143" t="str">
-        <x:v>Source sheet "1"; source row 41; year 2017 column Y (cell Y41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2017 column Y (cell Y42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L143" s="32" t="n">
         <x:v>46237</x:v>
@@ -5953,7 +5953,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K144" t="str">
-        <x:v>Source sheet "1"; source row 42; year 2017 column Y (cell Y42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 43; year 2017 column Y (cell Y43); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L144" s="32" t="n">
         <x:v>46237</x:v>
@@ -5991,7 +5991,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K145" t="str">
-        <x:v>Source sheet "1"; source row 21; year 2017 column Y (cell Y21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2017 column Y (cell Y22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L145" s="32" t="n">
         <x:v>46237</x:v>
@@ -6029,7 +6029,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K146" t="str">
-        <x:v>Source sheet "1"; source row 30; year 2017 column Y (cell Y30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2017 column Y (cell Y31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L146" s="32" t="n">
         <x:v>46237</x:v>
@@ -6067,7 +6067,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K147" t="str">
-        <x:v>Source sheet "1"; source row 28; year 2017 column Y (cell Y28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2017 column Y (cell Y29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L147" s="32" t="n">
         <x:v>46237</x:v>
@@ -6105,7 +6105,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K148" t="str">
-        <x:v>Source sheet "1"; source row 29; year 2017 column Y (cell Y29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2017 column Y (cell Y30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L148" s="32" t="n">
         <x:v>46237</x:v>
@@ -6143,7 +6143,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K149" t="str">
-        <x:v>Source sheet "1"; source row 22; year 2017 column Y (cell Y22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2017 column Y (cell Y23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L149" s="32" t="n">
         <x:v>46237</x:v>
@@ -6181,7 +6181,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K150" t="str">
-        <x:v>Source sheet "1"; source row 23; year 2017 column Y (cell Y23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2017 column Y (cell Y24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L150" s="32" t="n">
         <x:v>46237</x:v>
@@ -6219,7 +6219,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K151" t="str">
-        <x:v>Source sheet "1"; source row 24; year 2017 column Y (cell Y24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2017 column Y (cell Y25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L151" s="32" t="n">
         <x:v>46237</x:v>
@@ -6257,7 +6257,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K152" t="str">
-        <x:v>Source sheet "1"; source row 25; year 2017 column Y (cell Y25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2017 column Y (cell Y26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L152" s="32" t="n">
         <x:v>46237</x:v>
@@ -6295,7 +6295,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K153" t="str">
-        <x:v>Source sheet "1"; source row 26; year 2017 column Y (cell Y26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2017 column Y (cell Y27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L153" s="32" t="n">
         <x:v>46237</x:v>
@@ -6333,7 +6333,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K154" t="str">
-        <x:v>Source sheet "1"; source row 27; year 2017 column Y (cell Y27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2017 column Y (cell Y28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L154" s="32" t="n">
         <x:v>46237</x:v>
@@ -6371,7 +6371,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K155" t="str">
-        <x:v>Source sheet "1"; source row 31; year 2017 column Y (cell Y31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2017 column Y (cell Y32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L155" s="32" t="n">
         <x:v>46237</x:v>
@@ -6409,7 +6409,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K156" t="str">
-        <x:v>Source sheet "1"; source row 32; year 2017 column Y (cell Y32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 33; year 2017 column Y (cell Y33); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L156" s="32" t="n">
         <x:v>46237</x:v>
@@ -6447,7 +6447,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K157" t="str">
-        <x:v>Source sheet "1"; source row 58; year 2017 column Y (cell Y58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2017 column Y (cell Y59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L157" s="32" t="n">
         <x:v>46237</x:v>
@@ -6485,7 +6485,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K158" t="str">
-        <x:v>Source sheet "1"; source row 60; year 2017 column Y (cell Y60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2017 column Y (cell Y61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L158" s="32" t="n">
         <x:v>46237</x:v>
@@ -6523,7 +6523,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K159" t="str">
-        <x:v>Source sheet "1"; source row 59; year 2017 column Y (cell Y59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2017 column Y (cell Y60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L159" s="32" t="n">
         <x:v>46237</x:v>
@@ -6561,7 +6561,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K160" t="str">
-        <x:v>Source sheet "1"; source row 61; year 2017 column Y (cell Y61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2017 column Y (cell Y62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L160" s="32" t="n">
         <x:v>46237</x:v>
@@ -6599,7 +6599,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K161" t="str">
-        <x:v>Source sheet "1"; source row 62; year 2017 column Y (cell Y62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2017 column Y (cell Y63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L161" s="32" t="n">
         <x:v>46237</x:v>
@@ -6637,7 +6637,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K162" t="str">
-        <x:v>Source sheet "1"; source row 63; year 2017 column Y (cell Y63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2017 column Y (cell Y64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L162" s="32" t="n">
         <x:v>46237</x:v>
@@ -6675,7 +6675,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K163" t="str">
-        <x:v>Source sheet "1"; source row 64; year 2017 column Y (cell Y64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2017 column Y (cell Y65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L163" s="32" t="n">
         <x:v>46237</x:v>
@@ -6713,7 +6713,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K164" t="str">
-        <x:v>Source sheet "1"; source row 65; year 2017 column Y (cell Y65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2017 column Y (cell Y66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L164" s="32" t="n">
         <x:v>46237</x:v>
@@ -6751,7 +6751,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K165" t="str">
-        <x:v>Source sheet "1"; source row 66; year 2017 column Y (cell Y66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 67; year 2017 column Y (cell Y67); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L165" s="32" t="n">
         <x:v>46237</x:v>
@@ -6789,7 +6789,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K166" t="str">
-        <x:v>Source sheet "1"; source row 85; year 2017 column Y (cell Y85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 86; year 2017 column Y (cell Y86); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L166" s="32" t="n">
         <x:v>46237</x:v>
@@ -6827,7 +6827,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K167" t="str">
-        <x:v>Source sheet "1"; source row 89; year 2017 column Y (cell Y89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 90; year 2017 column Y (cell Y90); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L167" s="32" t="n">
         <x:v>46237</x:v>
@@ -6865,7 +6865,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K168" t="str">
-        <x:v>Source sheet "1"; source row 88; year 2017 column Y (cell Y88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2017 column Y (cell Y89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L168" s="32" t="n">
         <x:v>46237</x:v>
@@ -6903,7 +6903,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K169" t="str">
-        <x:v>Source sheet "1"; source row 91; year 2017 column Y (cell Y91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 92; year 2017 column Y (cell Y92); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L169" s="32" t="n">
         <x:v>46237</x:v>
@@ -6941,7 +6941,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K170" t="str">
-        <x:v>Source sheet "1"; source row 76; year 2017 column Y (cell Y76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2017 column Y (cell Y77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L170" s="32" t="n">
         <x:v>46237</x:v>
@@ -6979,7 +6979,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K171" t="str">
-        <x:v>Source sheet "1"; source row 77; year 2017 column Y (cell Y77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2017 column Y (cell Y78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L171" s="32" t="n">
         <x:v>46237</x:v>
@@ -7017,7 +7017,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K172" t="str">
-        <x:v>Source sheet "1"; source row 78; year 2017 column Y (cell Y78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2017 column Y (cell Y79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L172" s="32" t="n">
         <x:v>46237</x:v>
@@ -7055,7 +7055,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K173" t="str">
-        <x:v>Source sheet "1"; source row 79; year 2017 column Y (cell Y79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2017 column Y (cell Y80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L173" s="32" t="n">
         <x:v>46237</x:v>
@@ -7093,7 +7093,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K174" t="str">
-        <x:v>Source sheet "1"; source row 80; year 2017 column Y (cell Y80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2017 column Y (cell Y81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L174" s="32" t="n">
         <x:v>46237</x:v>
@@ -7131,7 +7131,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K175" t="str">
-        <x:v>Source sheet "1"; source row 81; year 2017 column Y (cell Y81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2017 column Y (cell Y82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L175" s="32" t="n">
         <x:v>46237</x:v>
@@ -7169,7 +7169,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K176" t="str">
-        <x:v>Source sheet "1"; source row 82; year 2017 column Y (cell Y82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 83; year 2017 column Y (cell Y83); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L176" s="32" t="n">
         <x:v>46237</x:v>
@@ -7207,7 +7207,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K177" t="str">
-        <x:v>Source sheet "1"; source row 17; year 2017 column Y (cell Y17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2017 column Y (cell Y18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L177" s="32" t="n">
         <x:v>46237</x:v>
@@ -7245,7 +7245,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K178" t="str">
-        <x:v>Source sheet "1"; source row 18; year 2017 column Y (cell Y18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2017 column Y (cell Y19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L178" s="32" t="n">
         <x:v>46237</x:v>
@@ -7283,7 +7283,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K179" t="str">
-        <x:v>Source sheet "1"; source row 19; year 2017 column Y (cell Y19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 20; year 2017 column Y (cell Y20); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L179" s="32" t="n">
         <x:v>46237</x:v>
@@ -7321,7 +7321,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K180" t="str">
-        <x:v>Source sheet "1"; source row 73; year 2017 column Y (cell Y73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2017 column Y (cell Y74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L180" s="32" t="n">
         <x:v>46237</x:v>
@@ -7359,7 +7359,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K181" t="str">
-        <x:v>Source sheet "1"; source row 69; year 2017 column Y (cell Y69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2017 column Y (cell Y70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L181" s="32" t="n">
         <x:v>46237</x:v>
@@ -7397,7 +7397,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K182" t="str">
-        <x:v>Source sheet "1"; source row 70; year 2017 column Y (cell Y70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2017 column Y (cell Y71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L182" s="32" t="n">
         <x:v>46237</x:v>
@@ -7435,7 +7435,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K183" t="str">
-        <x:v>Source sheet "1"; source row 71; year 2017 column Y (cell Y71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2017 column Y (cell Y72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L183" s="32" t="n">
         <x:v>46237</x:v>
@@ -7473,7 +7473,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K184" t="str">
-        <x:v>Source sheet "1"; source row 72; year 2017 column Y (cell Y72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2017 column Y (cell Y73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L184" s="32" t="n">
         <x:v>46237</x:v>
@@ -7511,7 +7511,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K185" t="str">
-        <x:v>Source sheet "1"; source row 74; year 2017 column Y (cell Y74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 75; year 2017 column Y (cell Y75); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L185" s="32" t="n">
         <x:v>46237</x:v>
@@ -7549,7 +7549,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K186" t="str">
-        <x:v>Source sheet "1"; source row 46; year 2017 column Y (cell Y46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2017 column Y (cell Y47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L186" s="32" t="n">
         <x:v>46237</x:v>
@@ -7587,7 +7587,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K187" t="str">
-        <x:v>Source sheet "1"; source row 47; year 2017 column Y (cell Y47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2017 column Y (cell Y48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L187" s="32" t="n">
         <x:v>46237</x:v>
@@ -7625,7 +7625,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K188" t="str">
-        <x:v>Source sheet "1"; source row 48; year 2017 column Y (cell Y48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2017 column Y (cell Y49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L188" s="32" t="n">
         <x:v>46237</x:v>
@@ -7663,7 +7663,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K189" t="str">
-        <x:v>Source sheet "1"; source row 49; year 2017 column Y (cell Y49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 50; year 2017 column Y (cell Y50); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L189" s="32" t="n">
         <x:v>46237</x:v>
@@ -7701,7 +7701,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K190" t="str">
-        <x:v>Source sheet "1"; source row 52; year 2017 column Y (cell Y52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2017 column Y (cell Y53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L190" s="32" t="n">
         <x:v>46237</x:v>
@@ -7739,7 +7739,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K191" t="str">
-        <x:v>Source sheet "1"; source row 53; year 2017 column Y (cell Y53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2017 column Y (cell Y54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L191" s="32" t="n">
         <x:v>46237</x:v>
@@ -7777,7 +7777,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K192" t="str">
-        <x:v>Source sheet "1"; source row 54; year 2017 column Y (cell Y54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2017 column Y (cell Y55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L192" s="32" t="n">
         <x:v>46237</x:v>
@@ -7815,7 +7815,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K193" t="str">
-        <x:v>Source sheet "1"; source row 55; year 2017 column Y (cell Y55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 56; year 2017 column Y (cell Y56); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L193" s="32" t="n">
         <x:v>46237</x:v>
@@ -7853,7 +7853,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K194" t="str">
-        <x:v>Source sheet "1"; source row 5; year 2018 column Z (cell Z5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 6; year 2018 column Z (cell Z6); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L194" s="32" t="n">
         <x:v>46237</x:v>
@@ -7891,7 +7891,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K195" t="str">
-        <x:v>Source sheet "1"; source row 9; year 2018 column Z (cell Z9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2018 column Z (cell Z10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L195" s="32" t="n">
         <x:v>46237</x:v>
@@ -7929,7 +7929,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K196" t="str">
-        <x:v>Source sheet "1"; source row 11; year 2018 column Z (cell Z11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2018 column Z (cell Z12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L196" s="32" t="n">
         <x:v>46237</x:v>
@@ -7967,7 +7967,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K197" t="str">
-        <x:v>Source sheet "1"; source row 13; year 2018 column Z (cell Z13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2018 column Z (cell Z14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L197" s="32" t="n">
         <x:v>46237</x:v>
@@ -8005,7 +8005,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K198" t="str">
-        <x:v>Source sheet "1"; source row 10; year 2018 column Z (cell Z10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2018 column Z (cell Z11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L198" s="32" t="n">
         <x:v>46237</x:v>
@@ -8043,7 +8043,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K199" t="str">
-        <x:v>Source sheet "1"; source row 12; year 2018 column Z (cell Z12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2018 column Z (cell Z13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L199" s="32" t="n">
         <x:v>46237</x:v>
@@ -8081,7 +8081,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K200" t="str">
-        <x:v>Source sheet "1"; source row 14; year 2018 column Z (cell Z14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 15; year 2018 column Z (cell Z15); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L200" s="32" t="n">
         <x:v>46237</x:v>
@@ -8119,7 +8119,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K201" t="str">
-        <x:v>Source sheet "1"; source row 35; year 2018 column Z (cell Z35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2018 column Z (cell Z36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L201" s="32" t="n">
         <x:v>46237</x:v>
@@ -8157,7 +8157,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K202" t="str">
-        <x:v>Source sheet "1"; source row 36; year 2018 column Z (cell Z36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2018 column Z (cell Z37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L202" s="32" t="n">
         <x:v>46237</x:v>
@@ -8195,7 +8195,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K203" t="str">
-        <x:v>Source sheet "1"; source row 37; year 2018 column Z (cell Z37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2018 column Z (cell Z38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L203" s="32" t="n">
         <x:v>46237</x:v>
@@ -8233,7 +8233,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K204" t="str">
-        <x:v>Source sheet "1"; source row 38; year 2018 column Z (cell Z38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2018 column Z (cell Z39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L204" s="32" t="n">
         <x:v>46237</x:v>
@@ -8271,7 +8271,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K205" t="str">
-        <x:v>Source sheet "1"; source row 39; year 2018 column Z (cell Z39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2018 column Z (cell Z40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L205" s="32" t="n">
         <x:v>46237</x:v>
@@ -8309,7 +8309,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K206" t="str">
-        <x:v>Source sheet "1"; source row 40; year 2018 column Z (cell Z40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2018 column Z (cell Z41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L206" s="32" t="n">
         <x:v>46237</x:v>
@@ -8347,7 +8347,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K207" t="str">
-        <x:v>Source sheet "1"; source row 41; year 2018 column Z (cell Z41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2018 column Z (cell Z42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L207" s="32" t="n">
         <x:v>46237</x:v>
@@ -8385,7 +8385,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K208" t="str">
-        <x:v>Source sheet "1"; source row 42; year 2018 column Z (cell Z42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 43; year 2018 column Z (cell Z43); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L208" s="32" t="n">
         <x:v>46237</x:v>
@@ -8423,7 +8423,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K209" t="str">
-        <x:v>Source sheet "1"; source row 21; year 2018 column Z (cell Z21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2018 column Z (cell Z22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L209" s="32" t="n">
         <x:v>46237</x:v>
@@ -8461,7 +8461,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K210" t="str">
-        <x:v>Source sheet "1"; source row 30; year 2018 column Z (cell Z30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2018 column Z (cell Z31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L210" s="32" t="n">
         <x:v>46237</x:v>
@@ -8499,7 +8499,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K211" t="str">
-        <x:v>Source sheet "1"; source row 28; year 2018 column Z (cell Z28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2018 column Z (cell Z29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L211" s="32" t="n">
         <x:v>46237</x:v>
@@ -8537,7 +8537,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K212" t="str">
-        <x:v>Source sheet "1"; source row 29; year 2018 column Z (cell Z29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2018 column Z (cell Z30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L212" s="32" t="n">
         <x:v>46237</x:v>
@@ -8575,7 +8575,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K213" t="str">
-        <x:v>Source sheet "1"; source row 22; year 2018 column Z (cell Z22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2018 column Z (cell Z23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L213" s="32" t="n">
         <x:v>46237</x:v>
@@ -8613,7 +8613,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K214" t="str">
-        <x:v>Source sheet "1"; source row 23; year 2018 column Z (cell Z23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2018 column Z (cell Z24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L214" s="32" t="n">
         <x:v>46237</x:v>
@@ -8651,7 +8651,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K215" t="str">
-        <x:v>Source sheet "1"; source row 24; year 2018 column Z (cell Z24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2018 column Z (cell Z25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L215" s="32" t="n">
         <x:v>46237</x:v>
@@ -8689,7 +8689,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K216" t="str">
-        <x:v>Source sheet "1"; source row 25; year 2018 column Z (cell Z25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2018 column Z (cell Z26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L216" s="32" t="n">
         <x:v>46237</x:v>
@@ -8727,7 +8727,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K217" t="str">
-        <x:v>Source sheet "1"; source row 26; year 2018 column Z (cell Z26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2018 column Z (cell Z27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L217" s="32" t="n">
         <x:v>46237</x:v>
@@ -8765,7 +8765,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K218" t="str">
-        <x:v>Source sheet "1"; source row 27; year 2018 column Z (cell Z27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2018 column Z (cell Z28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L218" s="32" t="n">
         <x:v>46237</x:v>
@@ -8803,7 +8803,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K219" t="str">
-        <x:v>Source sheet "1"; source row 31; year 2018 column Z (cell Z31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2018 column Z (cell Z32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L219" s="32" t="n">
         <x:v>46237</x:v>
@@ -8841,7 +8841,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K220" t="str">
-        <x:v>Source sheet "1"; source row 32; year 2018 column Z (cell Z32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 33; year 2018 column Z (cell Z33); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L220" s="32" t="n">
         <x:v>46237</x:v>
@@ -8879,7 +8879,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K221" t="str">
-        <x:v>Source sheet "1"; source row 58; year 2018 column Z (cell Z58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2018 column Z (cell Z59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L221" s="32" t="n">
         <x:v>46237</x:v>
@@ -8917,7 +8917,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K222" t="str">
-        <x:v>Source sheet "1"; source row 60; year 2018 column Z (cell Z60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2018 column Z (cell Z61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L222" s="32" t="n">
         <x:v>46237</x:v>
@@ -8955,7 +8955,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K223" t="str">
-        <x:v>Source sheet "1"; source row 59; year 2018 column Z (cell Z59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2018 column Z (cell Z60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L223" s="32" t="n">
         <x:v>46237</x:v>
@@ -8993,7 +8993,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K224" t="str">
-        <x:v>Source sheet "1"; source row 61; year 2018 column Z (cell Z61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2018 column Z (cell Z62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L224" s="32" t="n">
         <x:v>46237</x:v>
@@ -9031,7 +9031,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K225" t="str">
-        <x:v>Source sheet "1"; source row 62; year 2018 column Z (cell Z62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2018 column Z (cell Z63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L225" s="32" t="n">
         <x:v>46237</x:v>
@@ -9069,7 +9069,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K226" t="str">
-        <x:v>Source sheet "1"; source row 63; year 2018 column Z (cell Z63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2018 column Z (cell Z64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L226" s="32" t="n">
         <x:v>46237</x:v>
@@ -9107,7 +9107,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K227" t="str">
-        <x:v>Source sheet "1"; source row 64; year 2018 column Z (cell Z64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2018 column Z (cell Z65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L227" s="32" t="n">
         <x:v>46237</x:v>
@@ -9145,7 +9145,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K228" t="str">
-        <x:v>Source sheet "1"; source row 65; year 2018 column Z (cell Z65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2018 column Z (cell Z66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L228" s="32" t="n">
         <x:v>46237</x:v>
@@ -9183,7 +9183,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K229" t="str">
-        <x:v>Source sheet "1"; source row 66; year 2018 column Z (cell Z66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 67; year 2018 column Z (cell Z67); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L229" s="32" t="n">
         <x:v>46237</x:v>
@@ -9221,7 +9221,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K230" t="str">
-        <x:v>Source sheet "1"; source row 85; year 2018 column Z (cell Z85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 86; year 2018 column Z (cell Z86); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L230" s="32" t="n">
         <x:v>46237</x:v>
@@ -9259,7 +9259,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K231" t="str">
-        <x:v>Source sheet "1"; source row 89; year 2018 column Z (cell Z89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 90; year 2018 column Z (cell Z90); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L231" s="32" t="n">
         <x:v>46237</x:v>
@@ -9297,7 +9297,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K232" t="str">
-        <x:v>Source sheet "1"; source row 88; year 2018 column Z (cell Z88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2018 column Z (cell Z89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L232" s="32" t="n">
         <x:v>46237</x:v>
@@ -9335,7 +9335,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K233" t="str">
-        <x:v>Source sheet "1"; source row 91; year 2018 column Z (cell Z91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 92; year 2018 column Z (cell Z92); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L233" s="32" t="n">
         <x:v>46237</x:v>
@@ -9373,7 +9373,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K234" t="str">
-        <x:v>Source sheet "1"; source row 76; year 2018 column Z (cell Z76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2018 column Z (cell Z77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L234" s="32" t="n">
         <x:v>46237</x:v>
@@ -9411,7 +9411,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K235" t="str">
-        <x:v>Source sheet "1"; source row 77; year 2018 column Z (cell Z77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2018 column Z (cell Z78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L235" s="32" t="n">
         <x:v>46237</x:v>
@@ -9449,7 +9449,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K236" t="str">
-        <x:v>Source sheet "1"; source row 78; year 2018 column Z (cell Z78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2018 column Z (cell Z79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L236" s="32" t="n">
         <x:v>46237</x:v>
@@ -9487,7 +9487,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K237" t="str">
-        <x:v>Source sheet "1"; source row 79; year 2018 column Z (cell Z79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2018 column Z (cell Z80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L237" s="32" t="n">
         <x:v>46237</x:v>
@@ -9525,7 +9525,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K238" t="str">
-        <x:v>Source sheet "1"; source row 80; year 2018 column Z (cell Z80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2018 column Z (cell Z81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L238" s="32" t="n">
         <x:v>46237</x:v>
@@ -9563,7 +9563,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K239" t="str">
-        <x:v>Source sheet "1"; source row 81; year 2018 column Z (cell Z81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2018 column Z (cell Z82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L239" s="32" t="n">
         <x:v>46237</x:v>
@@ -9601,7 +9601,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K240" t="str">
-        <x:v>Source sheet "1"; source row 82; year 2018 column Z (cell Z82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 83; year 2018 column Z (cell Z83); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L240" s="32" t="n">
         <x:v>46237</x:v>
@@ -9639,7 +9639,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K241" t="str">
-        <x:v>Source sheet "1"; source row 17; year 2018 column Z (cell Z17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2018 column Z (cell Z18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L241" s="32" t="n">
         <x:v>46237</x:v>
@@ -9677,7 +9677,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K242" t="str">
-        <x:v>Source sheet "1"; source row 18; year 2018 column Z (cell Z18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2018 column Z (cell Z19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L242" s="32" t="n">
         <x:v>46237</x:v>
@@ -9715,7 +9715,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K243" t="str">
-        <x:v>Source sheet "1"; source row 19; year 2018 column Z (cell Z19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 20; year 2018 column Z (cell Z20); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L243" s="32" t="n">
         <x:v>46237</x:v>
@@ -9753,7 +9753,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K244" t="str">
-        <x:v>Source sheet "1"; source row 73; year 2018 column Z (cell Z73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2018 column Z (cell Z74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L244" s="32" t="n">
         <x:v>46237</x:v>
@@ -9791,7 +9791,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K245" t="str">
-        <x:v>Source sheet "1"; source row 69; year 2018 column Z (cell Z69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2018 column Z (cell Z70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L245" s="32" t="n">
         <x:v>46237</x:v>
@@ -9829,7 +9829,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K246" t="str">
-        <x:v>Source sheet "1"; source row 70; year 2018 column Z (cell Z70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2018 column Z (cell Z71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L246" s="32" t="n">
         <x:v>46237</x:v>
@@ -9867,7 +9867,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K247" t="str">
-        <x:v>Source sheet "1"; source row 71; year 2018 column Z (cell Z71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2018 column Z (cell Z72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L247" s="32" t="n">
         <x:v>46237</x:v>
@@ -9905,7 +9905,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K248" t="str">
-        <x:v>Source sheet "1"; source row 72; year 2018 column Z (cell Z72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2018 column Z (cell Z73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L248" s="32" t="n">
         <x:v>46237</x:v>
@@ -9943,7 +9943,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K249" t="str">
-        <x:v>Source sheet "1"; source row 74; year 2018 column Z (cell Z74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 75; year 2018 column Z (cell Z75); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L249" s="32" t="n">
         <x:v>46237</x:v>
@@ -9981,7 +9981,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K250" t="str">
-        <x:v>Source sheet "1"; source row 46; year 2018 column Z (cell Z46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2018 column Z (cell Z47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L250" s="32" t="n">
         <x:v>46237</x:v>
@@ -10019,7 +10019,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K251" t="str">
-        <x:v>Source sheet "1"; source row 47; year 2018 column Z (cell Z47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2018 column Z (cell Z48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L251" s="32" t="n">
         <x:v>46237</x:v>
@@ -10057,7 +10057,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K252" t="str">
-        <x:v>Source sheet "1"; source row 48; year 2018 column Z (cell Z48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2018 column Z (cell Z49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L252" s="32" t="n">
         <x:v>46237</x:v>
@@ -10095,7 +10095,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K253" t="str">
-        <x:v>Source sheet "1"; source row 49; year 2018 column Z (cell Z49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 50; year 2018 column Z (cell Z50); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L253" s="32" t="n">
         <x:v>46237</x:v>
@@ -10133,7 +10133,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K254" t="str">
-        <x:v>Source sheet "1"; source row 52; year 2018 column Z (cell Z52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2018 column Z (cell Z53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L254" s="32" t="n">
         <x:v>46237</x:v>
@@ -10171,7 +10171,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K255" t="str">
-        <x:v>Source sheet "1"; source row 53; year 2018 column Z (cell Z53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2018 column Z (cell Z54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L255" s="32" t="n">
         <x:v>46237</x:v>
@@ -10209,7 +10209,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K256" t="str">
-        <x:v>Source sheet "1"; source row 54; year 2018 column Z (cell Z54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2018 column Z (cell Z55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L256" s="32" t="n">
         <x:v>46237</x:v>
@@ -10247,7 +10247,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K257" t="str">
-        <x:v>Source sheet "1"; source row 55; year 2018 column Z (cell Z55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 56; year 2018 column Z (cell Z56); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L257" s="32" t="n">
         <x:v>46237</x:v>
@@ -10285,7 +10285,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K258" t="str">
-        <x:v>Source sheet "1"; source row 5; year 2019 column AA (cell AA5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 6; year 2019 column AA (cell AA6); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L258" s="32" t="n">
         <x:v>46237</x:v>
@@ -10323,7 +10323,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K259" t="str">
-        <x:v>Source sheet "1"; source row 9; year 2019 column AA (cell AA9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2019 column AA (cell AA10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L259" s="32" t="n">
         <x:v>46237</x:v>
@@ -10361,7 +10361,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K260" t="str">
-        <x:v>Source sheet "1"; source row 11; year 2019 column AA (cell AA11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2019 column AA (cell AA12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L260" s="32" t="n">
         <x:v>46237</x:v>
@@ -10399,7 +10399,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K261" t="str">
-        <x:v>Source sheet "1"; source row 13; year 2019 column AA (cell AA13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2019 column AA (cell AA14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L261" s="32" t="n">
         <x:v>46237</x:v>
@@ -10437,7 +10437,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K262" t="str">
-        <x:v>Source sheet "1"; source row 10; year 2019 column AA (cell AA10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2019 column AA (cell AA11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L262" s="32" t="n">
         <x:v>46237</x:v>
@@ -10475,7 +10475,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K263" t="str">
-        <x:v>Source sheet "1"; source row 12; year 2019 column AA (cell AA12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2019 column AA (cell AA13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L263" s="32" t="n">
         <x:v>46237</x:v>
@@ -10513,7 +10513,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K264" t="str">
-        <x:v>Source sheet "1"; source row 14; year 2019 column AA (cell AA14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 15; year 2019 column AA (cell AA15); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L264" s="32" t="n">
         <x:v>46237</x:v>
@@ -10551,7 +10551,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K265" t="str">
-        <x:v>Source sheet "1"; source row 35; year 2019 column AA (cell AA35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2019 column AA (cell AA36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L265" s="32" t="n">
         <x:v>46237</x:v>
@@ -10589,7 +10589,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K266" t="str">
-        <x:v>Source sheet "1"; source row 36; year 2019 column AA (cell AA36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2019 column AA (cell AA37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L266" s="32" t="n">
         <x:v>46237</x:v>
@@ -10627,7 +10627,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K267" t="str">
-        <x:v>Source sheet "1"; source row 37; year 2019 column AA (cell AA37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2019 column AA (cell AA38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L267" s="32" t="n">
         <x:v>46237</x:v>
@@ -10665,7 +10665,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K268" t="str">
-        <x:v>Source sheet "1"; source row 38; year 2019 column AA (cell AA38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2019 column AA (cell AA39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L268" s="32" t="n">
         <x:v>46237</x:v>
@@ -10703,7 +10703,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K269" t="str">
-        <x:v>Source sheet "1"; source row 39; year 2019 column AA (cell AA39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2019 column AA (cell AA40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L269" s="32" t="n">
         <x:v>46237</x:v>
@@ -10741,7 +10741,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K270" t="str">
-        <x:v>Source sheet "1"; source row 40; year 2019 column AA (cell AA40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2019 column AA (cell AA41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L270" s="32" t="n">
         <x:v>46237</x:v>
@@ -10779,7 +10779,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K271" t="str">
-        <x:v>Source sheet "1"; source row 41; year 2019 column AA (cell AA41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2019 column AA (cell AA42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L271" s="32" t="n">
         <x:v>46237</x:v>
@@ -10817,7 +10817,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K272" t="str">
-        <x:v>Source sheet "1"; source row 42; year 2019 column AA (cell AA42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 43; year 2019 column AA (cell AA43); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L272" s="32" t="n">
         <x:v>46237</x:v>
@@ -10855,7 +10855,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K273" t="str">
-        <x:v>Source sheet "1"; source row 21; year 2019 column AA (cell AA21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2019 column AA (cell AA22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L273" s="32" t="n">
         <x:v>46237</x:v>
@@ -10893,7 +10893,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K274" t="str">
-        <x:v>Source sheet "1"; source row 30; year 2019 column AA (cell AA30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2019 column AA (cell AA31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L274" s="32" t="n">
         <x:v>46237</x:v>
@@ -10931,7 +10931,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K275" t="str">
-        <x:v>Source sheet "1"; source row 28; year 2019 column AA (cell AA28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2019 column AA (cell AA29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L275" s="32" t="n">
         <x:v>46237</x:v>
@@ -10969,7 +10969,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K276" t="str">
-        <x:v>Source sheet "1"; source row 29; year 2019 column AA (cell AA29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2019 column AA (cell AA30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L276" s="32" t="n">
         <x:v>46237</x:v>
@@ -11007,7 +11007,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K277" t="str">
-        <x:v>Source sheet "1"; source row 22; year 2019 column AA (cell AA22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2019 column AA (cell AA23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L277" s="32" t="n">
         <x:v>46237</x:v>
@@ -11045,7 +11045,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K278" t="str">
-        <x:v>Source sheet "1"; source row 23; year 2019 column AA (cell AA23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2019 column AA (cell AA24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L278" s="32" t="n">
         <x:v>46237</x:v>
@@ -11083,7 +11083,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K279" t="str">
-        <x:v>Source sheet "1"; source row 24; year 2019 column AA (cell AA24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2019 column AA (cell AA25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L279" s="32" t="n">
         <x:v>46237</x:v>
@@ -11121,7 +11121,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K280" t="str">
-        <x:v>Source sheet "1"; source row 25; year 2019 column AA (cell AA25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2019 column AA (cell AA26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L280" s="32" t="n">
         <x:v>46237</x:v>
@@ -11159,7 +11159,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K281" t="str">
-        <x:v>Source sheet "1"; source row 26; year 2019 column AA (cell AA26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2019 column AA (cell AA27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L281" s="32" t="n">
         <x:v>46237</x:v>
@@ -11197,7 +11197,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K282" t="str">
-        <x:v>Source sheet "1"; source row 27; year 2019 column AA (cell AA27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2019 column AA (cell AA28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L282" s="32" t="n">
         <x:v>46237</x:v>
@@ -11235,7 +11235,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K283" t="str">
-        <x:v>Source sheet "1"; source row 31; year 2019 column AA (cell AA31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2019 column AA (cell AA32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L283" s="32" t="n">
         <x:v>46237</x:v>
@@ -11273,7 +11273,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K284" t="str">
-        <x:v>Source sheet "1"; source row 32; year 2019 column AA (cell AA32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 33; year 2019 column AA (cell AA33); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L284" s="32" t="n">
         <x:v>46237</x:v>
@@ -11311,7 +11311,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K285" t="str">
-        <x:v>Source sheet "1"; source row 58; year 2019 column AA (cell AA58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2019 column AA (cell AA59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L285" s="32" t="n">
         <x:v>46237</x:v>
@@ -11349,7 +11349,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K286" t="str">
-        <x:v>Source sheet "1"; source row 60; year 2019 column AA (cell AA60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2019 column AA (cell AA61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L286" s="32" t="n">
         <x:v>46237</x:v>
@@ -11387,7 +11387,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K287" t="str">
-        <x:v>Source sheet "1"; source row 59; year 2019 column AA (cell AA59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2019 column AA (cell AA60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L287" s="32" t="n">
         <x:v>46237</x:v>
@@ -11425,7 +11425,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K288" t="str">
-        <x:v>Source sheet "1"; source row 61; year 2019 column AA (cell AA61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2019 column AA (cell AA62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L288" s="32" t="n">
         <x:v>46237</x:v>
@@ -11463,7 +11463,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K289" t="str">
-        <x:v>Source sheet "1"; source row 62; year 2019 column AA (cell AA62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2019 column AA (cell AA63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L289" s="32" t="n">
         <x:v>46237</x:v>
@@ -11501,7 +11501,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K290" t="str">
-        <x:v>Source sheet "1"; source row 63; year 2019 column AA (cell AA63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2019 column AA (cell AA64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L290" s="32" t="n">
         <x:v>46237</x:v>
@@ -11539,7 +11539,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K291" t="str">
-        <x:v>Source sheet "1"; source row 64; year 2019 column AA (cell AA64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2019 column AA (cell AA65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L291" s="32" t="n">
         <x:v>46237</x:v>
@@ -11577,7 +11577,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K292" t="str">
-        <x:v>Source sheet "1"; source row 65; year 2019 column AA (cell AA65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2019 column AA (cell AA66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L292" s="32" t="n">
         <x:v>46237</x:v>
@@ -11615,7 +11615,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K293" t="str">
-        <x:v>Source sheet "1"; source row 66; year 2019 column AA (cell AA66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 67; year 2019 column AA (cell AA67); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L293" s="32" t="n">
         <x:v>46237</x:v>
@@ -11653,7 +11653,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K294" t="str">
-        <x:v>Source sheet "1"; source row 85; year 2019 column AA (cell AA85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 86; year 2019 column AA (cell AA86); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L294" s="32" t="n">
         <x:v>46237</x:v>
@@ -11691,7 +11691,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K295" t="str">
-        <x:v>Source sheet "1"; source row 89; year 2019 column AA (cell AA89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 90; year 2019 column AA (cell AA90); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L295" s="32" t="n">
         <x:v>46237</x:v>
@@ -11729,7 +11729,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K296" t="str">
-        <x:v>Source sheet "1"; source row 88; year 2019 column AA (cell AA88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2019 column AA (cell AA89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L296" s="32" t="n">
         <x:v>46237</x:v>
@@ -11767,7 +11767,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K297" t="str">
-        <x:v>Source sheet "1"; source row 91; year 2019 column AA (cell AA91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 92; year 2019 column AA (cell AA92); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L297" s="32" t="n">
         <x:v>46237</x:v>
@@ -11805,7 +11805,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K298" t="str">
-        <x:v>Source sheet "1"; source row 76; year 2019 column AA (cell AA76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2019 column AA (cell AA77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L298" s="32" t="n">
         <x:v>46237</x:v>
@@ -11843,7 +11843,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K299" t="str">
-        <x:v>Source sheet "1"; source row 77; year 2019 column AA (cell AA77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2019 column AA (cell AA78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L299" s="32" t="n">
         <x:v>46237</x:v>
@@ -11881,7 +11881,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K300" t="str">
-        <x:v>Source sheet "1"; source row 78; year 2019 column AA (cell AA78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2019 column AA (cell AA79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L300" s="32" t="n">
         <x:v>46237</x:v>
@@ -11919,7 +11919,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K301" t="str">
-        <x:v>Source sheet "1"; source row 79; year 2019 column AA (cell AA79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2019 column AA (cell AA80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L301" s="32" t="n">
         <x:v>46237</x:v>
@@ -11957,7 +11957,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K302" t="str">
-        <x:v>Source sheet "1"; source row 80; year 2019 column AA (cell AA80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2019 column AA (cell AA81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L302" s="32" t="n">
         <x:v>46237</x:v>
@@ -11995,7 +11995,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K303" t="str">
-        <x:v>Source sheet "1"; source row 81; year 2019 column AA (cell AA81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2019 column AA (cell AA82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L303" s="32" t="n">
         <x:v>46237</x:v>
@@ -12033,7 +12033,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K304" t="str">
-        <x:v>Source sheet "1"; source row 82; year 2019 column AA (cell AA82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 83; year 2019 column AA (cell AA83); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L304" s="32" t="n">
         <x:v>46237</x:v>
@@ -12071,7 +12071,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K305" t="str">
-        <x:v>Source sheet "1"; source row 17; year 2019 column AA (cell AA17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2019 column AA (cell AA18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L305" s="32" t="n">
         <x:v>46237</x:v>
@@ -12109,7 +12109,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K306" t="str">
-        <x:v>Source sheet "1"; source row 18; year 2019 column AA (cell AA18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2019 column AA (cell AA19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L306" s="32" t="n">
         <x:v>46237</x:v>
@@ -12147,7 +12147,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K307" t="str">
-        <x:v>Source sheet "1"; source row 19; year 2019 column AA (cell AA19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 20; year 2019 column AA (cell AA20); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L307" s="32" t="n">
         <x:v>46237</x:v>
@@ -12185,7 +12185,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K308" t="str">
-        <x:v>Source sheet "1"; source row 73; year 2019 column AA (cell AA73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2019 column AA (cell AA74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L308" s="32" t="n">
         <x:v>46237</x:v>
@@ -12223,7 +12223,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K309" t="str">
-        <x:v>Source sheet "1"; source row 69; year 2019 column AA (cell AA69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2019 column AA (cell AA70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L309" s="32" t="n">
         <x:v>46237</x:v>
@@ -12261,7 +12261,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K310" t="str">
-        <x:v>Source sheet "1"; source row 70; year 2019 column AA (cell AA70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2019 column AA (cell AA71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L310" s="32" t="n">
         <x:v>46237</x:v>
@@ -12299,7 +12299,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K311" t="str">
-        <x:v>Source sheet "1"; source row 71; year 2019 column AA (cell AA71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2019 column AA (cell AA72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L311" s="32" t="n">
         <x:v>46237</x:v>
@@ -12337,7 +12337,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K312" t="str">
-        <x:v>Source sheet "1"; source row 72; year 2019 column AA (cell AA72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2019 column AA (cell AA73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L312" s="32" t="n">
         <x:v>46237</x:v>
@@ -12375,7 +12375,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K313" t="str">
-        <x:v>Source sheet "1"; source row 74; year 2019 column AA (cell AA74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 75; year 2019 column AA (cell AA75); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L313" s="32" t="n">
         <x:v>46237</x:v>
@@ -12413,7 +12413,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K314" t="str">
-        <x:v>Source sheet "1"; source row 46; year 2019 column AA (cell AA46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2019 column AA (cell AA47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L314" s="32" t="n">
         <x:v>46237</x:v>
@@ -12451,7 +12451,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K315" t="str">
-        <x:v>Source sheet "1"; source row 47; year 2019 column AA (cell AA47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2019 column AA (cell AA48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L315" s="32" t="n">
         <x:v>46237</x:v>
@@ -12489,7 +12489,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K316" t="str">
-        <x:v>Source sheet "1"; source row 48; year 2019 column AA (cell AA48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2019 column AA (cell AA49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L316" s="32" t="n">
         <x:v>46237</x:v>
@@ -12527,7 +12527,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K317" t="str">
-        <x:v>Source sheet "1"; source row 49; year 2019 column AA (cell AA49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 50; year 2019 column AA (cell AA50); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L317" s="32" t="n">
         <x:v>46237</x:v>
@@ -12565,7 +12565,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K318" t="str">
-        <x:v>Source sheet "1"; source row 52; year 2019 column AA (cell AA52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2019 column AA (cell AA53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L318" s="32" t="n">
         <x:v>46237</x:v>
@@ -12603,7 +12603,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K319" t="str">
-        <x:v>Source sheet "1"; source row 53; year 2019 column AA (cell AA53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2019 column AA (cell AA54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L319" s="32" t="n">
         <x:v>46237</x:v>
@@ -12641,7 +12641,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K320" t="str">
-        <x:v>Source sheet "1"; source row 54; year 2019 column AA (cell AA54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2019 column AA (cell AA55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L320" s="32" t="n">
         <x:v>46237</x:v>
@@ -12679,7 +12679,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K321" t="str">
-        <x:v>Source sheet "1"; source row 55; year 2019 column AA (cell AA55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 56; year 2019 column AA (cell AA56); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L321" s="32" t="n">
         <x:v>46237</x:v>
@@ -12717,7 +12717,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K322" t="str">
-        <x:v>Source sheet "1"; source row 5; year 2020 column AB (cell AB5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 6; year 2020 column AB (cell AB6); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L322" s="32" t="n">
         <x:v>46237</x:v>
@@ -12755,7 +12755,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K323" t="str">
-        <x:v>Source sheet "1"; source row 9; year 2020 column AB (cell AB9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2020 column AB (cell AB10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L323" s="32" t="n">
         <x:v>46237</x:v>
@@ -12793,7 +12793,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K324" t="str">
-        <x:v>Source sheet "1"; source row 11; year 2020 column AB (cell AB11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2020 column AB (cell AB12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L324" s="32" t="n">
         <x:v>46237</x:v>
@@ -12831,7 +12831,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K325" t="str">
-        <x:v>Source sheet "1"; source row 13; year 2020 column AB (cell AB13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2020 column AB (cell AB14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L325" s="32" t="n">
         <x:v>46237</x:v>
@@ -12869,7 +12869,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K326" t="str">
-        <x:v>Source sheet "1"; source row 10; year 2020 column AB (cell AB10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2020 column AB (cell AB11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L326" s="32" t="n">
         <x:v>46237</x:v>
@@ -12907,7 +12907,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K327" t="str">
-        <x:v>Source sheet "1"; source row 12; year 2020 column AB (cell AB12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2020 column AB (cell AB13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L327" s="32" t="n">
         <x:v>46237</x:v>
@@ -12945,7 +12945,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K328" t="str">
-        <x:v>Source sheet "1"; source row 14; year 2020 column AB (cell AB14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 15; year 2020 column AB (cell AB15); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L328" s="32" t="n">
         <x:v>46237</x:v>
@@ -12983,7 +12983,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K329" t="str">
-        <x:v>Source sheet "1"; source row 35; year 2020 column AB (cell AB35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2020 column AB (cell AB36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L329" s="32" t="n">
         <x:v>46237</x:v>
@@ -13021,7 +13021,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K330" t="str">
-        <x:v>Source sheet "1"; source row 36; year 2020 column AB (cell AB36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2020 column AB (cell AB37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L330" s="32" t="n">
         <x:v>46237</x:v>
@@ -13059,7 +13059,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K331" t="str">
-        <x:v>Source sheet "1"; source row 37; year 2020 column AB (cell AB37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2020 column AB (cell AB38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L331" s="32" t="n">
         <x:v>46237</x:v>
@@ -13097,7 +13097,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K332" t="str">
-        <x:v>Source sheet "1"; source row 38; year 2020 column AB (cell AB38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2020 column AB (cell AB39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L332" s="32" t="n">
         <x:v>46237</x:v>
@@ -13135,7 +13135,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K333" t="str">
-        <x:v>Source sheet "1"; source row 39; year 2020 column AB (cell AB39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2020 column AB (cell AB40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L333" s="32" t="n">
         <x:v>46237</x:v>
@@ -13173,7 +13173,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K334" t="str">
-        <x:v>Source sheet "1"; source row 40; year 2020 column AB (cell AB40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2020 column AB (cell AB41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L334" s="32" t="n">
         <x:v>46237</x:v>
@@ -13211,7 +13211,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K335" t="str">
-        <x:v>Source sheet "1"; source row 41; year 2020 column AB (cell AB41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2020 column AB (cell AB42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L335" s="32" t="n">
         <x:v>46237</x:v>
@@ -13249,7 +13249,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K336" t="str">
-        <x:v>Source sheet "1"; source row 42; year 2020 column AB (cell AB42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 43; year 2020 column AB (cell AB43); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L336" s="32" t="n">
         <x:v>46237</x:v>
@@ -13287,7 +13287,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K337" t="str">
-        <x:v>Source sheet "1"; source row 21; year 2020 column AB (cell AB21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2020 column AB (cell AB22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L337" s="32" t="n">
         <x:v>46237</x:v>
@@ -13325,7 +13325,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K338" t="str">
-        <x:v>Source sheet "1"; source row 30; year 2020 column AB (cell AB30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2020 column AB (cell AB31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L338" s="32" t="n">
         <x:v>46237</x:v>
@@ -13363,7 +13363,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K339" t="str">
-        <x:v>Source sheet "1"; source row 28; year 2020 column AB (cell AB28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2020 column AB (cell AB29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L339" s="32" t="n">
         <x:v>46237</x:v>
@@ -13401,7 +13401,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K340" t="str">
-        <x:v>Source sheet "1"; source row 29; year 2020 column AB (cell AB29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2020 column AB (cell AB30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L340" s="32" t="n">
         <x:v>46237</x:v>
@@ -13439,7 +13439,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K341" t="str">
-        <x:v>Source sheet "1"; source row 22; year 2020 column AB (cell AB22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2020 column AB (cell AB23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L341" s="32" t="n">
         <x:v>46237</x:v>
@@ -13477,7 +13477,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K342" t="str">
-        <x:v>Source sheet "1"; source row 23; year 2020 column AB (cell AB23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2020 column AB (cell AB24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L342" s="32" t="n">
         <x:v>46237</x:v>
@@ -13515,7 +13515,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K343" t="str">
-        <x:v>Source sheet "1"; source row 24; year 2020 column AB (cell AB24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2020 column AB (cell AB25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L343" s="32" t="n">
         <x:v>46237</x:v>
@@ -13553,7 +13553,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K344" t="str">
-        <x:v>Source sheet "1"; source row 25; year 2020 column AB (cell AB25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2020 column AB (cell AB26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L344" s="32" t="n">
         <x:v>46237</x:v>
@@ -13591,7 +13591,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K345" t="str">
-        <x:v>Source sheet "1"; source row 26; year 2020 column AB (cell AB26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2020 column AB (cell AB27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L345" s="32" t="n">
         <x:v>46237</x:v>
@@ -13629,7 +13629,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K346" t="str">
-        <x:v>Source sheet "1"; source row 27; year 2020 column AB (cell AB27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2020 column AB (cell AB28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L346" s="32" t="n">
         <x:v>46237</x:v>
@@ -13667,7 +13667,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K347" t="str">
-        <x:v>Source sheet "1"; source row 31; year 2020 column AB (cell AB31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2020 column AB (cell AB32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L347" s="32" t="n">
         <x:v>46237</x:v>
@@ -13705,7 +13705,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K348" t="str">
-        <x:v>Source sheet "1"; source row 32; year 2020 column AB (cell AB32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 33; year 2020 column AB (cell AB33); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L348" s="32" t="n">
         <x:v>46237</x:v>
@@ -13743,7 +13743,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K349" t="str">
-        <x:v>Source sheet "1"; source row 58; year 2020 column AB (cell AB58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2020 column AB (cell AB59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L349" s="32" t="n">
         <x:v>46237</x:v>
@@ -13781,7 +13781,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K350" t="str">
-        <x:v>Source sheet "1"; source row 60; year 2020 column AB (cell AB60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2020 column AB (cell AB61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L350" s="32" t="n">
         <x:v>46237</x:v>
@@ -13819,7 +13819,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K351" t="str">
-        <x:v>Source sheet "1"; source row 59; year 2020 column AB (cell AB59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2020 column AB (cell AB60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L351" s="32" t="n">
         <x:v>46237</x:v>
@@ -13857,7 +13857,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K352" t="str">
-        <x:v>Source sheet "1"; source row 61; year 2020 column AB (cell AB61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2020 column AB (cell AB62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L352" s="32" t="n">
         <x:v>46237</x:v>
@@ -13895,7 +13895,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K353" t="str">
-        <x:v>Source sheet "1"; source row 62; year 2020 column AB (cell AB62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2020 column AB (cell AB63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L353" s="32" t="n">
         <x:v>46237</x:v>
@@ -13933,7 +13933,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K354" t="str">
-        <x:v>Source sheet "1"; source row 63; year 2020 column AB (cell AB63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2020 column AB (cell AB64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L354" s="32" t="n">
         <x:v>46237</x:v>
@@ -13971,7 +13971,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K355" t="str">
-        <x:v>Source sheet "1"; source row 64; year 2020 column AB (cell AB64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2020 column AB (cell AB65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L355" s="32" t="n">
         <x:v>46237</x:v>
@@ -14009,7 +14009,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K356" t="str">
-        <x:v>Source sheet "1"; source row 65; year 2020 column AB (cell AB65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2020 column AB (cell AB66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L356" s="32" t="n">
         <x:v>46237</x:v>
@@ -14047,7 +14047,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K357" t="str">
-        <x:v>Source sheet "1"; source row 66; year 2020 column AB (cell AB66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 67; year 2020 column AB (cell AB67); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L357" s="32" t="n">
         <x:v>46237</x:v>
@@ -14085,7 +14085,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K358" t="str">
-        <x:v>Source sheet "1"; source row 85; year 2020 column AB (cell AB85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 86; year 2020 column AB (cell AB86); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L358" s="32" t="n">
         <x:v>46237</x:v>
@@ -14123,7 +14123,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K359" t="str">
-        <x:v>Source sheet "1"; source row 89; year 2020 column AB (cell AB89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 90; year 2020 column AB (cell AB90); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L359" s="32" t="n">
         <x:v>46237</x:v>
@@ -14161,7 +14161,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K360" t="str">
-        <x:v>Source sheet "1"; source row 88; year 2020 column AB (cell AB88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2020 column AB (cell AB89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L360" s="32" t="n">
         <x:v>46237</x:v>
@@ -14199,7 +14199,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K361" t="str">
-        <x:v>Source sheet "1"; source row 91; year 2020 column AB (cell AB91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 92; year 2020 column AB (cell AB92); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L361" s="32" t="n">
         <x:v>46237</x:v>
@@ -14237,7 +14237,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K362" t="str">
-        <x:v>Source sheet "1"; source row 76; year 2020 column AB (cell AB76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2020 column AB (cell AB77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L362" s="32" t="n">
         <x:v>46237</x:v>
@@ -14275,7 +14275,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K363" t="str">
-        <x:v>Source sheet "1"; source row 77; year 2020 column AB (cell AB77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2020 column AB (cell AB78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L363" s="32" t="n">
         <x:v>46237</x:v>
@@ -14313,7 +14313,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K364" t="str">
-        <x:v>Source sheet "1"; source row 78; year 2020 column AB (cell AB78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2020 column AB (cell AB79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L364" s="32" t="n">
         <x:v>46237</x:v>
@@ -14351,7 +14351,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K365" t="str">
-        <x:v>Source sheet "1"; source row 79; year 2020 column AB (cell AB79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2020 column AB (cell AB80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L365" s="32" t="n">
         <x:v>46237</x:v>
@@ -14389,7 +14389,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K366" t="str">
-        <x:v>Source sheet "1"; source row 80; year 2020 column AB (cell AB80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2020 column AB (cell AB81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L366" s="32" t="n">
         <x:v>46237</x:v>
@@ -14427,7 +14427,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K367" t="str">
-        <x:v>Source sheet "1"; source row 81; year 2020 column AB (cell AB81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2020 column AB (cell AB82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L367" s="32" t="n">
         <x:v>46237</x:v>
@@ -14465,7 +14465,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K368" t="str">
-        <x:v>Source sheet "1"; source row 82; year 2020 column AB (cell AB82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 83; year 2020 column AB (cell AB83); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L368" s="32" t="n">
         <x:v>46237</x:v>
@@ -14503,7 +14503,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K369" t="str">
-        <x:v>Source sheet "1"; source row 17; year 2020 column AB (cell AB17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2020 column AB (cell AB18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L369" s="32" t="n">
         <x:v>46237</x:v>
@@ -14541,7 +14541,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K370" t="str">
-        <x:v>Source sheet "1"; source row 18; year 2020 column AB (cell AB18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2020 column AB (cell AB19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L370" s="32" t="n">
         <x:v>46237</x:v>
@@ -14579,7 +14579,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K371" t="str">
-        <x:v>Source sheet "1"; source row 19; year 2020 column AB (cell AB19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 20; year 2020 column AB (cell AB20); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L371" s="32" t="n">
         <x:v>46237</x:v>
@@ -14617,7 +14617,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K372" t="str">
-        <x:v>Source sheet "1"; source row 73; year 2020 column AB (cell AB73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2020 column AB (cell AB74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L372" s="32" t="n">
         <x:v>46237</x:v>
@@ -14655,7 +14655,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K373" t="str">
-        <x:v>Source sheet "1"; source row 69; year 2020 column AB (cell AB69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2020 column AB (cell AB70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L373" s="32" t="n">
         <x:v>46237</x:v>
@@ -14693,7 +14693,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K374" t="str">
-        <x:v>Source sheet "1"; source row 70; year 2020 column AB (cell AB70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2020 column AB (cell AB71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L374" s="32" t="n">
         <x:v>46237</x:v>
@@ -14731,7 +14731,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K375" t="str">
-        <x:v>Source sheet "1"; source row 71; year 2020 column AB (cell AB71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2020 column AB (cell AB72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L375" s="32" t="n">
         <x:v>46237</x:v>
@@ -14769,7 +14769,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K376" t="str">
-        <x:v>Source sheet "1"; source row 72; year 2020 column AB (cell AB72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2020 column AB (cell AB73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L376" s="32" t="n">
         <x:v>46237</x:v>
@@ -14807,7 +14807,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K377" t="str">
-        <x:v>Source sheet "1"; source row 74; year 2020 column AB (cell AB74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 75; year 2020 column AB (cell AB75); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L377" s="32" t="n">
         <x:v>46237</x:v>
@@ -14845,7 +14845,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K378" t="str">
-        <x:v>Source sheet "1"; source row 46; year 2020 column AB (cell AB46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2020 column AB (cell AB47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L378" s="32" t="n">
         <x:v>46237</x:v>
@@ -14883,7 +14883,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K379" t="str">
-        <x:v>Source sheet "1"; source row 47; year 2020 column AB (cell AB47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2020 column AB (cell AB48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L379" s="32" t="n">
         <x:v>46237</x:v>
@@ -14921,7 +14921,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K380" t="str">
-        <x:v>Source sheet "1"; source row 48; year 2020 column AB (cell AB48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2020 column AB (cell AB49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L380" s="32" t="n">
         <x:v>46237</x:v>
@@ -14959,7 +14959,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K381" t="str">
-        <x:v>Source sheet "1"; source row 49; year 2020 column AB (cell AB49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 50; year 2020 column AB (cell AB50); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L381" s="32" t="n">
         <x:v>46237</x:v>
@@ -14997,7 +14997,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K382" t="str">
-        <x:v>Source sheet "1"; source row 52; year 2020 column AB (cell AB52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2020 column AB (cell AB53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L382" s="32" t="n">
         <x:v>46237</x:v>
@@ -15035,7 +15035,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K383" t="str">
-        <x:v>Source sheet "1"; source row 53; year 2020 column AB (cell AB53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2020 column AB (cell AB54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L383" s="32" t="n">
         <x:v>46237</x:v>
@@ -15073,7 +15073,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K384" t="str">
-        <x:v>Source sheet "1"; source row 54; year 2020 column AB (cell AB54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2020 column AB (cell AB55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L384" s="32" t="n">
         <x:v>46237</x:v>
@@ -15111,7 +15111,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K385" t="str">
-        <x:v>Source sheet "1"; source row 55; year 2020 column AB (cell AB55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 56; year 2020 column AB (cell AB56); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L385" s="32" t="n">
         <x:v>46237</x:v>
@@ -15149,7 +15149,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K386" t="str">
-        <x:v>Source sheet "1"; source row 5; year 2021 column AC (cell AC5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 6; year 2021 column AC (cell AC6); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L386" s="32" t="n">
         <x:v>46237</x:v>
@@ -15187,7 +15187,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K387" t="str">
-        <x:v>Source sheet "1"; source row 9; year 2021 column AC (cell AC9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2021 column AC (cell AC10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L387" s="32" t="n">
         <x:v>46237</x:v>
@@ -15225,7 +15225,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K388" t="str">
-        <x:v>Source sheet "1"; source row 11; year 2021 column AC (cell AC11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2021 column AC (cell AC12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L388" s="32" t="n">
         <x:v>46237</x:v>
@@ -15263,7 +15263,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K389" t="str">
-        <x:v>Source sheet "1"; source row 13; year 2021 column AC (cell AC13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2021 column AC (cell AC14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L389" s="32" t="n">
         <x:v>46237</x:v>
@@ -15301,7 +15301,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K390" t="str">
-        <x:v>Source sheet "1"; source row 10; year 2021 column AC (cell AC10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2021 column AC (cell AC11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L390" s="32" t="n">
         <x:v>46237</x:v>
@@ -15339,7 +15339,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K391" t="str">
-        <x:v>Source sheet "1"; source row 12; year 2021 column AC (cell AC12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2021 column AC (cell AC13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L391" s="32" t="n">
         <x:v>46237</x:v>
@@ -15377,7 +15377,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K392" t="str">
-        <x:v>Source sheet "1"; source row 14; year 2021 column AC (cell AC14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 15; year 2021 column AC (cell AC15); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L392" s="32" t="n">
         <x:v>46237</x:v>
@@ -15415,7 +15415,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K393" t="str">
-        <x:v>Source sheet "1"; source row 35; year 2021 column AC (cell AC35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2021 column AC (cell AC36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L393" s="32" t="n">
         <x:v>46237</x:v>
@@ -15453,7 +15453,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K394" t="str">
-        <x:v>Source sheet "1"; source row 36; year 2021 column AC (cell AC36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2021 column AC (cell AC37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L394" s="32" t="n">
         <x:v>46237</x:v>
@@ -15491,7 +15491,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K395" t="str">
-        <x:v>Source sheet "1"; source row 37; year 2021 column AC (cell AC37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2021 column AC (cell AC38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L395" s="32" t="n">
         <x:v>46237</x:v>
@@ -15529,7 +15529,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K396" t="str">
-        <x:v>Source sheet "1"; source row 38; year 2021 column AC (cell AC38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2021 column AC (cell AC39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L396" s="32" t="n">
         <x:v>46237</x:v>
@@ -15567,7 +15567,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K397" t="str">
-        <x:v>Source sheet "1"; source row 39; year 2021 column AC (cell AC39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2021 column AC (cell AC40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L397" s="32" t="n">
         <x:v>46237</x:v>
@@ -15605,7 +15605,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K398" t="str">
-        <x:v>Source sheet "1"; source row 40; year 2021 column AC (cell AC40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2021 column AC (cell AC41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L398" s="32" t="n">
         <x:v>46237</x:v>
@@ -15643,7 +15643,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K399" t="str">
-        <x:v>Source sheet "1"; source row 41; year 2021 column AC (cell AC41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2021 column AC (cell AC42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L399" s="32" t="n">
         <x:v>46237</x:v>
@@ -15681,7 +15681,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K400" t="str">
-        <x:v>Source sheet "1"; source row 42; year 2021 column AC (cell AC42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 43; year 2021 column AC (cell AC43); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L400" s="32" t="n">
         <x:v>46237</x:v>
@@ -15719,7 +15719,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K401" t="str">
-        <x:v>Source sheet "1"; source row 21; year 2021 column AC (cell AC21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2021 column AC (cell AC22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L401" s="32" t="n">
         <x:v>46237</x:v>
@@ -15757,7 +15757,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K402" t="str">
-        <x:v>Source sheet "1"; source row 30; year 2021 column AC (cell AC30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2021 column AC (cell AC31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L402" s="32" t="n">
         <x:v>46237</x:v>
@@ -15795,7 +15795,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K403" t="str">
-        <x:v>Source sheet "1"; source row 28; year 2021 column AC (cell AC28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2021 column AC (cell AC29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L403" s="32" t="n">
         <x:v>46237</x:v>
@@ -15833,7 +15833,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K404" t="str">
-        <x:v>Source sheet "1"; source row 29; year 2021 column AC (cell AC29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2021 column AC (cell AC30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L404" s="32" t="n">
         <x:v>46237</x:v>
@@ -15871,7 +15871,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K405" t="str">
-        <x:v>Source sheet "1"; source row 22; year 2021 column AC (cell AC22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2021 column AC (cell AC23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L405" s="32" t="n">
         <x:v>46237</x:v>
@@ -15909,7 +15909,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K406" t="str">
-        <x:v>Source sheet "1"; source row 23; year 2021 column AC (cell AC23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2021 column AC (cell AC24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L406" s="32" t="n">
         <x:v>46237</x:v>
@@ -15947,7 +15947,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K407" t="str">
-        <x:v>Source sheet "1"; source row 24; year 2021 column AC (cell AC24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2021 column AC (cell AC25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L407" s="32" t="n">
         <x:v>46237</x:v>
@@ -15985,7 +15985,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K408" t="str">
-        <x:v>Source sheet "1"; source row 25; year 2021 column AC (cell AC25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2021 column AC (cell AC26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L408" s="32" t="n">
         <x:v>46237</x:v>
@@ -16023,7 +16023,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K409" t="str">
-        <x:v>Source sheet "1"; source row 26; year 2021 column AC (cell AC26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2021 column AC (cell AC27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L409" s="32" t="n">
         <x:v>46237</x:v>
@@ -16061,7 +16061,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K410" t="str">
-        <x:v>Source sheet "1"; source row 27; year 2021 column AC (cell AC27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2021 column AC (cell AC28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L410" s="32" t="n">
         <x:v>46237</x:v>
@@ -16099,7 +16099,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K411" t="str">
-        <x:v>Source sheet "1"; source row 31; year 2021 column AC (cell AC31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2021 column AC (cell AC32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L411" s="32" t="n">
         <x:v>46237</x:v>
@@ -16137,7 +16137,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K412" t="str">
-        <x:v>Source sheet "1"; source row 32; year 2021 column AC (cell AC32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 33; year 2021 column AC (cell AC33); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L412" s="32" t="n">
         <x:v>46237</x:v>
@@ -16175,7 +16175,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K413" t="str">
-        <x:v>Source sheet "1"; source row 58; year 2021 column AC (cell AC58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2021 column AC (cell AC59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L413" s="32" t="n">
         <x:v>46237</x:v>
@@ -16213,7 +16213,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K414" t="str">
-        <x:v>Source sheet "1"; source row 60; year 2021 column AC (cell AC60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2021 column AC (cell AC61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L414" s="32" t="n">
         <x:v>46237</x:v>
@@ -16251,7 +16251,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K415" t="str">
-        <x:v>Source sheet "1"; source row 59; year 2021 column AC (cell AC59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2021 column AC (cell AC60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L415" s="32" t="n">
         <x:v>46237</x:v>
@@ -16289,7 +16289,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K416" t="str">
-        <x:v>Source sheet "1"; source row 61; year 2021 column AC (cell AC61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2021 column AC (cell AC62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L416" s="32" t="n">
         <x:v>46237</x:v>
@@ -16327,7 +16327,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K417" t="str">
-        <x:v>Source sheet "1"; source row 62; year 2021 column AC (cell AC62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2021 column AC (cell AC63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L417" s="32" t="n">
         <x:v>46237</x:v>
@@ -16365,7 +16365,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K418" t="str">
-        <x:v>Source sheet "1"; source row 63; year 2021 column AC (cell AC63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2021 column AC (cell AC64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L418" s="32" t="n">
         <x:v>46237</x:v>
@@ -16403,7 +16403,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K419" t="str">
-        <x:v>Source sheet "1"; source row 64; year 2021 column AC (cell AC64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2021 column AC (cell AC65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L419" s="32" t="n">
         <x:v>46237</x:v>
@@ -16441,7 +16441,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K420" t="str">
-        <x:v>Source sheet "1"; source row 65; year 2021 column AC (cell AC65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2021 column AC (cell AC66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L420" s="32" t="n">
         <x:v>46237</x:v>
@@ -16479,7 +16479,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K421" t="str">
-        <x:v>Source sheet "1"; source row 66; year 2021 column AC (cell AC66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 67; year 2021 column AC (cell AC67); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L421" s="32" t="n">
         <x:v>46237</x:v>
@@ -16517,7 +16517,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K422" t="str">
-        <x:v>Source sheet "1"; source row 85; year 2021 column AC (cell AC85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 86; year 2021 column AC (cell AC86); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L422" s="32" t="n">
         <x:v>46237</x:v>
@@ -16555,7 +16555,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K423" t="str">
-        <x:v>Source sheet "1"; source row 89; year 2021 column AC (cell AC89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 90; year 2021 column AC (cell AC90); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L423" s="32" t="n">
         <x:v>46237</x:v>
@@ -16593,7 +16593,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K424" t="str">
-        <x:v>Source sheet "1"; source row 88; year 2021 column AC (cell AC88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2021 column AC (cell AC89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L424" s="32" t="n">
         <x:v>46237</x:v>
@@ -16631,7 +16631,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K425" t="str">
-        <x:v>Source sheet "1"; source row 91; year 2021 column AC (cell AC91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 92; year 2021 column AC (cell AC92); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L425" s="32" t="n">
         <x:v>46237</x:v>
@@ -16669,7 +16669,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K426" t="str">
-        <x:v>Source sheet "1"; source row 76; year 2021 column AC (cell AC76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2021 column AC (cell AC77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L426" s="32" t="n">
         <x:v>46237</x:v>
@@ -16707,7 +16707,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K427" t="str">
-        <x:v>Source sheet "1"; source row 77; year 2021 column AC (cell AC77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2021 column AC (cell AC78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L427" s="32" t="n">
         <x:v>46237</x:v>
@@ -16745,7 +16745,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K428" t="str">
-        <x:v>Source sheet "1"; source row 78; year 2021 column AC (cell AC78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2021 column AC (cell AC79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L428" s="32" t="n">
         <x:v>46237</x:v>
@@ -16783,7 +16783,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K429" t="str">
-        <x:v>Source sheet "1"; source row 79; year 2021 column AC (cell AC79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2021 column AC (cell AC80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L429" s="32" t="n">
         <x:v>46237</x:v>
@@ -16821,7 +16821,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K430" t="str">
-        <x:v>Source sheet "1"; source row 80; year 2021 column AC (cell AC80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2021 column AC (cell AC81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L430" s="32" t="n">
         <x:v>46237</x:v>
@@ -16859,7 +16859,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K431" t="str">
-        <x:v>Source sheet "1"; source row 81; year 2021 column AC (cell AC81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2021 column AC (cell AC82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L431" s="32" t="n">
         <x:v>46237</x:v>
@@ -16897,7 +16897,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K432" t="str">
-        <x:v>Source sheet "1"; source row 82; year 2021 column AC (cell AC82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 83; year 2021 column AC (cell AC83); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L432" s="32" t="n">
         <x:v>46237</x:v>
@@ -16935,7 +16935,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K433" t="str">
-        <x:v>Source sheet "1"; source row 17; year 2021 column AC (cell AC17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2021 column AC (cell AC18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L433" s="32" t="n">
         <x:v>46237</x:v>
@@ -16973,7 +16973,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K434" t="str">
-        <x:v>Source sheet "1"; source row 18; year 2021 column AC (cell AC18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2021 column AC (cell AC19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L434" s="32" t="n">
         <x:v>46237</x:v>
@@ -17011,7 +17011,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K435" t="str">
-        <x:v>Source sheet "1"; source row 19; year 2021 column AC (cell AC19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 20; year 2021 column AC (cell AC20); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L435" s="32" t="n">
         <x:v>46237</x:v>
@@ -17049,7 +17049,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K436" t="str">
-        <x:v>Source sheet "1"; source row 73; year 2021 column AC (cell AC73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2021 column AC (cell AC74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L436" s="32" t="n">
         <x:v>46237</x:v>
@@ -17087,7 +17087,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K437" t="str">
-        <x:v>Source sheet "1"; source row 69; year 2021 column AC (cell AC69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2021 column AC (cell AC70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L437" s="32" t="n">
         <x:v>46237</x:v>
@@ -17125,7 +17125,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K438" t="str">
-        <x:v>Source sheet "1"; source row 70; year 2021 column AC (cell AC70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2021 column AC (cell AC71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L438" s="32" t="n">
         <x:v>46237</x:v>
@@ -17163,7 +17163,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K439" t="str">
-        <x:v>Source sheet "1"; source row 71; year 2021 column AC (cell AC71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2021 column AC (cell AC72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L439" s="32" t="n">
         <x:v>46237</x:v>
@@ -17201,7 +17201,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K440" t="str">
-        <x:v>Source sheet "1"; source row 72; year 2021 column AC (cell AC72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2021 column AC (cell AC73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L440" s="32" t="n">
         <x:v>46237</x:v>
@@ -17239,7 +17239,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K441" t="str">
-        <x:v>Source sheet "1"; source row 74; year 2021 column AC (cell AC74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 75; year 2021 column AC (cell AC75); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L441" s="32" t="n">
         <x:v>46237</x:v>
@@ -17277,7 +17277,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K442" t="str">
-        <x:v>Source sheet "1"; source row 46; year 2021 column AC (cell AC46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2021 column AC (cell AC47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L442" s="32" t="n">
         <x:v>46237</x:v>
@@ -17315,7 +17315,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K443" t="str">
-        <x:v>Source sheet "1"; source row 47; year 2021 column AC (cell AC47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2021 column AC (cell AC48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L443" s="32" t="n">
         <x:v>46237</x:v>
@@ -17353,7 +17353,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K444" t="str">
-        <x:v>Source sheet "1"; source row 48; year 2021 column AC (cell AC48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2021 column AC (cell AC49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L444" s="32" t="n">
         <x:v>46237</x:v>
@@ -17391,7 +17391,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K445" t="str">
-        <x:v>Source sheet "1"; source row 49; year 2021 column AC (cell AC49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 50; year 2021 column AC (cell AC50); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L445" s="32" t="n">
         <x:v>46237</x:v>
@@ -17429,7 +17429,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K446" t="str">
-        <x:v>Source sheet "1"; source row 52; year 2021 column AC (cell AC52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2021 column AC (cell AC53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L446" s="32" t="n">
         <x:v>46237</x:v>
@@ -17467,7 +17467,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K447" t="str">
-        <x:v>Source sheet "1"; source row 53; year 2021 column AC (cell AC53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2021 column AC (cell AC54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L447" s="32" t="n">
         <x:v>46237</x:v>
@@ -17505,7 +17505,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K448" t="str">
-        <x:v>Source sheet "1"; source row 54; year 2021 column AC (cell AC54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2021 column AC (cell AC55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L448" s="32" t="n">
         <x:v>46237</x:v>
@@ -17543,7 +17543,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K449" t="str">
-        <x:v>Source sheet "1"; source row 55; year 2021 column AC (cell AC55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 56; year 2021 column AC (cell AC56); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L449" s="32" t="n">
         <x:v>46237</x:v>
@@ -17581,7 +17581,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K450" t="str">
-        <x:v>Source sheet "1"; source row 5; year 2022 column AD (cell AD5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 6; year 2022 column AD (cell AD6); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L450" s="32" t="n">
         <x:v>46237</x:v>
@@ -17619,7 +17619,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K451" t="str">
-        <x:v>Source sheet "1"; source row 9; year 2022 column AD (cell AD9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2022 column AD (cell AD10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L451" s="32" t="n">
         <x:v>46237</x:v>
@@ -17657,7 +17657,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K452" t="str">
-        <x:v>Source sheet "1"; source row 11; year 2022 column AD (cell AD11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2022 column AD (cell AD12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L452" s="32" t="n">
         <x:v>46237</x:v>
@@ -17695,7 +17695,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K453" t="str">
-        <x:v>Source sheet "1"; source row 13; year 2022 column AD (cell AD13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2022 column AD (cell AD14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L453" s="32" t="n">
         <x:v>46237</x:v>
@@ -17733,7 +17733,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K454" t="str">
-        <x:v>Source sheet "1"; source row 10; year 2022 column AD (cell AD10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2022 column AD (cell AD11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L454" s="32" t="n">
         <x:v>46237</x:v>
@@ -17771,7 +17771,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K455" t="str">
-        <x:v>Source sheet "1"; source row 12; year 2022 column AD (cell AD12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2022 column AD (cell AD13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L455" s="32" t="n">
         <x:v>46237</x:v>
@@ -17809,7 +17809,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K456" t="str">
-        <x:v>Source sheet "1"; source row 14; year 2022 column AD (cell AD14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 15; year 2022 column AD (cell AD15); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L456" s="32" t="n">
         <x:v>46237</x:v>
@@ -17847,7 +17847,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K457" t="str">
-        <x:v>Source sheet "1"; source row 35; year 2022 column AD (cell AD35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2022 column AD (cell AD36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L457" s="32" t="n">
         <x:v>46237</x:v>
@@ -17885,7 +17885,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K458" t="str">
-        <x:v>Source sheet "1"; source row 36; year 2022 column AD (cell AD36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2022 column AD (cell AD37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L458" s="32" t="n">
         <x:v>46237</x:v>
@@ -17923,7 +17923,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K459" t="str">
-        <x:v>Source sheet "1"; source row 37; year 2022 column AD (cell AD37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2022 column AD (cell AD38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L459" s="32" t="n">
         <x:v>46237</x:v>
@@ -17961,7 +17961,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K460" t="str">
-        <x:v>Source sheet "1"; source row 38; year 2022 column AD (cell AD38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2022 column AD (cell AD39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L460" s="32" t="n">
         <x:v>46237</x:v>
@@ -17999,7 +17999,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K461" t="str">
-        <x:v>Source sheet "1"; source row 39; year 2022 column AD (cell AD39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2022 column AD (cell AD40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L461" s="32" t="n">
         <x:v>46237</x:v>
@@ -18037,7 +18037,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K462" t="str">
-        <x:v>Source sheet "1"; source row 40; year 2022 column AD (cell AD40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2022 column AD (cell AD41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L462" s="32" t="n">
         <x:v>46237</x:v>
@@ -18075,7 +18075,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K463" t="str">
-        <x:v>Source sheet "1"; source row 41; year 2022 column AD (cell AD41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2022 column AD (cell AD42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L463" s="32" t="n">
         <x:v>46237</x:v>
@@ -18113,7 +18113,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K464" t="str">
-        <x:v>Source sheet "1"; source row 42; year 2022 column AD (cell AD42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 43; year 2022 column AD (cell AD43); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L464" s="32" t="n">
         <x:v>46237</x:v>
@@ -18151,7 +18151,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K465" t="str">
-        <x:v>Source sheet "1"; source row 21; year 2022 column AD (cell AD21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2022 column AD (cell AD22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L465" s="32" t="n">
         <x:v>46237</x:v>
@@ -18189,7 +18189,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K466" t="str">
-        <x:v>Source sheet "1"; source row 30; year 2022 column AD (cell AD30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2022 column AD (cell AD31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L466" s="32" t="n">
         <x:v>46237</x:v>
@@ -18227,7 +18227,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K467" t="str">
-        <x:v>Source sheet "1"; source row 28; year 2022 column AD (cell AD28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2022 column AD (cell AD29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L467" s="32" t="n">
         <x:v>46237</x:v>
@@ -18265,7 +18265,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K468" t="str">
-        <x:v>Source sheet "1"; source row 29; year 2022 column AD (cell AD29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2022 column AD (cell AD30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L468" s="32" t="n">
         <x:v>46237</x:v>
@@ -18303,7 +18303,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K469" t="str">
-        <x:v>Source sheet "1"; source row 22; year 2022 column AD (cell AD22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2022 column AD (cell AD23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L469" s="32" t="n">
         <x:v>46237</x:v>
@@ -18341,7 +18341,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K470" t="str">
-        <x:v>Source sheet "1"; source row 23; year 2022 column AD (cell AD23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2022 column AD (cell AD24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L470" s="32" t="n">
         <x:v>46237</x:v>
@@ -18379,7 +18379,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K471" t="str">
-        <x:v>Source sheet "1"; source row 24; year 2022 column AD (cell AD24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2022 column AD (cell AD25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L471" s="32" t="n">
         <x:v>46237</x:v>
@@ -18417,7 +18417,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K472" t="str">
-        <x:v>Source sheet "1"; source row 25; year 2022 column AD (cell AD25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2022 column AD (cell AD26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L472" s="32" t="n">
         <x:v>46237</x:v>
@@ -18455,7 +18455,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K473" t="str">
-        <x:v>Source sheet "1"; source row 26; year 2022 column AD (cell AD26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2022 column AD (cell AD27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L473" s="32" t="n">
         <x:v>46237</x:v>
@@ -18493,7 +18493,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K474" t="str">
-        <x:v>Source sheet "1"; source row 27; year 2022 column AD (cell AD27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2022 column AD (cell AD28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L474" s="32" t="n">
         <x:v>46237</x:v>
@@ -18531,7 +18531,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K475" t="str">
-        <x:v>Source sheet "1"; source row 31; year 2022 column AD (cell AD31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2022 column AD (cell AD32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L475" s="32" t="n">
         <x:v>46237</x:v>
@@ -18569,7 +18569,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K476" t="str">
-        <x:v>Source sheet "1"; source row 32; year 2022 column AD (cell AD32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 33; year 2022 column AD (cell AD33); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L476" s="32" t="n">
         <x:v>46237</x:v>
@@ -18607,7 +18607,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K477" t="str">
-        <x:v>Source sheet "1"; source row 58; year 2022 column AD (cell AD58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2022 column AD (cell AD59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L477" s="32" t="n">
         <x:v>46237</x:v>
@@ -18645,7 +18645,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K478" t="str">
-        <x:v>Source sheet "1"; source row 60; year 2022 column AD (cell AD60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2022 column AD (cell AD61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L478" s="32" t="n">
         <x:v>46237</x:v>
@@ -18683,7 +18683,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K479" t="str">
-        <x:v>Source sheet "1"; source row 59; year 2022 column AD (cell AD59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2022 column AD (cell AD60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L479" s="32" t="n">
         <x:v>46237</x:v>
@@ -18721,7 +18721,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K480" t="str">
-        <x:v>Source sheet "1"; source row 61; year 2022 column AD (cell AD61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2022 column AD (cell AD62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L480" s="32" t="n">
         <x:v>46237</x:v>
@@ -18759,7 +18759,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K481" t="str">
-        <x:v>Source sheet "1"; source row 62; year 2022 column AD (cell AD62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2022 column AD (cell AD63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L481" s="32" t="n">
         <x:v>46237</x:v>
@@ -18797,7 +18797,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K482" t="str">
-        <x:v>Source sheet "1"; source row 63; year 2022 column AD (cell AD63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2022 column AD (cell AD64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L482" s="32" t="n">
         <x:v>46237</x:v>
@@ -18835,7 +18835,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K483" t="str">
-        <x:v>Source sheet "1"; source row 64; year 2022 column AD (cell AD64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2022 column AD (cell AD65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L483" s="32" t="n">
         <x:v>46237</x:v>
@@ -18873,7 +18873,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K484" t="str">
-        <x:v>Source sheet "1"; source row 65; year 2022 column AD (cell AD65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2022 column AD (cell AD66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L484" s="32" t="n">
         <x:v>46237</x:v>
@@ -18911,7 +18911,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K485" t="str">
-        <x:v>Source sheet "1"; source row 66; year 2022 column AD (cell AD66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 67; year 2022 column AD (cell AD67); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L485" s="32" t="n">
         <x:v>46237</x:v>
@@ -18949,7 +18949,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K486" t="str">
-        <x:v>Source sheet "1"; source row 85; year 2022 column AD (cell AD85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 86; year 2022 column AD (cell AD86); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L486" s="32" t="n">
         <x:v>46237</x:v>
@@ -18987,7 +18987,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K487" t="str">
-        <x:v>Source sheet "1"; source row 89; year 2022 column AD (cell AD89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 90; year 2022 column AD (cell AD90); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L487" s="32" t="n">
         <x:v>46237</x:v>
@@ -19025,7 +19025,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K488" t="str">
-        <x:v>Source sheet "1"; source row 88; year 2022 column AD (cell AD88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2022 column AD (cell AD89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L488" s="32" t="n">
         <x:v>46237</x:v>
@@ -19063,7 +19063,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K489" t="str">
-        <x:v>Source sheet "1"; source row 91; year 2022 column AD (cell AD91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 92; year 2022 column AD (cell AD92); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L489" s="32" t="n">
         <x:v>46237</x:v>
@@ -19101,7 +19101,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K490" t="str">
-        <x:v>Source sheet "1"; source row 76; year 2022 column AD (cell AD76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2022 column AD (cell AD77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L490" s="32" t="n">
         <x:v>46237</x:v>
@@ -19139,7 +19139,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K491" t="str">
-        <x:v>Source sheet "1"; source row 77; year 2022 column AD (cell AD77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2022 column AD (cell AD78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L491" s="32" t="n">
         <x:v>46237</x:v>
@@ -19177,7 +19177,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K492" t="str">
-        <x:v>Source sheet "1"; source row 78; year 2022 column AD (cell AD78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2022 column AD (cell AD79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L492" s="32" t="n">
         <x:v>46237</x:v>
@@ -19215,7 +19215,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K493" t="str">
-        <x:v>Source sheet "1"; source row 79; year 2022 column AD (cell AD79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2022 column AD (cell AD80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L493" s="32" t="n">
         <x:v>46237</x:v>
@@ -19253,7 +19253,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K494" t="str">
-        <x:v>Source sheet "1"; source row 80; year 2022 column AD (cell AD80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2022 column AD (cell AD81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L494" s="32" t="n">
         <x:v>46237</x:v>
@@ -19291,7 +19291,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K495" t="str">
-        <x:v>Source sheet "1"; source row 81; year 2022 column AD (cell AD81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2022 column AD (cell AD82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L495" s="32" t="n">
         <x:v>46237</x:v>
@@ -19329,7 +19329,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K496" t="str">
-        <x:v>Source sheet "1"; source row 82; year 2022 column AD (cell AD82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 83; year 2022 column AD (cell AD83); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L496" s="32" t="n">
         <x:v>46237</x:v>
@@ -19367,7 +19367,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K497" t="str">
-        <x:v>Source sheet "1"; source row 17; year 2022 column AD (cell AD17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2022 column AD (cell AD18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L497" s="32" t="n">
         <x:v>46237</x:v>
@@ -19405,7 +19405,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K498" t="str">
-        <x:v>Source sheet "1"; source row 18; year 2022 column AD (cell AD18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2022 column AD (cell AD19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L498" s="32" t="n">
         <x:v>46237</x:v>
@@ -19443,7 +19443,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K499" t="str">
-        <x:v>Source sheet "1"; source row 19; year 2022 column AD (cell AD19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 20; year 2022 column AD (cell AD20); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L499" s="32" t="n">
         <x:v>46237</x:v>
@@ -19481,7 +19481,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K500" t="str">
-        <x:v>Source sheet "1"; source row 73; year 2022 column AD (cell AD73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2022 column AD (cell AD74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L500" s="32" t="n">
         <x:v>46237</x:v>
@@ -19519,7 +19519,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K501" t="str">
-        <x:v>Source sheet "1"; source row 69; year 2022 column AD (cell AD69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2022 column AD (cell AD70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L501" s="32" t="n">
         <x:v>46237</x:v>
@@ -19557,7 +19557,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K502" t="str">
-        <x:v>Source sheet "1"; source row 70; year 2022 column AD (cell AD70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2022 column AD (cell AD71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L502" s="32" t="n">
         <x:v>46237</x:v>
@@ -19595,7 +19595,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K503" t="str">
-        <x:v>Source sheet "1"; source row 71; year 2022 column AD (cell AD71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2022 column AD (cell AD72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L503" s="32" t="n">
         <x:v>46237</x:v>
@@ -19633,7 +19633,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K504" t="str">
-        <x:v>Source sheet "1"; source row 72; year 2022 column AD (cell AD72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2022 column AD (cell AD73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L504" s="32" t="n">
         <x:v>46237</x:v>
@@ -19671,7 +19671,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K505" t="str">
-        <x:v>Source sheet "1"; source row 74; year 2022 column AD (cell AD74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 75; year 2022 column AD (cell AD75); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L505" s="32" t="n">
         <x:v>46237</x:v>
@@ -19709,7 +19709,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K506" t="str">
-        <x:v>Source sheet "1"; source row 46; year 2022 column AD (cell AD46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2022 column AD (cell AD47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L506" s="32" t="n">
         <x:v>46237</x:v>
@@ -19747,7 +19747,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K507" t="str">
-        <x:v>Source sheet "1"; source row 47; year 2022 column AD (cell AD47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2022 column AD (cell AD48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L507" s="32" t="n">
         <x:v>46237</x:v>
@@ -19785,7 +19785,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K508" t="str">
-        <x:v>Source sheet "1"; source row 48; year 2022 column AD (cell AD48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2022 column AD (cell AD49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L508" s="32" t="n">
         <x:v>46237</x:v>
@@ -19823,7 +19823,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K509" t="str">
-        <x:v>Source sheet "1"; source row 49; year 2022 column AD (cell AD49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 50; year 2022 column AD (cell AD50); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L509" s="32" t="n">
         <x:v>46237</x:v>
@@ -19861,7 +19861,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K510" t="str">
-        <x:v>Source sheet "1"; source row 52; year 2022 column AD (cell AD52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2022 column AD (cell AD53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L510" s="32" t="n">
         <x:v>46237</x:v>
@@ -19899,7 +19899,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K511" t="str">
-        <x:v>Source sheet "1"; source row 53; year 2022 column AD (cell AD53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2022 column AD (cell AD54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L511" s="32" t="n">
         <x:v>46237</x:v>
@@ -19937,7 +19937,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K512" t="str">
-        <x:v>Source sheet "1"; source row 54; year 2022 column AD (cell AD54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2022 column AD (cell AD55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L512" s="32" t="n">
         <x:v>46237</x:v>
@@ -19975,7 +19975,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K513" t="str">
-        <x:v>Source sheet "1"; source row 55; year 2022 column AD (cell AD55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 56; year 2022 column AD (cell AD56); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L513" s="32" t="n">
         <x:v>46237</x:v>
@@ -20013,7 +20013,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K514" t="str">
-        <x:v>Source sheet "1"; source row 5; year 2023 column AE (cell AE5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 6; year 2023 column AE (cell AE6); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L514" s="32" t="n">
         <x:v>46237</x:v>
@@ -20051,7 +20051,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K515" t="str">
-        <x:v>Source sheet "1"; source row 9; year 2023 column AE (cell AE9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2023 column AE (cell AE10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L515" s="32" t="n">
         <x:v>46237</x:v>
@@ -20089,7 +20089,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K516" t="str">
-        <x:v>Source sheet "1"; source row 11; year 2023 column AE (cell AE11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2023 column AE (cell AE12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L516" s="32" t="n">
         <x:v>46237</x:v>
@@ -20127,7 +20127,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K517" t="str">
-        <x:v>Source sheet "1"; source row 13; year 2023 column AE (cell AE13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2023 column AE (cell AE14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L517" s="32" t="n">
         <x:v>46237</x:v>
@@ -20165,7 +20165,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K518" t="str">
-        <x:v>Source sheet "1"; source row 10; year 2023 column AE (cell AE10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2023 column AE (cell AE11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L518" s="32" t="n">
         <x:v>46237</x:v>
@@ -20203,7 +20203,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K519" t="str">
-        <x:v>Source sheet "1"; source row 12; year 2023 column AE (cell AE12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2023 column AE (cell AE13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L519" s="32" t="n">
         <x:v>46237</x:v>
@@ -20241,7 +20241,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K520" t="str">
-        <x:v>Source sheet "1"; source row 14; year 2023 column AE (cell AE14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 15; year 2023 column AE (cell AE15); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L520" s="32" t="n">
         <x:v>46237</x:v>
@@ -20279,7 +20279,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K521" t="str">
-        <x:v>Source sheet "1"; source row 35; year 2023 column AE (cell AE35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2023 column AE (cell AE36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L521" s="32" t="n">
         <x:v>46237</x:v>
@@ -20317,7 +20317,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K522" t="str">
-        <x:v>Source sheet "1"; source row 36; year 2023 column AE (cell AE36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2023 column AE (cell AE37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L522" s="32" t="n">
         <x:v>46237</x:v>
@@ -20355,7 +20355,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K523" t="str">
-        <x:v>Source sheet "1"; source row 37; year 2023 column AE (cell AE37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2023 column AE (cell AE38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L523" s="32" t="n">
         <x:v>46237</x:v>
@@ -20393,7 +20393,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K524" t="str">
-        <x:v>Source sheet "1"; source row 38; year 2023 column AE (cell AE38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2023 column AE (cell AE39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L524" s="32" t="n">
         <x:v>46237</x:v>
@@ -20431,7 +20431,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K525" t="str">
-        <x:v>Source sheet "1"; source row 39; year 2023 column AE (cell AE39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2023 column AE (cell AE40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L525" s="32" t="n">
         <x:v>46237</x:v>
@@ -20469,7 +20469,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K526" t="str">
-        <x:v>Source sheet "1"; source row 40; year 2023 column AE (cell AE40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2023 column AE (cell AE41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L526" s="32" t="n">
         <x:v>46237</x:v>
@@ -20507,7 +20507,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K527" t="str">
-        <x:v>Source sheet "1"; source row 41; year 2023 column AE (cell AE41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2023 column AE (cell AE42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L527" s="32" t="n">
         <x:v>46237</x:v>
@@ -20545,7 +20545,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K528" t="str">
-        <x:v>Source sheet "1"; source row 42; year 2023 column AE (cell AE42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 43; year 2023 column AE (cell AE43); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L528" s="32" t="n">
         <x:v>46237</x:v>
@@ -20583,7 +20583,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K529" t="str">
-        <x:v>Source sheet "1"; source row 21; year 2023 column AE (cell AE21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2023 column AE (cell AE22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L529" s="32" t="n">
         <x:v>46237</x:v>
@@ -20621,7 +20621,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K530" t="str">
-        <x:v>Source sheet "1"; source row 30; year 2023 column AE (cell AE30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2023 column AE (cell AE31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L530" s="32" t="n">
         <x:v>46237</x:v>
@@ -20659,7 +20659,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K531" t="str">
-        <x:v>Source sheet "1"; source row 28; year 2023 column AE (cell AE28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2023 column AE (cell AE29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L531" s="32" t="n">
         <x:v>46237</x:v>
@@ -20697,7 +20697,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K532" t="str">
-        <x:v>Source sheet "1"; source row 29; year 2023 column AE (cell AE29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2023 column AE (cell AE30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L532" s="32" t="n">
         <x:v>46237</x:v>
@@ -20735,7 +20735,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K533" t="str">
-        <x:v>Source sheet "1"; source row 22; year 2023 column AE (cell AE22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2023 column AE (cell AE23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L533" s="32" t="n">
         <x:v>46237</x:v>
@@ -20773,7 +20773,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K534" t="str">
-        <x:v>Source sheet "1"; source row 23; year 2023 column AE (cell AE23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2023 column AE (cell AE24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L534" s="32" t="n">
         <x:v>46237</x:v>
@@ -20811,7 +20811,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K535" t="str">
-        <x:v>Source sheet "1"; source row 24; year 2023 column AE (cell AE24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2023 column AE (cell AE25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L535" s="32" t="n">
         <x:v>46237</x:v>
@@ -20849,7 +20849,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K536" t="str">
-        <x:v>Source sheet "1"; source row 25; year 2023 column AE (cell AE25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2023 column AE (cell AE26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L536" s="32" t="n">
         <x:v>46237</x:v>
@@ -20887,7 +20887,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K537" t="str">
-        <x:v>Source sheet "1"; source row 26; year 2023 column AE (cell AE26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2023 column AE (cell AE27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L537" s="32" t="n">
         <x:v>46237</x:v>
@@ -20925,7 +20925,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K538" t="str">
-        <x:v>Source sheet "1"; source row 27; year 2023 column AE (cell AE27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2023 column AE (cell AE28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L538" s="32" t="n">
         <x:v>46237</x:v>
@@ -20963,7 +20963,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K539" t="str">
-        <x:v>Source sheet "1"; source row 31; year 2023 column AE (cell AE31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2023 column AE (cell AE32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L539" s="32" t="n">
         <x:v>46237</x:v>
@@ -21001,7 +21001,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K540" t="str">
-        <x:v>Source sheet "1"; source row 32; year 2023 column AE (cell AE32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 33; year 2023 column AE (cell AE33); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L540" s="32" t="n">
         <x:v>46237</x:v>
@@ -21039,7 +21039,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K541" t="str">
-        <x:v>Source sheet "1"; source row 58; year 2023 column AE (cell AE58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2023 column AE (cell AE59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L541" s="32" t="n">
         <x:v>46237</x:v>
@@ -21077,7 +21077,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K542" t="str">
-        <x:v>Source sheet "1"; source row 60; year 2023 column AE (cell AE60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2023 column AE (cell AE61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L542" s="32" t="n">
         <x:v>46237</x:v>
@@ -21115,7 +21115,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K543" t="str">
-        <x:v>Source sheet "1"; source row 59; year 2023 column AE (cell AE59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2023 column AE (cell AE60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L543" s="32" t="n">
         <x:v>46237</x:v>
@@ -21153,7 +21153,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K544" t="str">
-        <x:v>Source sheet "1"; source row 61; year 2023 column AE (cell AE61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2023 column AE (cell AE62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L544" s="32" t="n">
         <x:v>46237</x:v>
@@ -21191,7 +21191,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K545" t="str">
-        <x:v>Source sheet "1"; source row 62; year 2023 column AE (cell AE62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2023 column AE (cell AE63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L545" s="32" t="n">
         <x:v>46237</x:v>
@@ -21229,7 +21229,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K546" t="str">
-        <x:v>Source sheet "1"; source row 63; year 2023 column AE (cell AE63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2023 column AE (cell AE64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L546" s="32" t="n">
         <x:v>46237</x:v>
@@ -21267,7 +21267,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K547" t="str">
-        <x:v>Source sheet "1"; source row 64; year 2023 column AE (cell AE64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2023 column AE (cell AE65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L547" s="32" t="n">
         <x:v>46237</x:v>
@@ -21305,7 +21305,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K548" t="str">
-        <x:v>Source sheet "1"; source row 65; year 2023 column AE (cell AE65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2023 column AE (cell AE66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L548" s="32" t="n">
         <x:v>46237</x:v>
@@ -21343,7 +21343,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K549" t="str">
-        <x:v>Source sheet "1"; source row 66; year 2023 column AE (cell AE66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 67; year 2023 column AE (cell AE67); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L549" s="32" t="n">
         <x:v>46237</x:v>
@@ -21381,7 +21381,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K550" t="str">
-        <x:v>Source sheet "1"; source row 85; year 2023 column AE (cell AE85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 86; year 2023 column AE (cell AE86); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L550" s="32" t="n">
         <x:v>46237</x:v>
@@ -21419,7 +21419,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K551" t="str">
-        <x:v>Source sheet "1"; source row 89; year 2023 column AE (cell AE89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 90; year 2023 column AE (cell AE90); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L551" s="32" t="n">
         <x:v>46237</x:v>
@@ -21457,7 +21457,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K552" t="str">
-        <x:v>Source sheet "1"; source row 88; year 2023 column AE (cell AE88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2023 column AE (cell AE89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L552" s="32" t="n">
         <x:v>46237</x:v>
@@ -21495,7 +21495,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K553" t="str">
-        <x:v>Source sheet "1"; source row 91; year 2023 column AE (cell AE91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 92; year 2023 column AE (cell AE92); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L553" s="32" t="n">
         <x:v>46237</x:v>
@@ -21533,7 +21533,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K554" t="str">
-        <x:v>Source sheet "1"; source row 76; year 2023 column AE (cell AE76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2023 column AE (cell AE77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L554" s="32" t="n">
         <x:v>46237</x:v>
@@ -21571,7 +21571,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K555" t="str">
-        <x:v>Source sheet "1"; source row 77; year 2023 column AE (cell AE77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2023 column AE (cell AE78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L555" s="32" t="n">
         <x:v>46237</x:v>
@@ -21609,7 +21609,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K556" t="str">
-        <x:v>Source sheet "1"; source row 78; year 2023 column AE (cell AE78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2023 column AE (cell AE79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L556" s="32" t="n">
         <x:v>46237</x:v>
@@ -21647,7 +21647,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K557" t="str">
-        <x:v>Source sheet "1"; source row 79; year 2023 column AE (cell AE79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2023 column AE (cell AE80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L557" s="32" t="n">
         <x:v>46237</x:v>
@@ -21685,7 +21685,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K558" t="str">
-        <x:v>Source sheet "1"; source row 80; year 2023 column AE (cell AE80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2023 column AE (cell AE81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L558" s="32" t="n">
         <x:v>46237</x:v>
@@ -21723,7 +21723,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K559" t="str">
-        <x:v>Source sheet "1"; source row 81; year 2023 column AE (cell AE81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2023 column AE (cell AE82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L559" s="32" t="n">
         <x:v>46237</x:v>
@@ -21761,7 +21761,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K560" t="str">
-        <x:v>Source sheet "1"; source row 82; year 2023 column AE (cell AE82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 83; year 2023 column AE (cell AE83); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L560" s="32" t="n">
         <x:v>46237</x:v>
@@ -21799,7 +21799,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K561" t="str">
-        <x:v>Source sheet "1"; source row 17; year 2023 column AE (cell AE17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2023 column AE (cell AE18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L561" s="32" t="n">
         <x:v>46237</x:v>
@@ -21837,7 +21837,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K562" t="str">
-        <x:v>Source sheet "1"; source row 18; year 2023 column AE (cell AE18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2023 column AE (cell AE19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L562" s="32" t="n">
         <x:v>46237</x:v>
@@ -21875,7 +21875,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K563" t="str">
-        <x:v>Source sheet "1"; source row 19; year 2023 column AE (cell AE19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 20; year 2023 column AE (cell AE20); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L563" s="32" t="n">
         <x:v>46237</x:v>
@@ -21913,7 +21913,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K564" t="str">
-        <x:v>Source sheet "1"; source row 73; year 2023 column AE (cell AE73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2023 column AE (cell AE74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L564" s="32" t="n">
         <x:v>46237</x:v>
@@ -21951,7 +21951,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K565" t="str">
-        <x:v>Source sheet "1"; source row 69; year 2023 column AE (cell AE69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2023 column AE (cell AE70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L565" s="32" t="n">
         <x:v>46237</x:v>
@@ -21989,7 +21989,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K566" t="str">
-        <x:v>Source sheet "1"; source row 70; year 2023 column AE (cell AE70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2023 column AE (cell AE71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L566" s="32" t="n">
         <x:v>46237</x:v>
@@ -22027,7 +22027,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K567" t="str">
-        <x:v>Source sheet "1"; source row 71; year 2023 column AE (cell AE71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2023 column AE (cell AE72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L567" s="32" t="n">
         <x:v>46237</x:v>
@@ -22065,7 +22065,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K568" t="str">
-        <x:v>Source sheet "1"; source row 72; year 2023 column AE (cell AE72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2023 column AE (cell AE73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L568" s="32" t="n">
         <x:v>46237</x:v>
@@ -22103,7 +22103,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K569" t="str">
-        <x:v>Source sheet "1"; source row 74; year 2023 column AE (cell AE74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 75; year 2023 column AE (cell AE75); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L569" s="32" t="n">
         <x:v>46237</x:v>
@@ -22141,7 +22141,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K570" t="str">
-        <x:v>Source sheet "1"; source row 46; year 2023 column AE (cell AE46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2023 column AE (cell AE47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L570" s="32" t="n">
         <x:v>46237</x:v>
@@ -22179,7 +22179,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K571" t="str">
-        <x:v>Source sheet "1"; source row 47; year 2023 column AE (cell AE47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2023 column AE (cell AE48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L571" s="32" t="n">
         <x:v>46237</x:v>
@@ -22217,7 +22217,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K572" t="str">
-        <x:v>Source sheet "1"; source row 48; year 2023 column AE (cell AE48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2023 column AE (cell AE49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L572" s="32" t="n">
         <x:v>46237</x:v>
@@ -22255,7 +22255,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K573" t="str">
-        <x:v>Source sheet "1"; source row 49; year 2023 column AE (cell AE49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 50; year 2023 column AE (cell AE50); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L573" s="32" t="n">
         <x:v>46237</x:v>
@@ -22293,7 +22293,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K574" t="str">
-        <x:v>Source sheet "1"; source row 52; year 2023 column AE (cell AE52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2023 column AE (cell AE53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L574" s="32" t="n">
         <x:v>46237</x:v>
@@ -22331,7 +22331,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K575" t="str">
-        <x:v>Source sheet "1"; source row 53; year 2023 column AE (cell AE53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2023 column AE (cell AE54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L575" s="32" t="n">
         <x:v>46237</x:v>
@@ -22369,7 +22369,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K576" t="str">
-        <x:v>Source sheet "1"; source row 54; year 2023 column AE (cell AE54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2023 column AE (cell AE55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L576" s="32" t="n">
         <x:v>46237</x:v>
@@ -22407,7 +22407,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K577" t="str">
-        <x:v>Source sheet "1"; source row 55; year 2023 column AE (cell AE55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 56; year 2023 column AE (cell AE56); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L577" s="32" t="n">
         <x:v>46237</x:v>
@@ -22445,7 +22445,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K578" t="str">
-        <x:v>Source sheet "1"; source row 5; year 2024 column AF (cell AF5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 6; year 2024 column AF (cell AF6); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L578" s="32" t="n">
         <x:v>46237</x:v>
@@ -22483,7 +22483,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K579" t="str">
-        <x:v>Source sheet "1"; source row 9; year 2024 column AF (cell AF9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2024 column AF (cell AF10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L579" s="32" t="n">
         <x:v>46237</x:v>
@@ -22521,7 +22521,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K580" t="str">
-        <x:v>Source sheet "1"; source row 11; year 2024 column AF (cell AF11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2024 column AF (cell AF12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L580" s="32" t="n">
         <x:v>46237</x:v>
@@ -22559,7 +22559,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K581" t="str">
-        <x:v>Source sheet "1"; source row 13; year 2024 column AF (cell AF13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2024 column AF (cell AF14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L581" s="32" t="n">
         <x:v>46237</x:v>
@@ -22597,7 +22597,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K582" t="str">
-        <x:v>Source sheet "1"; source row 10; year 2024 column AF (cell AF10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2024 column AF (cell AF11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L582" s="32" t="n">
         <x:v>46237</x:v>
@@ -22635,7 +22635,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K583" t="str">
-        <x:v>Source sheet "1"; source row 12; year 2024 column AF (cell AF12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2024 column AF (cell AF13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L583" s="32" t="n">
         <x:v>46237</x:v>
@@ -22673,7 +22673,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K584" t="str">
-        <x:v>Source sheet "1"; source row 14; year 2024 column AF (cell AF14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 15; year 2024 column AF (cell AF15); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L584" s="32" t="n">
         <x:v>46237</x:v>
@@ -22711,7 +22711,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K585" t="str">
-        <x:v>Source sheet "1"; source row 35; year 2024 column AF (cell AF35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2024 column AF (cell AF36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L585" s="32" t="n">
         <x:v>46237</x:v>
@@ -22749,7 +22749,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K586" t="str">
-        <x:v>Source sheet "1"; source row 36; year 2024 column AF (cell AF36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2024 column AF (cell AF37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L586" s="32" t="n">
         <x:v>46237</x:v>
@@ -22787,7 +22787,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K587" t="str">
-        <x:v>Source sheet "1"; source row 37; year 2024 column AF (cell AF37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2024 column AF (cell AF38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L587" s="32" t="n">
         <x:v>46237</x:v>
@@ -22825,7 +22825,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K588" t="str">
-        <x:v>Source sheet "1"; source row 38; year 2024 column AF (cell AF38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2024 column AF (cell AF39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L588" s="32" t="n">
         <x:v>46237</x:v>
@@ -22863,7 +22863,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K589" t="str">
-        <x:v>Source sheet "1"; source row 39; year 2024 column AF (cell AF39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2024 column AF (cell AF40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L589" s="32" t="n">
         <x:v>46237</x:v>
@@ -22901,7 +22901,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K590" t="str">
-        <x:v>Source sheet "1"; source row 40; year 2024 column AF (cell AF40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2024 column AF (cell AF41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L590" s="32" t="n">
         <x:v>46237</x:v>
@@ -22939,7 +22939,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K591" t="str">
-        <x:v>Source sheet "1"; source row 41; year 2024 column AF (cell AF41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2024 column AF (cell AF42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L591" s="32" t="n">
         <x:v>46237</x:v>
@@ -22977,7 +22977,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K592" t="str">
-        <x:v>Source sheet "1"; source row 42; year 2024 column AF (cell AF42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 43; year 2024 column AF (cell AF43); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L592" s="32" t="n">
         <x:v>46237</x:v>
@@ -23015,7 +23015,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K593" t="str">
-        <x:v>Source sheet "1"; source row 21; year 2024 column AF (cell AF21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2024 column AF (cell AF22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L593" s="32" t="n">
         <x:v>46237</x:v>
@@ -23053,7 +23053,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K594" t="str">
-        <x:v>Source sheet "1"; source row 30; year 2024 column AF (cell AF30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2024 column AF (cell AF31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L594" s="32" t="n">
         <x:v>46237</x:v>
@@ -23091,7 +23091,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K595" t="str">
-        <x:v>Source sheet "1"; source row 28; year 2024 column AF (cell AF28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2024 column AF (cell AF29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L595" s="32" t="n">
         <x:v>46237</x:v>
@@ -23129,7 +23129,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K596" t="str">
-        <x:v>Source sheet "1"; source row 29; year 2024 column AF (cell AF29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2024 column AF (cell AF30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L596" s="32" t="n">
         <x:v>46237</x:v>
@@ -23167,7 +23167,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K597" t="str">
-        <x:v>Source sheet "1"; source row 22; year 2024 column AF (cell AF22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2024 column AF (cell AF23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L597" s="32" t="n">
         <x:v>46237</x:v>
@@ -23205,7 +23205,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K598" t="str">
-        <x:v>Source sheet "1"; source row 23; year 2024 column AF (cell AF23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2024 column AF (cell AF24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L598" s="32" t="n">
         <x:v>46237</x:v>
@@ -23243,7 +23243,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K599" t="str">
-        <x:v>Source sheet "1"; source row 24; year 2024 column AF (cell AF24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2024 column AF (cell AF25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L599" s="32" t="n">
         <x:v>46237</x:v>
@@ -23281,7 +23281,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K600" t="str">
-        <x:v>Source sheet "1"; source row 25; year 2024 column AF (cell AF25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2024 column AF (cell AF26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L600" s="32" t="n">
         <x:v>46237</x:v>
@@ -23319,7 +23319,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K601" t="str">
-        <x:v>Source sheet "1"; source row 26; year 2024 column AF (cell AF26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2024 column AF (cell AF27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L601" s="32" t="n">
         <x:v>46237</x:v>
@@ -23357,7 +23357,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K602" t="str">
-        <x:v>Source sheet "1"; source row 27; year 2024 column AF (cell AF27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2024 column AF (cell AF28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L602" s="32" t="n">
         <x:v>46237</x:v>
@@ -23395,7 +23395,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K603" t="str">
-        <x:v>Source sheet "1"; source row 31; year 2024 column AF (cell AF31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2024 column AF (cell AF32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L603" s="32" t="n">
         <x:v>46237</x:v>
@@ -23433,7 +23433,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K604" t="str">
-        <x:v>Source sheet "1"; source row 32; year 2024 column AF (cell AF32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 33; year 2024 column AF (cell AF33); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L604" s="32" t="n">
         <x:v>46237</x:v>
@@ -23471,7 +23471,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K605" t="str">
-        <x:v>Source sheet "1"; source row 58; year 2024 column AF (cell AF58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2024 column AF (cell AF59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L605" s="32" t="n">
         <x:v>46237</x:v>
@@ -23509,7 +23509,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K606" t="str">
-        <x:v>Source sheet "1"; source row 60; year 2024 column AF (cell AF60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2024 column AF (cell AF61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L606" s="32" t="n">
         <x:v>46237</x:v>
@@ -23547,7 +23547,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K607" t="str">
-        <x:v>Source sheet "1"; source row 59; year 2024 column AF (cell AF59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2024 column AF (cell AF60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L607" s="32" t="n">
         <x:v>46237</x:v>
@@ -23585,7 +23585,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K608" t="str">
-        <x:v>Source sheet "1"; source row 61; year 2024 column AF (cell AF61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2024 column AF (cell AF62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L608" s="32" t="n">
         <x:v>46237</x:v>
@@ -23623,7 +23623,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K609" t="str">
-        <x:v>Source sheet "1"; source row 62; year 2024 column AF (cell AF62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2024 column AF (cell AF63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L609" s="32" t="n">
         <x:v>46237</x:v>
@@ -23661,7 +23661,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K610" t="str">
-        <x:v>Source sheet "1"; source row 63; year 2024 column AF (cell AF63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2024 column AF (cell AF64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L610" s="32" t="n">
         <x:v>46237</x:v>
@@ -23699,7 +23699,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K611" t="str">
-        <x:v>Source sheet "1"; source row 64; year 2024 column AF (cell AF64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2024 column AF (cell AF65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L611" s="32" t="n">
         <x:v>46237</x:v>
@@ -23737,7 +23737,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K612" t="str">
-        <x:v>Source sheet "1"; source row 65; year 2024 column AF (cell AF65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2024 column AF (cell AF66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L612" s="32" t="n">
         <x:v>46237</x:v>
@@ -23775,7 +23775,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K613" t="str">
-        <x:v>Source sheet "1"; source row 66; year 2024 column AF (cell AF66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 67; year 2024 column AF (cell AF67); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L613" s="32" t="n">
         <x:v>46237</x:v>
@@ -23813,7 +23813,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K614" t="str">
-        <x:v>Source sheet "1"; source row 85; year 2024 column AF (cell AF85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 86; year 2024 column AF (cell AF86); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L614" s="32" t="n">
         <x:v>46237</x:v>
@@ -23851,7 +23851,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K615" t="str">
-        <x:v>Source sheet "1"; source row 89; year 2024 column AF (cell AF89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 90; year 2024 column AF (cell AF90); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L615" s="32" t="n">
         <x:v>46237</x:v>
@@ -23889,7 +23889,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K616" t="str">
-        <x:v>Source sheet "1"; source row 88; year 2024 column AF (cell AF88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2024 column AF (cell AF89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L616" s="32" t="n">
         <x:v>46237</x:v>
@@ -23927,7 +23927,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K617" t="str">
-        <x:v>Source sheet "1"; source row 91; year 2024 column AF (cell AF91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 92; year 2024 column AF (cell AF92); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L617" s="32" t="n">
         <x:v>46237</x:v>
@@ -23965,7 +23965,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K618" t="str">
-        <x:v>Source sheet "1"; source row 76; year 2024 column AF (cell AF76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2024 column AF (cell AF77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L618" s="32" t="n">
         <x:v>46237</x:v>
@@ -24003,7 +24003,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K619" t="str">
-        <x:v>Source sheet "1"; source row 77; year 2024 column AF (cell AF77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2024 column AF (cell AF78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L619" s="32" t="n">
         <x:v>46237</x:v>
@@ -24041,7 +24041,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K620" t="str">
-        <x:v>Source sheet "1"; source row 78; year 2024 column AF (cell AF78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2024 column AF (cell AF79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L620" s="32" t="n">
         <x:v>46237</x:v>
@@ -24079,7 +24079,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K621" t="str">
-        <x:v>Source sheet "1"; source row 79; year 2024 column AF (cell AF79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2024 column AF (cell AF80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L621" s="32" t="n">
         <x:v>46237</x:v>
@@ -24117,7 +24117,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K622" t="str">
-        <x:v>Source sheet "1"; source row 80; year 2024 column AF (cell AF80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2024 column AF (cell AF81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L622" s="32" t="n">
         <x:v>46237</x:v>
@@ -24155,7 +24155,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K623" t="str">
-        <x:v>Source sheet "1"; source row 81; year 2024 column AF (cell AF81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2024 column AF (cell AF82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L623" s="32" t="n">
         <x:v>46237</x:v>
@@ -24193,7 +24193,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K624" t="str">
-        <x:v>Source sheet "1"; source row 82; year 2024 column AF (cell AF82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 83; year 2024 column AF (cell AF83); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L624" s="32" t="n">
         <x:v>46237</x:v>
@@ -24231,7 +24231,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K625" t="str">
-        <x:v>Source sheet "1"; source row 17; year 2024 column AF (cell AF17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2024 column AF (cell AF18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L625" s="32" t="n">
         <x:v>46237</x:v>
@@ -24269,7 +24269,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K626" t="str">
-        <x:v>Source sheet "1"; source row 18; year 2024 column AF (cell AF18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2024 column AF (cell AF19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L626" s="32" t="n">
         <x:v>46237</x:v>
@@ -24307,7 +24307,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K627" t="str">
-        <x:v>Source sheet "1"; source row 19; year 2024 column AF (cell AF19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 20; year 2024 column AF (cell AF20); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L627" s="32" t="n">
         <x:v>46237</x:v>
@@ -24345,7 +24345,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K628" t="str">
-        <x:v>Source sheet "1"; source row 73; year 2024 column AF (cell AF73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2024 column AF (cell AF74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L628" s="32" t="n">
         <x:v>46237</x:v>
@@ -24383,7 +24383,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K629" t="str">
-        <x:v>Source sheet "1"; source row 69; year 2024 column AF (cell AF69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2024 column AF (cell AF70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L629" s="32" t="n">
         <x:v>46237</x:v>
@@ -24421,7 +24421,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K630" t="str">
-        <x:v>Source sheet "1"; source row 70; year 2024 column AF (cell AF70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2024 column AF (cell AF71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L630" s="32" t="n">
         <x:v>46237</x:v>
@@ -24459,7 +24459,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K631" t="str">
-        <x:v>Source sheet "1"; source row 71; year 2024 column AF (cell AF71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2024 column AF (cell AF72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L631" s="32" t="n">
         <x:v>46237</x:v>
@@ -24497,7 +24497,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K632" t="str">
-        <x:v>Source sheet "1"; source row 72; year 2024 column AF (cell AF72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2024 column AF (cell AF73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L632" s="32" t="n">
         <x:v>46237</x:v>
@@ -24535,7 +24535,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K633" t="str">
-        <x:v>Source sheet "1"; source row 74; year 2024 column AF (cell AF74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 75; year 2024 column AF (cell AF75); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L633" s="32" t="n">
         <x:v>46237</x:v>
@@ -24573,7 +24573,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K634" t="str">
-        <x:v>Source sheet "1"; source row 46; year 2024 column AF (cell AF46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2024 column AF (cell AF47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L634" s="32" t="n">
         <x:v>46237</x:v>
@@ -24611,7 +24611,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K635" t="str">
-        <x:v>Source sheet "1"; source row 47; year 2024 column AF (cell AF47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2024 column AF (cell AF48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L635" s="32" t="n">
         <x:v>46237</x:v>
@@ -24649,7 +24649,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K636" t="str">
-        <x:v>Source sheet "1"; source row 48; year 2024 column AF (cell AF48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2024 column AF (cell AF49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L636" s="32" t="n">
         <x:v>46237</x:v>
@@ -24687,7 +24687,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K637" t="str">
-        <x:v>Source sheet "1"; source row 49; year 2024 column AF (cell AF49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 50; year 2024 column AF (cell AF50); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L637" s="32" t="n">
         <x:v>46237</x:v>
@@ -24725,7 +24725,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K638" t="str">
-        <x:v>Source sheet "1"; source row 52; year 2024 column AF (cell AF52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2024 column AF (cell AF53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L638" s="32" t="n">
         <x:v>46237</x:v>
@@ -24763,7 +24763,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K639" t="str">
-        <x:v>Source sheet "1"; source row 53; year 2024 column AF (cell AF53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2024 column AF (cell AF54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L639" s="32" t="n">
         <x:v>46237</x:v>
@@ -24801,7 +24801,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K640" t="str">
-        <x:v>Source sheet "1"; source row 54; year 2024 column AF (cell AF54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2024 column AF (cell AF55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L640" s="32" t="n">
         <x:v>46237</x:v>
@@ -24839,7 +24839,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K641" t="str">
-        <x:v>Source sheet "1"; source row 55; year 2024 column AF (cell AF55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 56; year 2024 column AF (cell AF56); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L641" s="32" t="n">
         <x:v>46237</x:v>
@@ -24877,7 +24877,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K642" t="str">
-        <x:v>Source sheet "1"; source row 5; year 2025 column AG (cell AG5); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 6; year 2025 column AG (cell AG6); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L642" s="32" t="n">
         <x:v>46237</x:v>
@@ -24915,7 +24915,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K643" t="str">
-        <x:v>Source sheet "1"; source row 9; year 2025 column AG (cell AG9); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 10; year 2025 column AG (cell AG10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L643" s="32" t="n">
         <x:v>46237</x:v>
@@ -24953,7 +24953,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K644" t="str">
-        <x:v>Source sheet "1"; source row 11; year 2025 column AG (cell AG11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 12; year 2025 column AG (cell AG12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L644" s="32" t="n">
         <x:v>46237</x:v>
@@ -24991,7 +24991,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K645" t="str">
-        <x:v>Source sheet "1"; source row 13; year 2025 column AG (cell AG13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 14; year 2025 column AG (cell AG14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L645" s="32" t="n">
         <x:v>46237</x:v>
@@ -25029,7 +25029,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K646" t="str">
-        <x:v>Source sheet "1"; source row 10; year 2025 column AG (cell AG10); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 11; year 2025 column AG (cell AG11); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L646" s="32" t="n">
         <x:v>46237</x:v>
@@ -25067,7 +25067,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K647" t="str">
-        <x:v>Source sheet "1"; source row 12; year 2025 column AG (cell AG12); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 13; year 2025 column AG (cell AG13); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L647" s="32" t="n">
         <x:v>46237</x:v>
@@ -25105,7 +25105,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K648" t="str">
-        <x:v>Source sheet "1"; source row 14; year 2025 column AG (cell AG14); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 15; year 2025 column AG (cell AG15); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L648" s="32" t="n">
         <x:v>46237</x:v>
@@ -25143,7 +25143,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K649" t="str">
-        <x:v>Source sheet "1"; source row 35; year 2025 column AG (cell AG35); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 36; year 2025 column AG (cell AG36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L649" s="32" t="n">
         <x:v>46237</x:v>
@@ -25181,7 +25181,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K650" t="str">
-        <x:v>Source sheet "1"; source row 36; year 2025 column AG (cell AG36); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 37; year 2025 column AG (cell AG37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L650" s="32" t="n">
         <x:v>46237</x:v>
@@ -25219,7 +25219,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K651" t="str">
-        <x:v>Source sheet "1"; source row 37; year 2025 column AG (cell AG37); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 38; year 2025 column AG (cell AG38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L651" s="32" t="n">
         <x:v>46237</x:v>
@@ -25257,7 +25257,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K652" t="str">
-        <x:v>Source sheet "1"; source row 38; year 2025 column AG (cell AG38); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 39; year 2025 column AG (cell AG39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L652" s="32" t="n">
         <x:v>46237</x:v>
@@ -25295,7 +25295,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K653" t="str">
-        <x:v>Source sheet "1"; source row 39; year 2025 column AG (cell AG39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 40; year 2025 column AG (cell AG40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L653" s="32" t="n">
         <x:v>46237</x:v>
@@ -25333,7 +25333,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K654" t="str">
-        <x:v>Source sheet "1"; source row 40; year 2025 column AG (cell AG40); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 41; year 2025 column AG (cell AG41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L654" s="32" t="n">
         <x:v>46237</x:v>
@@ -25371,7 +25371,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K655" t="str">
-        <x:v>Source sheet "1"; source row 41; year 2025 column AG (cell AG41); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 42; year 2025 column AG (cell AG42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L655" s="32" t="n">
         <x:v>46237</x:v>
@@ -25409,7 +25409,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K656" t="str">
-        <x:v>Source sheet "1"; source row 42; year 2025 column AG (cell AG42); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 43; year 2025 column AG (cell AG43); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L656" s="32" t="n">
         <x:v>46237</x:v>
@@ -25447,7 +25447,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K657" t="str">
-        <x:v>Source sheet "1"; source row 21; year 2025 column AG (cell AG21); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 22; year 2025 column AG (cell AG22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L657" s="32" t="n">
         <x:v>46237</x:v>
@@ -25485,7 +25485,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K658" t="str">
-        <x:v>Source sheet "1"; source row 30; year 2025 column AG (cell AG30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 31; year 2025 column AG (cell AG31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L658" s="32" t="n">
         <x:v>46237</x:v>
@@ -25523,7 +25523,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K659" t="str">
-        <x:v>Source sheet "1"; source row 28; year 2025 column AG (cell AG28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 29; year 2025 column AG (cell AG29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L659" s="32" t="n">
         <x:v>46237</x:v>
@@ -25561,7 +25561,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K660" t="str">
-        <x:v>Source sheet "1"; source row 29; year 2025 column AG (cell AG29); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 30; year 2025 column AG (cell AG30); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L660" s="32" t="n">
         <x:v>46237</x:v>
@@ -25599,7 +25599,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K661" t="str">
-        <x:v>Source sheet "1"; source row 22; year 2025 column AG (cell AG22); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 23; year 2025 column AG (cell AG23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L661" s="32" t="n">
         <x:v>46237</x:v>
@@ -25637,7 +25637,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K662" t="str">
-        <x:v>Source sheet "1"; source row 23; year 2025 column AG (cell AG23); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 24; year 2025 column AG (cell AG24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L662" s="32" t="n">
         <x:v>46237</x:v>
@@ -25675,7 +25675,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K663" t="str">
-        <x:v>Source sheet "1"; source row 24; year 2025 column AG (cell AG24); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 25; year 2025 column AG (cell AG25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L663" s="32" t="n">
         <x:v>46237</x:v>
@@ -25713,7 +25713,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K664" t="str">
-        <x:v>Source sheet "1"; source row 25; year 2025 column AG (cell AG25); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 26; year 2025 column AG (cell AG26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L664" s="32" t="n">
         <x:v>46237</x:v>
@@ -25751,7 +25751,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K665" t="str">
-        <x:v>Source sheet "1"; source row 26; year 2025 column AG (cell AG26); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 27; year 2025 column AG (cell AG27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L665" s="32" t="n">
         <x:v>46237</x:v>
@@ -25789,7 +25789,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K666" t="str">
-        <x:v>Source sheet "1"; source row 27; year 2025 column AG (cell AG27); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 28; year 2025 column AG (cell AG28); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L666" s="32" t="n">
         <x:v>46237</x:v>
@@ -25827,7 +25827,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K667" t="str">
-        <x:v>Source sheet "1"; source row 31; year 2025 column AG (cell AG31); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 32; year 2025 column AG (cell AG32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L667" s="32" t="n">
         <x:v>46237</x:v>
@@ -25865,7 +25865,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K668" t="str">
-        <x:v>Source sheet "1"; source row 32; year 2025 column AG (cell AG32); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 33; year 2025 column AG (cell AG33); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L668" s="32" t="n">
         <x:v>46237</x:v>
@@ -25903,7 +25903,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K669" t="str">
-        <x:v>Source sheet "1"; source row 58; year 2025 column AG (cell AG58); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 59; year 2025 column AG (cell AG59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L669" s="32" t="n">
         <x:v>46237</x:v>
@@ -25941,7 +25941,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K670" t="str">
-        <x:v>Source sheet "1"; source row 60; year 2025 column AG (cell AG60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 61; year 2025 column AG (cell AG61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L670" s="32" t="n">
         <x:v>46237</x:v>
@@ -25979,7 +25979,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K671" t="str">
-        <x:v>Source sheet "1"; source row 59; year 2025 column AG (cell AG59); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 60; year 2025 column AG (cell AG60); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L671" s="32" t="n">
         <x:v>46237</x:v>
@@ -26017,7 +26017,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K672" t="str">
-        <x:v>Source sheet "1"; source row 61; year 2025 column AG (cell AG61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 62; year 2025 column AG (cell AG62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L672" s="32" t="n">
         <x:v>46237</x:v>
@@ -26055,7 +26055,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K673" t="str">
-        <x:v>Source sheet "1"; source row 62; year 2025 column AG (cell AG62); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 63; year 2025 column AG (cell AG63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L673" s="32" t="n">
         <x:v>46237</x:v>
@@ -26093,7 +26093,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K674" t="str">
-        <x:v>Source sheet "1"; source row 63; year 2025 column AG (cell AG63); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 64; year 2025 column AG (cell AG64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L674" s="32" t="n">
         <x:v>46237</x:v>
@@ -26131,7 +26131,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K675" t="str">
-        <x:v>Source sheet "1"; source row 64; year 2025 column AG (cell AG64); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 65; year 2025 column AG (cell AG65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L675" s="32" t="n">
         <x:v>46237</x:v>
@@ -26169,7 +26169,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K676" t="str">
-        <x:v>Source sheet "1"; source row 65; year 2025 column AG (cell AG65); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 66; year 2025 column AG (cell AG66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L676" s="32" t="n">
         <x:v>46237</x:v>
@@ -26207,7 +26207,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K677" t="str">
-        <x:v>Source sheet "1"; source row 66; year 2025 column AG (cell AG66); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 67; year 2025 column AG (cell AG67); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L677" s="32" t="n">
         <x:v>46237</x:v>
@@ -26245,7 +26245,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K678" t="str">
-        <x:v>Source sheet "1"; source row 85; year 2025 column AG (cell AG85); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 86; year 2025 column AG (cell AG86); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L678" s="32" t="n">
         <x:v>46237</x:v>
@@ -26283,7 +26283,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K679" t="str">
-        <x:v>Source sheet "1"; source row 89; year 2025 column AG (cell AG89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 90; year 2025 column AG (cell AG90); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L679" s="32" t="n">
         <x:v>46237</x:v>
@@ -26321,7 +26321,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K680" t="str">
-        <x:v>Source sheet "1"; source row 88; year 2025 column AG (cell AG88); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 89; year 2025 column AG (cell AG89); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L680" s="32" t="n">
         <x:v>46237</x:v>
@@ -26359,7 +26359,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K681" t="str">
-        <x:v>Source sheet "1"; source row 91; year 2025 column AG (cell AG91); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 92; year 2025 column AG (cell AG92); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L681" s="32" t="n">
         <x:v>46237</x:v>
@@ -26397,7 +26397,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K682" t="str">
-        <x:v>Source sheet "1"; source row 76; year 2025 column AG (cell AG76); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 77; year 2025 column AG (cell AG77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L682" s="32" t="n">
         <x:v>46237</x:v>
@@ -26435,7 +26435,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K683" t="str">
-        <x:v>Source sheet "1"; source row 77; year 2025 column AG (cell AG77); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 78; year 2025 column AG (cell AG78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L683" s="32" t="n">
         <x:v>46237</x:v>
@@ -26473,7 +26473,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K684" t="str">
-        <x:v>Source sheet "1"; source row 78; year 2025 column AG (cell AG78); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 79; year 2025 column AG (cell AG79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L684" s="32" t="n">
         <x:v>46237</x:v>
@@ -26511,7 +26511,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K685" t="str">
-        <x:v>Source sheet "1"; source row 79; year 2025 column AG (cell AG79); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 80; year 2025 column AG (cell AG80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L685" s="32" t="n">
         <x:v>46237</x:v>
@@ -26549,7 +26549,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K686" t="str">
-        <x:v>Source sheet "1"; source row 80; year 2025 column AG (cell AG80); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 81; year 2025 column AG (cell AG81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L686" s="32" t="n">
         <x:v>46237</x:v>
@@ -26587,7 +26587,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K687" t="str">
-        <x:v>Source sheet "1"; source row 81; year 2025 column AG (cell AG81); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 82; year 2025 column AG (cell AG82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L687" s="32" t="n">
         <x:v>46237</x:v>
@@ -26625,7 +26625,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K688" t="str">
-        <x:v>Source sheet "1"; source row 82; year 2025 column AG (cell AG82); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 83; year 2025 column AG (cell AG83); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L688" s="32" t="n">
         <x:v>46237</x:v>
@@ -26663,7 +26663,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K689" t="str">
-        <x:v>Source sheet "1"; source row 17; year 2025 column AG (cell AG17); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 18; year 2025 column AG (cell AG18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L689" s="32" t="n">
         <x:v>46237</x:v>
@@ -26701,7 +26701,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K690" t="str">
-        <x:v>Source sheet "1"; source row 18; year 2025 column AG (cell AG18); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 19; year 2025 column AG (cell AG19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L690" s="32" t="n">
         <x:v>46237</x:v>
@@ -26739,7 +26739,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K691" t="str">
-        <x:v>Source sheet "1"; source row 19; year 2025 column AG (cell AG19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 20; year 2025 column AG (cell AG20); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L691" s="32" t="n">
         <x:v>46237</x:v>
@@ -26777,7 +26777,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K692" t="str">
-        <x:v>Source sheet "1"; source row 73; year 2025 column AG (cell AG73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 74; year 2025 column AG (cell AG74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L692" s="32" t="n">
         <x:v>46237</x:v>
@@ -26815,7 +26815,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K693" t="str">
-        <x:v>Source sheet "1"; source row 69; year 2025 column AG (cell AG69); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 70; year 2025 column AG (cell AG70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L693" s="32" t="n">
         <x:v>46237</x:v>
@@ -26853,7 +26853,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K694" t="str">
-        <x:v>Source sheet "1"; source row 70; year 2025 column AG (cell AG70); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 71; year 2025 column AG (cell AG71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L694" s="32" t="n">
         <x:v>46237</x:v>
@@ -26891,7 +26891,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K695" t="str">
-        <x:v>Source sheet "1"; source row 71; year 2025 column AG (cell AG71); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 72; year 2025 column AG (cell AG72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L695" s="32" t="n">
         <x:v>46237</x:v>
@@ -26929,7 +26929,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K696" t="str">
-        <x:v>Source sheet "1"; source row 72; year 2025 column AG (cell AG72); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 73; year 2025 column AG (cell AG73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L696" s="32" t="n">
         <x:v>46237</x:v>
@@ -26967,7 +26967,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K697" t="str">
-        <x:v>Source sheet "1"; source row 74; year 2025 column AG (cell AG74); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 75; year 2025 column AG (cell AG75); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L697" s="32" t="n">
         <x:v>46237</x:v>
@@ -27005,7 +27005,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K698" t="str">
-        <x:v>Source sheet "1"; source row 46; year 2025 column AG (cell AG46); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 47; year 2025 column AG (cell AG47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L698" s="32" t="n">
         <x:v>46237</x:v>
@@ -27043,7 +27043,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K699" t="str">
-        <x:v>Source sheet "1"; source row 47; year 2025 column AG (cell AG47); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 48; year 2025 column AG (cell AG48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L699" s="32" t="n">
         <x:v>46237</x:v>
@@ -27081,7 +27081,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K700" t="str">
-        <x:v>Source sheet "1"; source row 48; year 2025 column AG (cell AG48); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 49; year 2025 column AG (cell AG49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L700" s="32" t="n">
         <x:v>46237</x:v>
@@ -27119,7 +27119,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K701" t="str">
-        <x:v>Source sheet "1"; source row 49; year 2025 column AG (cell AG49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 50; year 2025 column AG (cell AG50); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L701" s="32" t="n">
         <x:v>46237</x:v>
@@ -27157,7 +27157,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K702" t="str">
-        <x:v>Source sheet "1"; source row 52; year 2025 column AG (cell AG52); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 53; year 2025 column AG (cell AG53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L702" s="32" t="n">
         <x:v>46237</x:v>
@@ -27195,7 +27195,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K703" t="str">
-        <x:v>Source sheet "1"; source row 53; year 2025 column AG (cell AG53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 54; year 2025 column AG (cell AG54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L703" s="32" t="n">
         <x:v>46237</x:v>
@@ -27233,7 +27233,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K704" t="str">
-        <x:v>Source sheet "1"; source row 54; year 2025 column AG (cell AG54); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 55; year 2025 column AG (cell AG55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L704" s="32" t="n">
         <x:v>46237</x:v>
@@ -27271,7 +27271,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K705" t="str">
-        <x:v>Source sheet "1"; source row 55; year 2025 column AG (cell AG55); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source row 56; year 2025 column AG (cell AG56); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L705" s="32" t="n">
         <x:v>46237</x:v>

--- a/docs/Raw Data/Municipalities/geostat-population-regional-gdp/municipal-population-and-regional-gdp.xlsx
+++ b/docs/Raw Data/Municipalities/geostat-population-regional-gdp/municipal-population-and-regional-gdp.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R4dea224f262d4e0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Population" sheetId="2" r:id="Rfb111adcceaf435e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional GDP" sheetId="3" r:id="R1355dd1b93cb41aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geography map" sheetId="4" r:id="R23710fb2f1d040af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R84a1de35e4f64689"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Population" sheetId="2" r:id="R561c4d48166648ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional GDP" sheetId="3" r:id="Ra52c7e161c6c4890"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geography map" sheetId="4" r:id="R93cd7c6c3efa4fa1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -361,7 +361,7 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="88" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -397,67 +397,75 @@
         <x:v>2015–2025; 704 rows; 0 official gaps.</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
+    <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="20" t="str">
-        <x:v>Regional GDP definition</x:v>
+        <x:v>Population component rules</x:v>
       </x:c>
       <x:c r="B6" s="21" t="str">
-        <x:v>Total GDP by region at current prices in million GEL; not municipal GDP.</x:v>
+        <x:v>7 explicit sum rules; 21 municipality-year rows in 2015–2017 add separately published starred city cells to the surrounding municipality.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="20" t="str">
-        <x:v>Regional GDP coverage</x:v>
+        <x:v>Regional GDP definition</x:v>
       </x:c>
       <x:c r="B7" s="21" t="str">
-        <x:v>2010–2024; 165 rows; 0 official gaps.</x:v>
+        <x:v>Total GDP by region at current prices in million GEL; not municipal GDP.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="20" t="str">
-        <x:v>Validation status</x:v>
+        <x:v>Regional GDP coverage</x:v>
       </x:c>
       <x:c r="B8" s="21" t="str">
-        <x:v>complete</x:v>
+        <x:v>2010–2024; 165 rows; 0 official gaps.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="20" t="str">
-        <x:v>Estimates created</x:v>
-      </x:c>
-      <x:c r="B9" s="21" t="n">
-        <x:v>0</x:v>
+        <x:v>Validation status</x:v>
+      </x:c>
+      <x:c r="B9" s="21" t="str">
+        <x:v>complete</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="20" t="str">
-        <x:v>Retrieval/review date</x:v>
-      </x:c>
-      <x:c r="B10" s="24" t="n">
-        <x:v>46237</x:v>
+        <x:v>Estimates created</x:v>
+      </x:c>
+      <x:c r="B10" s="21" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="20" t="str">
-        <x:v>Population source page</x:v>
-      </x:c>
-      <x:c r="B11" s="21" t="str">
-        <x:v>https://www.geostat.ge/en/modules/categories/41/population</x:v>
+        <x:v>Retrieval/review date</x:v>
+      </x:c>
+      <x:c r="B11" s="24" t="n">
+        <x:v>46237</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="20" t="str">
+        <x:v>Population source page</x:v>
+      </x:c>
+      <x:c r="B12" s="21" t="str">
+        <x:v>https://www.geostat.ge/en/modules/categories/41/population</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="20" t="str">
         <x:v>Regional GDP source page</x:v>
       </x:c>
-      <x:c r="B12" s="21" t="str">
+      <x:c r="B13" s="21" t="str">
         <x:v>https://www.geostat.ge/en/modules/categories/23/gross-domestic-product-gdp</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="22" t="str">
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="22" t="str">
         <x:v>Exclusions</x:v>
       </x:c>
-      <x:c r="B13" s="23" t="str">
+      <x:c r="B14" s="23" t="str">
         <x:v>Codes 05, 42, 43, 46, and 64; national GDP total retained only for reconciliation.</x:v>
       </x:c>
     </x:row>
@@ -483,7 +491,7 @@
     <x:col min="8" max="8" width="42" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="116" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="122" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -919,10 +927,10 @@
         <x:v>region.kakheti</x:v>
       </x:c>
       <x:c r="E12" s="30" t="n">
-        <x:v>38.4</x:v>
+        <x:v>58.2</x:v>
       </x:c>
       <x:c r="F12" s="31" t="n">
-        <x:v>38400</x:v>
+        <x:v>58200</x:v>
       </x:c>
       <x:c r="G12" s="32" t="n">
         <x:v>42005</x:v>
@@ -937,7 +945,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K12" t="str">
-        <x:v>Source sheet "1"; source row 39; year 2015 column W (cell W39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 39 + 35; year 2015 column W (cells W39 + W35); population_thousand = W39 + W35; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L12" s="32" t="n">
         <x:v>46237</x:v>
@@ -1603,10 +1611,10 @@
         <x:v>region.samegrelo_zemo_svaneti</x:v>
       </x:c>
       <x:c r="E30" s="30" t="n">
-        <x:v>62.9</x:v>
+        <x:v>106.7</x:v>
       </x:c>
       <x:c r="F30" s="31" t="n">
-        <x:v>62900</x:v>
+        <x:v>106700</x:v>
       </x:c>
       <x:c r="G30" s="32" t="n">
         <x:v>42005</x:v>
@@ -1621,7 +1629,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>Source sheet "1"; source row 61; year 2015 column W (cell W61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 61 + 58; year 2015 column W (cells W61 + W58); population_thousand = W61 + W58; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L30" s="32" t="n">
         <x:v>46237</x:v>
@@ -1907,10 +1915,10 @@
         <x:v>region.shida_kartli</x:v>
       </x:c>
       <x:c r="E38" s="30" t="n">
-        <x:v>77.6</x:v>
+        <x:v>125.4</x:v>
       </x:c>
       <x:c r="F38" s="31" t="n">
-        <x:v>77600</x:v>
+        <x:v>125400</x:v>
       </x:c>
       <x:c r="G38" s="32" t="n">
         <x:v>42005</x:v>
@@ -1925,7 +1933,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K38" t="str">
-        <x:v>Source sheet "1"; source row 86; year 2015 column W (cell W86); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 86 + 85; year 2015 column W (cells W86 + W85); population_thousand = W86 + W85; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L38" s="32" t="n">
         <x:v>46237</x:v>
@@ -2363,10 +2371,10 @@
         <x:v>region.guria</x:v>
       </x:c>
       <x:c r="E50" s="30" t="n">
-        <x:v>47.8</x:v>
+        <x:v>62.8</x:v>
       </x:c>
       <x:c r="F50" s="31" t="n">
-        <x:v>47800</x:v>
+        <x:v>62800</x:v>
       </x:c>
       <x:c r="G50" s="32" t="n">
         <x:v>42005</x:v>
@@ -2381,7 +2389,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K50" t="str">
-        <x:v>Source sheet "1"; source row 19; year 2015 column W (cell W19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 19 + 17; year 2015 column W (cells W19 + W17); population_thousand = W19 + W17; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L50" s="32" t="n">
         <x:v>46237</x:v>
@@ -2591,10 +2599,10 @@
         <x:v>region.samtskhe_javakheti</x:v>
       </x:c>
       <x:c r="E56" s="30" t="n">
-        <x:v>22.9</x:v>
+        <x:v>39.2</x:v>
       </x:c>
       <x:c r="F56" s="31" t="n">
-        <x:v>22900</x:v>
+        <x:v>39200</x:v>
       </x:c>
       <x:c r="G56" s="32" t="n">
         <x:v>42005</x:v>
@@ -2609,7 +2617,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K56" t="str">
-        <x:v>Source sheet "1"; source row 73; year 2015 column W (cell W73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 73 + 69; year 2015 column W (cells W73 + W69); population_thousand = W73 + W69; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L56" s="32" t="n">
         <x:v>46237</x:v>
@@ -2743,10 +2751,10 @@
         <x:v>region.mtskheta_mtianeti</x:v>
       </x:c>
       <x:c r="E60" s="30" t="n">
-        <x:v>46.8</x:v>
+        <x:v>54.6</x:v>
       </x:c>
       <x:c r="F60" s="31" t="n">
-        <x:v>46800</x:v>
+        <x:v>54600</x:v>
       </x:c>
       <x:c r="G60" s="32" t="n">
         <x:v>42005</x:v>
@@ -2761,7 +2769,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K60" t="str">
-        <x:v>Source sheet "1"; source row 49; year 2015 column W (cell W49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 49 + 45; year 2015 column W (cells W49 + W45); population_thousand = W49 + W45; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L60" s="32" t="n">
         <x:v>46237</x:v>
@@ -2819,10 +2827,10 @@
         <x:v>region.racha_lechkhumi_kvemo_svaneti</x:v>
       </x:c>
       <x:c r="E62" s="30" t="n">
-        <x:v>9.1</x:v>
+        <x:v>11.2</x:v>
       </x:c>
       <x:c r="F62" s="31" t="n">
-        <x:v>9100</x:v>
+        <x:v>11200</x:v>
       </x:c>
       <x:c r="G62" s="32" t="n">
         <x:v>42005</x:v>
@@ -2837,7 +2845,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K62" t="str">
-        <x:v>Source sheet "1"; source row 53; year 2015 column W (cell W53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 53 + 52; year 2015 column W (cells W53 + W52); population_thousand = W53 + W52; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L62" s="32" t="n">
         <x:v>46237</x:v>
@@ -3351,10 +3359,10 @@
         <x:v>region.kakheti</x:v>
       </x:c>
       <x:c r="E76" s="30" t="n">
-        <x:v>37.9</x:v>
+        <x:v>57.7</x:v>
       </x:c>
       <x:c r="F76" s="31" t="n">
-        <x:v>37900</x:v>
+        <x:v>57700</x:v>
       </x:c>
       <x:c r="G76" s="32" t="n">
         <x:v>42370</x:v>
@@ -3369,7 +3377,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K76" t="str">
-        <x:v>Source sheet "1"; source row 39; year 2016 column X (cell X39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 39 + 35; year 2016 column X (cells X39 + X35); population_thousand = X39 + X35; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L76" s="32" t="n">
         <x:v>46237</x:v>
@@ -4035,10 +4043,10 @@
         <x:v>region.samegrelo_zemo_svaneti</x:v>
       </x:c>
       <x:c r="E94" s="30" t="n">
-        <x:v>62.3</x:v>
+        <x:v>105.7</x:v>
       </x:c>
       <x:c r="F94" s="31" t="n">
-        <x:v>62300</x:v>
+        <x:v>105700</x:v>
       </x:c>
       <x:c r="G94" s="32" t="n">
         <x:v>42370</x:v>
@@ -4053,7 +4061,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K94" t="str">
-        <x:v>Source sheet "1"; source row 61; year 2016 column X (cell X61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 61 + 58; year 2016 column X (cells X61 + X58); population_thousand = X61 + X58; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L94" s="32" t="n">
         <x:v>46237</x:v>
@@ -4339,10 +4347,10 @@
         <x:v>region.shida_kartli</x:v>
       </x:c>
       <x:c r="E102" s="30" t="n">
-        <x:v>77.3</x:v>
+        <x:v>124.7</x:v>
       </x:c>
       <x:c r="F102" s="31" t="n">
-        <x:v>77300</x:v>
+        <x:v>124700</x:v>
       </x:c>
       <x:c r="G102" s="32" t="n">
         <x:v>42370</x:v>
@@ -4357,7 +4365,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K102" t="str">
-        <x:v>Source sheet "1"; source row 86; year 2016 column X (cell X86); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 86 + 85; year 2016 column X (cells X86 + X85); population_thousand = X86 + X85; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L102" s="32" t="n">
         <x:v>46237</x:v>
@@ -4795,10 +4803,10 @@
         <x:v>region.guria</x:v>
       </x:c>
       <x:c r="E114" s="30" t="n">
-        <x:v>47.4</x:v>
+        <x:v>62.3</x:v>
       </x:c>
       <x:c r="F114" s="31" t="n">
-        <x:v>47400</x:v>
+        <x:v>62300</x:v>
       </x:c>
       <x:c r="G114" s="32" t="n">
         <x:v>42370</x:v>
@@ -4813,7 +4821,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K114" t="str">
-        <x:v>Source sheet "1"; source row 19; year 2016 column X (cell X19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 19 + 17; year 2016 column X (cells X19 + X17); population_thousand = X19 + X17; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L114" s="32" t="n">
         <x:v>46237</x:v>
@@ -5023,10 +5031,10 @@
         <x:v>region.samtskhe_javakheti</x:v>
       </x:c>
       <x:c r="E120" s="30" t="n">
-        <x:v>22.8</x:v>
+        <x:v>39.2</x:v>
       </x:c>
       <x:c r="F120" s="31" t="n">
-        <x:v>22800</x:v>
+        <x:v>39200</x:v>
       </x:c>
       <x:c r="G120" s="32" t="n">
         <x:v>42370</x:v>
@@ -5041,7 +5049,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K120" t="str">
-        <x:v>Source sheet "1"; source row 73; year 2016 column X (cell X73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 73 + 69; year 2016 column X (cells X73 + X69); population_thousand = X73 + X69; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L120" s="32" t="n">
         <x:v>46237</x:v>
@@ -5175,10 +5183,10 @@
         <x:v>region.mtskheta_mtianeti</x:v>
       </x:c>
       <x:c r="E124" s="30" t="n">
-        <x:v>46.7</x:v>
+        <x:v>54.4</x:v>
       </x:c>
       <x:c r="F124" s="31" t="n">
-        <x:v>46700</x:v>
+        <x:v>54400</x:v>
       </x:c>
       <x:c r="G124" s="32" t="n">
         <x:v>42370</x:v>
@@ -5193,7 +5201,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K124" t="str">
-        <x:v>Source sheet "1"; source row 49; year 2016 column X (cell X49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 49 + 45; year 2016 column X (cells X49 + X45); population_thousand = X49 + X45; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L124" s="32" t="n">
         <x:v>46237</x:v>
@@ -5251,10 +5259,10 @@
         <x:v>region.racha_lechkhumi_kvemo_svaneti</x:v>
       </x:c>
       <x:c r="E126" s="30" t="n">
-        <x:v>9</x:v>
+        <x:v>11.1</x:v>
       </x:c>
       <x:c r="F126" s="31" t="n">
-        <x:v>9000</x:v>
+        <x:v>11100</x:v>
       </x:c>
       <x:c r="G126" s="32" t="n">
         <x:v>42370</x:v>
@@ -5269,7 +5277,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K126" t="str">
-        <x:v>Source sheet "1"; source row 53; year 2016 column X (cell X53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 53 + 52; year 2016 column X (cells X53 + X52); population_thousand = X53 + X52; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L126" s="32" t="n">
         <x:v>46237</x:v>
@@ -5783,10 +5791,10 @@
         <x:v>region.kakheti</x:v>
       </x:c>
       <x:c r="E140" s="30" t="n">
-        <x:v>37.4</x:v>
+        <x:v>57.2</x:v>
       </x:c>
       <x:c r="F140" s="31" t="n">
-        <x:v>37400</x:v>
+        <x:v>57200</x:v>
       </x:c>
       <x:c r="G140" s="32" t="n">
         <x:v>42736</x:v>
@@ -5801,7 +5809,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K140" t="str">
-        <x:v>Source sheet "1"; source row 39; year 2017 column Y (cell Y39); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 39 + 35; year 2017 column Y (cells Y39 + Y35); population_thousand = Y39 + Y35; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L140" s="32" t="n">
         <x:v>46237</x:v>
@@ -6467,10 +6475,10 @@
         <x:v>region.samegrelo_zemo_svaneti</x:v>
       </x:c>
       <x:c r="E158" s="30" t="n">
-        <x:v>61.5</x:v>
+        <x:v>104.2</x:v>
       </x:c>
       <x:c r="F158" s="31" t="n">
-        <x:v>61500</x:v>
+        <x:v>104200</x:v>
       </x:c>
       <x:c r="G158" s="32" t="n">
         <x:v>42736</x:v>
@@ -6485,7 +6493,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K158" t="str">
-        <x:v>Source sheet "1"; source row 61; year 2017 column Y (cell Y61); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 61 + 58; year 2017 column Y (cells Y61 + Y58); population_thousand = Y61 + Y58; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L158" s="32" t="n">
         <x:v>46237</x:v>
@@ -6771,10 +6779,10 @@
         <x:v>region.shida_kartli</x:v>
       </x:c>
       <x:c r="E166" s="30" t="n">
-        <x:v>76.9</x:v>
+        <x:v>123.8</x:v>
       </x:c>
       <x:c r="F166" s="31" t="n">
-        <x:v>76900</x:v>
+        <x:v>123800</x:v>
       </x:c>
       <x:c r="G166" s="32" t="n">
         <x:v>42736</x:v>
@@ -6789,7 +6797,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K166" t="str">
-        <x:v>Source sheet "1"; source row 86; year 2017 column Y (cell Y86); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 86 + 85; year 2017 column Y (cells Y86 + Y85); population_thousand = Y86 + Y85; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L166" s="32" t="n">
         <x:v>46237</x:v>
@@ -7227,10 +7235,10 @@
         <x:v>region.guria</x:v>
       </x:c>
       <x:c r="E178" s="30" t="n">
-        <x:v>47</x:v>
+        <x:v>61.8</x:v>
       </x:c>
       <x:c r="F178" s="31" t="n">
-        <x:v>47000</x:v>
+        <x:v>61800</x:v>
       </x:c>
       <x:c r="G178" s="32" t="n">
         <x:v>42736</x:v>
@@ -7245,7 +7253,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K178" t="str">
-        <x:v>Source sheet "1"; source row 19; year 2017 column Y (cell Y19); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 19 + 17; year 2017 column Y (cells Y19 + Y17); population_thousand = Y19 + Y17; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L178" s="32" t="n">
         <x:v>46237</x:v>
@@ -7455,10 +7463,10 @@
         <x:v>region.samtskhe_javakheti</x:v>
       </x:c>
       <x:c r="E184" s="30" t="n">
-        <x:v>22.7</x:v>
+        <x:v>39.3</x:v>
       </x:c>
       <x:c r="F184" s="31" t="n">
-        <x:v>22700</x:v>
+        <x:v>39300</x:v>
       </x:c>
       <x:c r="G184" s="32" t="n">
         <x:v>42736</x:v>
@@ -7473,7 +7481,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K184" t="str">
-        <x:v>Source sheet "1"; source row 73; year 2017 column Y (cell Y73); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 73 + 69; year 2017 column Y (cells Y73 + Y69); population_thousand = Y73 + Y69; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L184" s="32" t="n">
         <x:v>46237</x:v>
@@ -7607,10 +7615,10 @@
         <x:v>region.mtskheta_mtianeti</x:v>
       </x:c>
       <x:c r="E188" s="30" t="n">
-        <x:v>46.5</x:v>
+        <x:v>54.2</x:v>
       </x:c>
       <x:c r="F188" s="31" t="n">
-        <x:v>46500</x:v>
+        <x:v>54200</x:v>
       </x:c>
       <x:c r="G188" s="32" t="n">
         <x:v>42736</x:v>
@@ -7625,7 +7633,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K188" t="str">
-        <x:v>Source sheet "1"; source row 49; year 2017 column Y (cell Y49); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 49 + 45; year 2017 column Y (cells Y49 + Y45); population_thousand = Y49 + Y45; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L188" s="32" t="n">
         <x:v>46237</x:v>
@@ -7683,10 +7691,10 @@
         <x:v>region.racha_lechkhumi_kvemo_svaneti</x:v>
       </x:c>
       <x:c r="E190" s="30" t="n">
-        <x:v>8.8</x:v>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="F190" s="31" t="n">
-        <x:v>8800</x:v>
+        <x:v>10800</x:v>
       </x:c>
       <x:c r="G190" s="32" t="n">
         <x:v>42736</x:v>
@@ -7701,7 +7709,7 @@
         <x:v>(thousands)</x:v>
       </x:c>
       <x:c r="K190" t="str">
-        <x:v>Source sheet "1"; source row 53; year 2017 column Y (cell Y53); retained published thousands; persons = thousands * 1000; no estimates.</x:v>
+        <x:v>Source sheet "1"; source rows 53 + 52; year 2017 column Y (cells Y53 + Y52); population_thousand = Y53 + Y52; persons = thousands * 1000; no estimates.</x:v>
       </x:c>
       <x:c r="L190" s="32" t="n">
         <x:v>46237</x:v>

--- a/docs/Raw Data/Municipalities/geostat-population-regional-gdp/municipal-population-and-regional-gdp.xlsx
+++ b/docs/Raw Data/Municipalities/geostat-population-regional-gdp/municipal-population-and-regional-gdp.xlsx
@@ -19,7 +19,7 @@
   <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="@"/>
-    <x:numFmt numFmtId="202" formatCode="#,##0.0"/>
+    <x:numFmt numFmtId="202" formatCode="#,##0.000"/>
     <x:numFmt numFmtId="203" formatCode="#,##0"/>
   </x:numFmts>
   <x:fonts count="4">
